--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra982ea540cb3437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R73cdca6946c34539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rf6b755b686324be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R4ce1fb746750422f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44385,7 +44385,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaac97334d08475d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9836efac66e74a6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44554,7 +44554,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>e11a382425915e4242010d581867fade379cf7d2552bb3e1f475521ad5601c91</x:v>
+        <x:v>c38a1e075d9976ea234f0513844269a0bf320396912ad01f6e8cbe2436f3d689</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44562,7 +44562,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>8f09eeed95250938a395b27c64b561a3dc4194208aac36e685902b281f13b0e2</x:v>
+        <x:v>c3e28863ef5ca2394dcc84c576ef3576b0e1bf44b193bf51d896a814713c86d4</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R666c9ee77f52460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R6709852dac51457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R64e06212abf14915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R007f0e7ca0a44da1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra493638b4a774839"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ffd77ab96574448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>b9a25747acd45fda8b1d87350e7a56cf3062296d7bad0012f22b0a40395e8b4b</x:v>
+        <x:v>c61fb70214174cc554075ef38b2bcf49596000be1fb346abf819063621d58a6a</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>7420b93fc431cba1af71cb213eeb4a55e0a809716b4de5383041cbd46c00e528</x:v>
+        <x:v>88d0673fc598f08275abc59d7b065cf84cc847217e977a788facfe4647c84b97</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R64e06212abf14915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R007f0e7ca0a44da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R593c80242dc444bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rf07e35ee77f34a35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ffd77ab96574448"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cadcd9313894ea2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>c61fb70214174cc554075ef38b2bcf49596000be1fb346abf819063621d58a6a</x:v>
+        <x:v>0e53500e02bd980d75759b24c2b11b63628a0f12b3ff037228029424f1b439ca</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>88d0673fc598f08275abc59d7b065cf84cc847217e977a788facfe4647c84b97</x:v>
+        <x:v>46676f3681a22fed60ceec4fd41b5312c03833848da523b8a1d402888c3178c0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R05fef613e1ef4fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R12f734399ceb4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R79f1365e58a14abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R752dd0d741c34525"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -521,26 +521,26 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.75" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="41.25" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="36.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="11.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="13.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="15.5600004196167" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4855769915b4a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18a502dceb6a479b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43836,9 +43836,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="71.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="2.25" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="63.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="2" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>7bdc2bac3b137cecc8fa37079920e4face1376b3c91e127d2e83f8fbcaa6bcce</x:v>
+        <x:v>57898bc67e755ef933e29d1983bf8c2ba7e1e8ba7006bca1f7222b3f67772a8b</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>601ef68883470fa5d2be9909342cd3e7b41636bf788737f5f7c319932ab8cd67</x:v>
+        <x:v>f9f28a5914c49a4d81559b65c8a0d8491be268fe38f584f969062ffa432a54bb</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R79f1365e58a14abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R752dd0d741c34525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R59155ccd91964930"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R235a6a0e8ec148a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18a502dceb6a479b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4678dd6b491945dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>57898bc67e755ef933e29d1983bf8c2ba7e1e8ba7006bca1f7222b3f67772a8b</x:v>
+        <x:v>972b5b8130c04de1b5cae923083e12c6acf2b7b4979f6bb5dfcc1d93c5376cdf</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>f9f28a5914c49a4d81559b65c8a0d8491be268fe38f584f969062ffa432a54bb</x:v>
+        <x:v>3df899b45eca0812a5a6a29466bf81d1686b79c3959563a1f93e1122413fa3d5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R59155ccd91964930"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R235a6a0e8ec148a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9720a2b1d9fa441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rbbfeea7ce98c4738"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4678dd6b491945dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4cf62fc5cc84343"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>972b5b8130c04de1b5cae923083e12c6acf2b7b4979f6bb5dfcc1d93c5376cdf</x:v>
+        <x:v>65c29e2f9c107cc19e560482f5d3448039da0fb2e49d0f26bcbe0fd074e2d384</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>3df899b45eca0812a5a6a29466bf81d1686b79c3959563a1f93e1122413fa3d5</x:v>
+        <x:v>19a5fb0e6d491bb271a89dc4acf92d5a5121dc7894a4f6c9794ae9ede36e1b44</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9720a2b1d9fa441c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rbbfeea7ce98c4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra74fd23afdd7495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rca3c7832dfc0487e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4cf62fc5cc84343"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4b26f3677804f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>65c29e2f9c107cc19e560482f5d3448039da0fb2e49d0f26bcbe0fd074e2d384</x:v>
+        <x:v>7cf502cd3ead8f15d3cc5ea9cf393d0c789a84a4db3f9e1549426134a7360ccc</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>19a5fb0e6d491bb271a89dc4acf92d5a5121dc7894a4f6c9794ae9ede36e1b44</x:v>
+        <x:v>ea82041e3cbb38cd047f59c5ec34806edf5fe4e22dbd16e33d9eb86486246211</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra74fd23afdd7495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rca3c7832dfc0487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R073cf1183f1347ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R918a410d1c4743e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -303,7 +303,7 @@
   <x:tableColumns count="20">
     <x:tableColumn id="1" name="作品名称"/>
     <x:tableColumn id="2" name="女女关系层级"/>
-    <x:tableColumn id="3" name="百合归档依据"/>
+    <x:tableColumn id="3" name="百合归档结论"/>
     <x:tableColumn id="4" name="女女恋爱位置"/>
     <x:tableColumn id="5" name="女女关系最高明确度"/>
     <x:tableColumn id="6" name="关系构成"/>
@@ -599,7 +599,7 @@
         <x:v>女女关系层级</x:v>
       </x:c>
       <x:c r="C4" s="44" t="str">
-        <x:v>百合归档依据</x:v>
+        <x:v>百合归档结论</x:v>
       </x:c>
       <x:c r="D4" s="44" t="str">
         <x:v>女女恋爱位置</x:v>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4b26f3677804f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra204c32af4de4281"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43913,7 +43913,7 @@
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="27" t="str">
-        <x:v>百合归档依据</x:v>
+        <x:v>百合归档结论</x:v>
       </x:c>
       <x:c r="B11" s="27" t="str">
         <x:v>说明是作品分类、读者解读、非百合或证据不足，不能由单一标签替代。</x:v>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>7cf502cd3ead8f15d3cc5ea9cf393d0c789a84a4db3f9e1549426134a7360ccc</x:v>
+        <x:v>f188437be8a903101ca9608319d2d2e944c6bb960011b394522f8279748cc609</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>ea82041e3cbb38cd047f59c5ec34806edf5fe4e22dbd16e33d9eb86486246211</x:v>
+        <x:v>7bfa0cc694aca983e834e5b56aa89f1421fcca69faf46c44e1295a5e3884c964</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R073cf1183f1347ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R918a410d1c4743e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R50a24446f3594ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R6b53c3746f254e9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43827,7 +43827,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra204c32af4de4281"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45345603b4a94d52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43996,7 +43996,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>f188437be8a903101ca9608319d2d2e944c6bb960011b394522f8279748cc609</x:v>
+        <x:v>3f0a1948b5c9758abd3df716d185dac3fdf80dff0bcc9ec94331ae16277aa0f1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -44004,7 +44004,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>7bfa0cc694aca983e834e5b56aa89f1421fcca69faf46c44e1295a5e3884c964</x:v>
+        <x:v>00831dfdfd6151f6e9f05c6f6c1513586538c403f4e10f4a563e16b62043435a</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rd00aef9dd3bb4a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R912b47fa08e3469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R3acbc759a24742f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R2ee6f9eaff82427b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf86fa24f41a489c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4feac85674754d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>2ea9c897fa11d64f31ca0b750efad695f53e0eabdc6d6308813e7923a7cd9b9c</x:v>
+        <x:v>dcdbb92b1fba02bf8489dab84ce8a7a9019779c2358478ef10a1a47b200cd690</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>2b8c2b02ea268a71a9e93d592f203662f4c780e27af606ef76d8eaf09755840d</x:v>
+        <x:v>8b5872a64dd145218308669186927671d971756467dd36e9de0b3398bede036d</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R3acbc759a24742f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R2ee6f9eaff82427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R2af57f1edad0468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R0fa1229a00a841c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>数据快照日期为 2026-08-10。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
+        <x:v>数据快照日期为 2026-08-11。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4feac85674754d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dafc09db3584db4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45944,7 +45944,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-10。AniList 相关度 0、无精确条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-11。AniList 相关度 0、无精确条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -46090,7 +46090,7 @@
         <x:v>数据日期</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>dcdbb92b1fba02bf8489dab84ce8a7a9019779c2358478ef10a1a47b200cd690</x:v>
+        <x:v>d0e664d216eb817ec7a21a003947c631cb6e1b7791077ad2aa06a368a84f1515</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>8b5872a64dd145218308669186927671d971756467dd36e9de0b3398bede036d</x:v>
+        <x:v>47c00884b207e9662ba5f978d6e72cbee93b0791bffe04cc9e5e3ddfe8ba75bd</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R2af57f1edad0468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R0fa1229a00a841c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9b51337959cb4d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rdbac9d420c4a4259"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dafc09db3584db4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9708b8f0e8f54ccf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>d0e664d216eb817ec7a21a003947c631cb6e1b7791077ad2aa06a368a84f1515</x:v>
+        <x:v>eb752e9258df91db4dd8f1897526361e6cd1c51da1a5566b806a9ec221646cee</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>47c00884b207e9662ba5f978d6e72cbee93b0791bffe04cc9e5e3ddfe8ba75bd</x:v>
+        <x:v>da67c356d42fa4950cdd4d0271d71deae67a887c9ab79805195b5bf4e93bd334</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9b51337959cb4d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rdbac9d420c4a4259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9494c1d1e3d54966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R1db8ad235a2a4688"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9708b8f0e8f54ccf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa421bfe5cb4beb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>eb752e9258df91db4dd8f1897526361e6cd1c51da1a5566b806a9ec221646cee</x:v>
+        <x:v>d31292b3e9a8a2ea054db5b07bb4d1bb46cea30ced4b5fd9f3fbe13b7308c98c</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>da67c356d42fa4950cdd4d0271d71deae67a887c9ab79805195b5bf4e93bd334</x:v>
+        <x:v>832cb39aa377feb02414730ca091cffd27927f297361a2e0e0f8fce63b48ee56</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9494c1d1e3d54966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R1db8ad235a2a4688"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9df4f9ef98a64e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rd00ab29cfc3c4d1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa421bfe5cb4beb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551be0d654ae4aa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>d31292b3e9a8a2ea054db5b07bb4d1bb46cea30ced4b5fd9f3fbe13b7308c98c</x:v>
+        <x:v>9ba8675897a2401370f5e78e043d6bc3e37260d3a78eccfca6a04b55739c511e</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>832cb39aa377feb02414730ca091cffd27927f297361a2e0e0f8fce63b48ee56</x:v>
+        <x:v>b717d80d044766c070b4941dfd0007edb8f2edd6a887ae18434df2bc1434f075</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R9df4f9ef98a64e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rd00ab29cfc3c4d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Re20b3daa5b964603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R243d802ef6234ab7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>数据快照日期为 2026-08-11。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
+        <x:v>数据快照日期为 2026-08-12。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551be0d654ae4aa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605e4f99913f41c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45944,7 +45944,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-11。AniList 相关度 0、无精确条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-12。AniList 相关度 0、无精确条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -46090,7 +46090,7 @@
         <x:v>数据日期</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>2026-08-11</x:v>
+        <x:v>2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>9ba8675897a2401370f5e78e043d6bc3e37260d3a78eccfca6a04b55739c511e</x:v>
+        <x:v>25b5f9cf5486cd4c978379417ed10e13fe4276f551482cb69809f366829ed52e</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>b717d80d044766c070b4941dfd0007edb8f2edd6a887ae18434df2bc1434f075</x:v>
+        <x:v>93025a2e4c83213bb0aeee4f23ccf3c0eff6e8ce31df56233da543cce24fd5a3</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Re20b3daa5b964603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R243d802ef6234ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R2c4a02816a004118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R4716cfa15f9b44fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605e4f99913f41c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8166577a253b46a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>25b5f9cf5486cd4c978379417ed10e13fe4276f551482cb69809f366829ed52e</x:v>
+        <x:v>2b0bd0c8a4f78f4b5704320be8d6432ad377331a14340c3362cba9973c6977f2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>93025a2e4c83213bb0aeee4f23ccf3c0eff6e8ce31df56233da543cce24fd5a3</x:v>
+        <x:v>46d9ec056d3473cb6c5e3cffad5156995d77351645ee45ef4bd8657dabdcbc9e</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R2c4a02816a004118"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R4716cfa15f9b44fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R6148f65dd9d34fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R55987b8174654be5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2860,7 +2860,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S38" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T38" s="33" t="n">
         <x:v>0</x:v>
@@ -3250,7 +3250,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S44" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T44" s="33" t="str">
         <x:v>无精确条目</x:v>
@@ -4745,7 +4745,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S67" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T67" s="33" t="n">
         <x:v>0</x:v>
@@ -6630,7 +6630,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S96" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T96" s="33" t="n">
         <x:v>0</x:v>
@@ -7800,7 +7800,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S114" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>有</x:v>
       </x:c>
       <x:c r="T114" s="33" t="n">
         <x:v>82</x:v>
@@ -8450,7 +8450,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S124" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>有</x:v>
       </x:c>
       <x:c r="T124" s="33" t="n">
         <x:v>92</x:v>
@@ -10400,7 +10400,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S154" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T154" s="33" t="n">
         <x:v>0</x:v>
@@ -12935,7 +12935,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S193" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T193" s="33" t="n">
         <x:v>0</x:v>
@@ -15730,7 +15730,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S236" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T236" s="33" t="n">
         <x:v>0</x:v>
@@ -15795,7 +15795,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S237" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T237" s="33" t="n">
         <x:v>0</x:v>
@@ -16965,7 +16965,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S255" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T255" s="33" t="n">
         <x:v>60</x:v>
@@ -17225,7 +17225,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S259" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T259" s="33" t="n">
         <x:v>0</x:v>
@@ -17290,7 +17290,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S260" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T260" s="33" t="n">
         <x:v>0</x:v>
@@ -18915,7 +18915,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S285" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T285" s="33" t="n">
         <x:v>0</x:v>
@@ -19175,7 +19175,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S289" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T289" s="33" t="n">
         <x:v>0</x:v>
@@ -20800,7 +20800,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S314" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>有</x:v>
       </x:c>
       <x:c r="T314" s="33" t="n">
         <x:v>60</x:v>
@@ -21840,7 +21840,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S330" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T330" s="33" t="n">
         <x:v>0</x:v>
@@ -24895,7 +24895,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S377" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T377" s="33" t="n">
         <x:v>73</x:v>
@@ -26000,7 +26000,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S394" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T394" s="33" t="n">
         <x:v>79</x:v>
@@ -28665,7 +28665,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S435" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T435" s="33" t="n">
         <x:v>0</x:v>
@@ -31200,7 +31200,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S474" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T474" s="33" t="n">
         <x:v>0</x:v>
@@ -31460,7 +31460,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S478" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T478" s="33" t="n">
         <x:v>0</x:v>
@@ -34385,7 +34385,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S523" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T523" s="33" t="n">
         <x:v>0</x:v>
@@ -41730,7 +41730,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S636" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T636" s="33" t="n">
         <x:v>0</x:v>
@@ -42900,7 +42900,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S654" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T654" s="33" t="n">
         <x:v>0</x:v>
@@ -43550,7 +43550,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S664" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T664" s="33" t="n">
         <x:v>0</x:v>
@@ -44395,7 +44395,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S677" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T677" s="33" t="n">
         <x:v>80</x:v>
@@ -44785,7 +44785,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S683" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T683" s="33" t="n">
         <x:v>0</x:v>
@@ -45175,7 +45175,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S689" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T689" s="33" t="n">
         <x:v>0</x:v>
@@ -45565,7 +45565,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S695" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T695" s="33" t="n">
         <x:v>50</x:v>
@@ -45890,7 +45890,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S700" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="T700" s="33" t="n">
         <x:v>82</x:v>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8166577a253b46a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R750879fa290141e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>2b0bd0c8a4f78f4b5704320be8d6432ad377331a14340c3362cba9973c6977f2</x:v>
+        <x:v>d9fc4ccda1257f4bcd4143b0de86781839d24434325ccaaff65c809577b7bd5f</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>46d9ec056d3473cb6c5e3cffad5156995d77351645ee45ef4bd8657dabdcbc9e</x:v>
+        <x:v>16b1a58ff8c886e9462ebff7104c9ee4aa50a850ad71158a483b15accc8fc1ed</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R6148f65dd9d34fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R55987b8174654be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R98bb68a2101c442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R53e6f140ea0c4631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -703,7 +703,7 @@
         <x:v>工作压力、过劳、职业挫折、制作事故、言语冲突与饮酒场面；未作画面复核。</x:v>
       </x:c>
       <x:c r="O5" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P5" s="36" t="n">
         <x:v>13</x:v>
@@ -768,7 +768,7 @@
         <x:v>不告而别造成的离别恐惧、才能比较、自我贬低、哭泣与激烈关系冲突。</x:v>
       </x:c>
       <x:c r="O6" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P6" s="36" t="n">
         <x:v>27</x:v>
@@ -833,7 +833,7 @@
         <x:v>未成年人遭致命暴力与死亡、遗体与葬礼、欺骗性契约及对未成年人危机的利用、身体与灵魂分离、绝望导致的异变、自毁式牺牲、同伴请求阻止自己变成怪物、家庭谋杀后自杀的回忆、失恋与嫉妒、灾害和群体伤亡威胁。</x:v>
       </x:c>
       <x:c r="O7" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P7" s="36" t="n">
         <x:v>34</x:v>
@@ -898,7 +898,7 @@
         <x:v>心理恐怖、身体与记忆变形、死亡与暴力、囚禁与世界重写、情感操控、宗教意象、强烈占有性语言。</x:v>
       </x:c>
       <x:c r="O8" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P8" s="36" t="n">
         <x:v>35</x:v>
@@ -963,7 +963,7 @@
         <x:v>毕业与别离、舞台竞争、占有性措辞、歌曲与日常语言需区分。</x:v>
       </x:c>
       <x:c r="O9" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P9" s="36" t="n">
         <x:v>43</x:v>
@@ -1028,7 +1028,7 @@
         <x:v>夸张肢体冲突、枪炮与爆炸笑料，校园捉弄与公开出丑，机器人身体改造及对身体差异暴露的焦虑，BL 漫画与暗恋受挫笑料。</x:v>
       </x:c>
       <x:c r="O10" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P10" s="36" t="n">
         <x:v>48</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>未成年学生对成年教师的单方爱恋、师生权力差异、失恋与拒绝、关系依赖、社团选拔冲突、家庭离别和竞赛压力。</x:v>
       </x:c>
       <x:c r="O11" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P11" s="36" t="n">
         <x:v>50</x:v>
@@ -1158,7 +1158,7 @@
         <x:v>毕业与暂时分离、社团与学业压力、成年教师让学生穿表演服装并以身体尴尬制造笑料、舞台剧和歌词中的恋爱语言、成人配角的男性恋爱往事与交往笑料。</x:v>
       </x:c>
       <x:c r="O12" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P12" s="36" t="n">
         <x:v>56</x:v>
@@ -1223,7 +1223,7 @@
         <x:v>校园年龄角色卷入成人性权力结构、诱骗与同意不对等、兄妹乱伦性虐待、占有与亲密暴力、受害者自责与厌女污名、身体和心理暴力、自杀念头与坠落意象。</x:v>
       </x:c>
       <x:c r="O13" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P13" s="36" t="n">
         <x:v>60</x:v>
@@ -1288,7 +1288,7 @@
         <x:v>毕业与离别压力、旅行中的喜剧性尴尬、歌曲的强烈友情用语。</x:v>
       </x:c>
       <x:c r="O14" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P14" s="36" t="n">
         <x:v>65</x:v>
@@ -1353,7 +1353,7 @@
         <x:v>战争与阶级压迫、枪械爆炸、死亡及儿童死亡、家庭分离、精神创伤与幻觉、自杀意念／尝试、囚禁与暴力审讯、药物依赖和人体实验、妓院场景、异性性场面。</x:v>
       </x:c>
       <x:c r="O15" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P15" s="36" t="n">
         <x:v>69</x:v>
@@ -1365,13 +1365,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S15" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T15" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U15" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="57" customHeight="1">
@@ -1418,7 +1418,7 @@
         <x:v>多次腿部骨折与严重赛场伤病、长期复健、复发恐惧、竞技压力、失去奔跑未来的痛苦</x:v>
       </x:c>
       <x:c r="O16" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P16" s="36" t="n">
         <x:v>71</x:v>
@@ -1483,7 +1483,7 @@
         <x:v>严重社会焦虑与回避、反复自我贬低、夸张身体崩坏或死亡意象、成年人酒精依赖与醉酒、借钱不还和人际利用、公开出丑、危险跳台及轻伤。</x:v>
       </x:c>
       <x:c r="O17" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P17" s="36" t="n">
         <x:v>72</x:v>
@@ -1548,7 +1548,7 @@
         <x:v>未成年偶像的泳装、写真和身体话题，娱乐行业压力，造谣与偷拍，家庭经济压力，手足死亡与创伤反应，舞台事故。</x:v>
       </x:c>
       <x:c r="O18" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P18" s="36" t="n">
         <x:v>83</x:v>
@@ -1613,7 +1613,7 @@
         <x:v>夜间独行、低温、交通与露营安全风险；少量公共浴池或泡澡场景；本季未确认女女恋爱。</x:v>
       </x:c>
       <x:c r="O19" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P19" s="36" t="n">
         <x:v>89</x:v>
@@ -1678,7 +1678,7 @@
         <x:v>学校存续危机、战车炮击与碰撞、军事化竞技语境</x:v>
       </x:c>
       <x:c r="O20" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P20" s="36" t="n">
         <x:v>91</x:v>
@@ -1743,7 +1743,7 @@
         <x:v>对未成年角色的性化及“萝莉控”笑料、把同学画入带性意味同人构想的笑料、亲人早逝与丧亲、病弱和体型笑料、危险驾驶喜剧。</x:v>
       </x:c>
       <x:c r="O21" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P21" s="36" t="n">
         <x:v>92</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>学生对成年教师的单方爱恋与权力差异、失恋与拒绝、社团派系冲突、偏袒指控、公开竞争和表演压力。</x:v>
       </x:c>
       <x:c r="O22" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P22" s="36" t="n">
         <x:v>95</x:v>
@@ -1873,7 +1873,7 @@
         <x:v>告别与职业转折带来的失落；前后辈和职业制度中的权力差异；关系性质未明的男性背景台词。</x:v>
       </x:c>
       <x:c r="O23" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P23" s="36" t="n">
         <x:v>102</x:v>
@@ -1938,7 +1938,7 @@
         <x:v>成人教师强迫学生更换表演服装、学生身体和服装被用于笑料、表演事故后的身体尴尬与公开笑料、打闹、成人配角的失恋与交往笑料。</x:v>
       </x:c>
       <x:c r="O24" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P24" s="36" t="n">
         <x:v>103</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>高风险杂技、严苛训练、过劳与运动损伤、职业竞争、企业夺权。</x:v>
       </x:c>
       <x:c r="O25" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P25" s="36" t="n">
         <x:v>112</x:v>
@@ -2068,7 +2068,7 @@
         <x:v>未成年人夜间迷路与受寒，明火、燃气、低温、独行和交通风险，成年教师大量饮酒，少量集体泡澡场面。</x:v>
       </x:c>
       <x:c r="O26" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P26" s="36" t="n">
         <x:v>118</x:v>
@@ -2133,7 +2133,7 @@
         <x:v>制度性订婚、亲属／权力关系中的性化暗示、死亡与创伤、身体变形和汽车碰撞意象。</x:v>
       </x:c>
       <x:c r="O27" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P27" s="36" t="n">
         <x:v>125</x:v>
@@ -2198,7 +2198,7 @@
         <x:v>未成年角色的成长笑料、玩偶与手作喜剧、饮酒与照护场景。</x:v>
       </x:c>
       <x:c r="O28" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P28" s="36" t="n">
         <x:v>130</x:v>
@@ -2263,7 +2263,7 @@
         <x:v>亲人失踪与长期哀伤，校园排挤与背叛，嫉妒、散播流言及破坏出行，晕船和呕吐，海上及极地旅行风险。</x:v>
       </x:c>
       <x:c r="O29" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P29" s="36" t="n">
         <x:v>146</x:v>
@@ -2328,7 +2328,7 @@
         <x:v>文明崩溃与战争遗迹、枪械及物资争夺、生存资源短缺、高处坠落等危险、死亡与孤独议题；含共同沐浴等身体接近场景。</x:v>
       </x:c>
       <x:c r="O30" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P30" s="36" t="n">
         <x:v>161</x:v>
@@ -2393,7 +2393,7 @@
         <x:v>高频裸露与性化变身、未成年人被性化展示、带性意味的强制身体接触与亲属间侵犯、家庭虐待、人体实验、精神操控、校园霸凌、严重暴力、身体恐怖及角色死亡。</x:v>
       </x:c>
       <x:c r="O31" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P31" s="36" t="n">
         <x:v>186</x:v>
@@ -2458,7 +2458,7 @@
         <x:v>儿童死亡与丧亲、交通事故、内疚与哀伤、校园排斥和欺凌、儿童被利用及陷入危险、意识分离与昏迷、惊悚追逐、虚拟宠物受损与离别。</x:v>
       </x:c>
       <x:c r="O32" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P32" s="36" t="n">
         <x:v>187</x:v>
@@ -2523,7 +2523,7 @@
         <x:v>死亡与身体／灵魂异化、绝望与自我牺牲、时间循环、记忆重置、心理恐怖和悲剧性结局。</x:v>
       </x:c>
       <x:c r="O33" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P33" s="36" t="n">
         <x:v>189</x:v>
@@ -2588,7 +2588,7 @@
         <x:v>家庭冲突与疏离、过劳、生存式战斗、离别与幻想性死亡、长时间跨度、AI／人格连续性议题。</x:v>
       </x:c>
       <x:c r="O34" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P34" s="36" t="n">
         <x:v>192</x:v>
@@ -2653,7 +2653,7 @@
         <x:v>户外采集中的陡坡、河流、海岸与废弃设施风险；锤击取样、酸液及实验操作；少量温泉洗浴场景；本次 TV 范围没有女女恋爱确认。</x:v>
       </x:c>
       <x:c r="O35" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P35" s="36" t="n">
         <x:v>194</x:v>
@@ -2718,7 +2718,7 @@
         <x:v>奇幻战斗与受伤、死亡与丧亲、亲人失踪、情绪困境被利用、误认性别恋爱笑料、儿童与青少年遇险</x:v>
       </x:c>
       <x:c r="O36" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P36" s="36" t="n">
         <x:v>201</x:v>
@@ -2783,7 +2783,7 @@
         <x:v>男性同学告白与关系暂缓、选拔冲突、孤立、哭泣、比赛压力和分离焦虑。</x:v>
       </x:c>
       <x:c r="O37" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P37" s="36" t="n">
         <x:v>202</x:v>
@@ -2848,7 +2848,7 @@
         <x:v>家庭冲突、退部压力、毕业离别、前后辈权力差异与局部异性恋爱关系。</x:v>
       </x:c>
       <x:c r="O38" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P38" s="36" t="n">
         <x:v>203</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>主要角色为小学生和中学生；含夜间迷路、泳池清扫、泳装、儿童成长笑料和未成年人接触酒类的喜剧情节。</x:v>
       </x:c>
       <x:c r="O39" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P39" s="36" t="n">
         <x:v>204</x:v>
@@ -2978,7 +2978,7 @@
         <x:v>登山风险、高山反应、童年坠落与恐高、吃醋和分离不安。</x:v>
       </x:c>
       <x:c r="O40" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P40" s="36" t="n">
         <x:v>205</x:v>
@@ -3043,7 +3043,7 @@
         <x:v>主要人物多为儿童；含未成年角色的泳装／体型笑料、萤对小鞠的同床想象与单方倾慕，以及童年旧录像中的“嫁给哥哥”笑料。</x:v>
       </x:c>
       <x:c r="O41" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P41" s="36" t="n">
         <x:v>227</x:v>
@@ -3108,7 +3108,7 @@
         <x:v>宇宙战争、组织排挤、能力丧失、胁迫性冲突、高风险战斗与分离。</x:v>
       </x:c>
       <x:c r="O42" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P42" s="36" t="n">
         <x:v>229</x:v>
@@ -3173,7 +3173,7 @@
         <x:v>未成年角色旅行、浮潜与皮艇活动、离别哭泣；萤与小鞠的恋爱方向未在本片确认。</x:v>
       </x:c>
       <x:c r="O43" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P43" s="36" t="n">
         <x:v>232</x:v>
@@ -3238,7 +3238,7 @@
         <x:v>母亲死亡与哀伤。</x:v>
       </x:c>
       <x:c r="O44" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P44" s="36" t="n">
         <x:v>249</x:v>
@@ -3253,10 +3253,10 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T44" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U44" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="57" customHeight="1">
@@ -3303,7 +3303,7 @@
         <x:v>关系操控与依赖、排斥和遗弃、激烈争执、公开情绪崩溃、家庭困境</x:v>
       </x:c>
       <x:c r="O45" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P45" s="36" t="n">
         <x:v>272</x:v>
@@ -3368,7 +3368,7 @@
         <x:v>升学压力、毕业离别、共同生活结束、饮食与身体玩笑</x:v>
       </x:c>
       <x:c r="O46" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P46" s="36" t="n">
         <x:v>281</x:v>
@@ -3433,7 +3433,7 @@
         <x:v>死亡与战斗暴力、遗体与葬礼、欺骗性契约、身体与灵魂异化、绝望、自我牺牲、失恋、嫉妒、心理恐怖和悲剧性结尾。</x:v>
       </x:c>
       <x:c r="O47" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P47" s="36" t="n">
         <x:v>285</x:v>
@@ -3498,7 +3498,7 @@
         <x:v>舞台化武器战斗、嫉妒与依存、离别、牺牲、时间循环。</x:v>
       </x:c>
       <x:c r="O48" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P48" s="36" t="n">
         <x:v>295</x:v>
@@ -3563,7 +3563,7 @@
         <x:v>幻想段中的强迫变装、强迫式羞耻台词和单向新娘角色扮演；身体与服装笑料、宠物闹剧和迷路。</x:v>
       </x:c>
       <x:c r="O49" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P49" s="36" t="n">
         <x:v>301</x:v>
@@ -3628,7 +3628,7 @@
         <x:v>姊妹制度中的名分与权力压力、祥子对男性接触的强烈抗拒、婚约及家庭期待、单向执着、学园祭冲突与群体压力。</x:v>
       </x:c>
       <x:c r="O50" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P50" s="36" t="n">
         <x:v>304</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>毕业与分别、升学／职业选择的不确定性、对已故父亲和遗物相机的回忆；没有范围内确认的女女恋爱。</x:v>
       </x:c>
       <x:c r="O51" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P51" s="36" t="n">
         <x:v>312</x:v>
@@ -3758,7 +3758,7 @@
         <x:v>野外遇险、受伤与中毒；绑架、帮派威胁与打斗；酒精和烟草；狩猎、捕鱼、屠宰与食用动物；泡澡／裸身相关台词；范围内没有确认的女女恋爱。</x:v>
       </x:c>
       <x:c r="O52" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P52" s="36" t="n">
         <x:v>330</x:v>
@@ -3823,7 +3823,7 @@
         <x:v>校园暴力袭击与角色死亡、创伤和幸存者内疚、武器伤害、社会退缩与孤独、后段重现性叙事。</x:v>
       </x:c>
       <x:c r="O53" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P53" s="36" t="n">
         <x:v>357</x:v>
@@ -3888,7 +3888,7 @@
         <x:v>主要角色为小学生和中学生；含作业、羽毛球活动、轻微运动事故、照看幼童、蜡笔涂墙、轻度责备与照护者落泪；未作完整视听复核。</x:v>
       </x:c>
       <x:c r="O54" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P54" s="36" t="n">
         <x:v>365</x:v>
@@ -3953,7 +3953,7 @@
         <x:v>突发且未事先询问的接吻、一处在拒绝主动接吻后继续发生的亲密行为、针对女性同性欲望的贬抑言论、丧亲与强烈自我否定。</x:v>
       </x:c>
       <x:c r="O55" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P55" s="36" t="n">
         <x:v>383</x:v>
@@ -4018,7 +4018,7 @@
         <x:v>僵尸身体恐怖与血腥、洪水及灾害意象、历史政治暴力与处刑、工作压力、死亡与哀伤。</x:v>
       </x:c>
       <x:c r="O56" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P56" s="36" t="n">
         <x:v>388</x:v>
@@ -4083,7 +4083,7 @@
         <x:v>战车炮击、爆炸、碰撞、翻覆与竞技险情；学校竞争与高风险比赛语境</x:v>
       </x:c>
       <x:c r="O57" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P57" s="36" t="n">
         <x:v>396</x:v>
@@ -4148,7 +4148,7 @@
         <x:v>喜剧化魔法战斗与受伤、梦境侵入、诅咒和记忆操控、魔法契约、家庭失踪与可能消失的威胁，以及未成年角色相关的身体变形笑料。</x:v>
       </x:c>
       <x:c r="O58" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P58" s="36" t="n">
         <x:v>402</x:v>
@@ -4213,7 +4213,7 @@
         <x:v>交通事故与死亡、僵尸身体恐怖和肢解／枪击、强制管理与言语羞辱、跨性别角色被旧名称呼及青春期焦虑、儿童死亡与亲子哀伤、偶像行业压力、雷击创伤、危险摩托车特技、失忆和抑郁退缩、舞台坍塌。</x:v>
       </x:c>
       <x:c r="O59" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P59" s="36" t="n">
         <x:v>404</x:v>
@@ -4278,7 +4278,7 @@
         <x:v>魔法战斗、儿童卷入危险、监护与病痛、牺牲与告别、家人式“爱”的语境区分</x:v>
       </x:c>
       <x:c r="O60" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P60" s="36" t="n">
         <x:v>405</x:v>
@@ -4343,7 +4343,7 @@
         <x:v>自杀、枪击与死亡、未成年人性内容、隐私侵犯、记忆操纵、身体恐怖、家庭离弃、邪教式控制及药物。</x:v>
       </x:c>
       <x:c r="O61" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P61" s="36" t="n">
         <x:v>415</x:v>
@@ -4408,7 +4408,7 @@
         <x:v>升学考试压力、毕业与分离焦虑、害羞推拉、身体与饮食笑料。</x:v>
       </x:c>
       <x:c r="O62" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P62" s="36" t="n">
         <x:v>419</x:v>
@@ -4473,7 +4473,7 @@
         <x:v>幻想战斗与未成年人遇险、反派操控情绪、家庭分离、短暂失忆、职业与家庭期待冲突、单向婚约笑料</x:v>
       </x:c>
       <x:c r="O63" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P63" s="36" t="n">
         <x:v>420</x:v>
@@ -4538,7 +4538,7 @@
         <x:v>姊妹制度中的名分与权力压力、领养与失亲创伤、害怕被抛弃、家出、选举竞争、误解与拒绝、男性婚约背景。</x:v>
       </x:c>
       <x:c r="O64" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P64" s="36" t="n">
         <x:v>423</x:v>
@@ -4603,7 +4603,7 @@
         <x:v>成年人频繁吸烟与饮酒、夸张肢体冲突和捉弄、围绕小学生角色的洗浴／身体与穿衣笑料。</x:v>
       </x:c>
       <x:c r="O65" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P65" s="36" t="n">
         <x:v>452</x:v>
@@ -4668,7 +4668,7 @@
         <x:v>分离、悲伤、身体亲密、快速剪辑与舞台演出。</x:v>
       </x:c>
       <x:c r="O66" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P66" s="36" t="n">
         <x:v>458</x:v>
@@ -4680,7 +4680,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S66" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T66" s="33" t="n">
         <x:v>85</x:v>
@@ -4733,7 +4733,7 @@
         <x:v>战车炮击、爆炸、碰撞与翻覆；升学与留级压力；校际竞争和欺敌战术</x:v>
       </x:c>
       <x:c r="O67" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P67" s="36" t="n">
         <x:v>466</x:v>
@@ -4798,7 +4798,7 @@
         <x:v>姊妹制度中的名分和选择压力、毕业分离、亲吻请求、嫉妒、校内传闻、年龄差与师生权力风险。</x:v>
       </x:c>
       <x:c r="O68" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P68" s="36" t="n">
         <x:v>477</x:v>
@@ -4863,7 +4863,7 @@
         <x:v>中学生角色的亲吻、婚姻和恋爱想象被用于喜剧，部分肢体接触与恋爱台词属于角色扮演或幻想。</x:v>
       </x:c>
       <x:c r="O69" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P69" s="36" t="n">
         <x:v>479</x:v>
@@ -4928,7 +4928,7 @@
         <x:v>战车炮击、碰撞与翻覆；升学和家庭照护压力；系列比赛未完结</x:v>
       </x:c>
       <x:c r="O70" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P70" s="36" t="n">
         <x:v>494</x:v>
@@ -4993,7 +4993,7 @@
         <x:v>未成年女学生、雪地跌落、恶梦与追逐的轻度喜剧场面；未作视听复核。</x:v>
       </x:c>
       <x:c r="O71" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P71" s="36" t="n">
         <x:v>495</x:v>
@@ -5058,7 +5058,7 @@
         <x:v>战争、革命、处刑、死亡、阶级暴力、政治压迫、强迫身体接触、性别角色冲突与恋爱悲剧。</x:v>
       </x:c>
       <x:c r="O72" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P72" s="36" t="n">
         <x:v>505</x:v>
@@ -5123,7 +5123,7 @@
         <x:v>怪物袭击与生命危险、身份及物种不确定、短暂分离、温泉脱衣与身体差异喜剧。</x:v>
       </x:c>
       <x:c r="O73" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P73" s="36" t="n">
         <x:v>513</x:v>
@@ -5188,7 +5188,7 @@
         <x:v>登山与天气风险、恐高焦虑、朋友冲突、吃醋与分离不安。</x:v>
       </x:c>
       <x:c r="O74" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P74" s="36" t="n">
         <x:v>516</x:v>
@@ -5253,7 +5253,7 @@
         <x:v>未记录</x:v>
       </x:c>
       <x:c r="O75" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P75" s="36" t="n">
         <x:v>526</x:v>
@@ -5318,7 +5318,7 @@
         <x:v>家族婚约与婚姻压力、亲属间姊妹关系、心脏手术、未成年出走计划、宗教志愿与同性爱恋冲突、分离及强烈情绪困扰。</x:v>
       </x:c>
       <x:c r="O76" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P76" s="36" t="n">
         <x:v>529</x:v>
@@ -5383,7 +5383,7 @@
         <x:v>儿童战斗与重伤、住院与身体障碍、主从制度、牺牲与告别、家庭式“爱”需与恋爱区分</x:v>
       </x:c>
       <x:c r="O77" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P77" s="36" t="n">
         <x:v>530</x:v>
@@ -5448,7 +5448,7 @@
         <x:v>主要角色包括小学生和中学生；含旅行准备与泳衣赠与。</x:v>
       </x:c>
       <x:c r="O78" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P78" s="36" t="n">
         <x:v>556</x:v>
@@ -5513,7 +5513,7 @@
         <x:v>总集篇压缩、少女对成年男教师的单向爱恋、独奏选拔与竞赛压力。</x:v>
       </x:c>
       <x:c r="O79" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P79" s="36" t="n">
         <x:v>577</x:v>
@@ -5578,7 +5578,7 @@
         <x:v>社交孤立、轻度误会、饮食与体重话题</x:v>
       </x:c>
       <x:c r="O80" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P80" s="36" t="n">
         <x:v>582</x:v>
@@ -5643,7 +5643,7 @@
         <x:v>中学生角色的性化玩笑与幻想、拒绝和逃开后仍被追逐求吻、洗浴情节、夸张肢体冲突与纠缠。</x:v>
       </x:c>
       <x:c r="O81" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P81" s="36" t="n">
         <x:v>605</x:v>
@@ -5708,7 +5708,7 @@
         <x:v>校园排斥与嘲弄、魔法造成的非自愿情感变化、情绪操纵与抽取、幻想战斗和生命危险、梦境／身体异变画面、导弹危机。</x:v>
       </x:c>
       <x:c r="O82" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P82" s="36" t="n">
         <x:v>607</x:v>
@@ -5773,7 +5773,7 @@
         <x:v>升学与离别、饮食和身体玩笑、男性关注及嫉妒话题、剧中小说的恋爱词汇。</x:v>
       </x:c>
       <x:c r="O83" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P83" s="36" t="n">
         <x:v>619</x:v>
@@ -5838,7 +5838,7 @@
         <x:v>成年人吸烟饮酒、夸张肢体冲突与恶作剧、小学生角色的洗浴和身体笑料</x:v>
       </x:c>
       <x:c r="O84" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P84" s="36" t="n">
         <x:v>632</x:v>
@@ -5903,7 +5903,7 @@
         <x:v>校园排挤与集体孤立、性化流言和辱骂、以死亡表达绝望及自杀意念、丧亲与病逝、家庭语言虐待、职业竞争与权力不对等、公开受害经历的伦理争议。</x:v>
       </x:c>
       <x:c r="O85" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P85" s="36" t="n">
         <x:v>633</x:v>
@@ -5968,7 +5968,7 @@
         <x:v>成年人吸烟与饮酒、夸张恶作剧和肢体冲突、小学生角色的身体与穿衣笑料、关于成长和分别的轻度感伤。</x:v>
       </x:c>
       <x:c r="O86" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P86" s="36" t="n">
         <x:v>636</x:v>
@@ -6033,7 +6033,7 @@
         <x:v>被迫选修；学校存续压力；军事装备竞技、炮击和车辆遇险；以男性恋爱为对象的喜剧台词</x:v>
       </x:c>
       <x:c r="O87" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P87" s="36" t="n">
         <x:v>642</x:v>
@@ -6098,7 +6098,7 @@
         <x:v>中学生角色的约会、亲吻与女朋友语汇常处于喜剧、游戏或排练情境，欲望方向并不对称。</x:v>
       </x:c>
       <x:c r="O88" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P88" s="36" t="n">
         <x:v>644</x:v>
@@ -6163,7 +6163,7 @@
         <x:v>战车炮击、爆炸、碰撞、翻覆与夜战；升学、毕业与学校延续压力；本篇为六部制系列中段</x:v>
       </x:c>
       <x:c r="O89" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P89" s="36" t="n">
         <x:v>651</x:v>
@@ -6228,7 +6228,7 @@
         <x:v>校园霸凌与校方淡化、家庭冲突与离家、激烈争执及肢体冲突、酒精、职场种族歧视、丧亲与被父母遗弃、职业及财务压力。</x:v>
       </x:c>
       <x:c r="O90" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P90" s="36" t="n">
         <x:v>661</x:v>
@@ -6293,7 +6293,7 @@
         <x:v>死亡与离别、创伤记忆、血与身体疼痛、疑似自杀及自伤意象、儿童／少女受险、嫉妒与信任破裂、宗教与赎罪意象</x:v>
       </x:c>
       <x:c r="O91" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P91" s="36" t="n">
         <x:v>663</x:v>
@@ -6358,7 +6358,7 @@
         <x:v>幻想枪械与近战暴力、角色死亡与肢体创伤、对 Faunus 的歧视、心理操控与嫁祸、前男性盟友的胁迫占有和暴力</x:v>
       </x:c>
       <x:c r="O92" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P92" s="36" t="n">
         <x:v>669</x:v>
@@ -6370,13 +6370,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S92" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T92" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U92" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="57" customHeight="1">
@@ -6423,7 +6423,7 @@
         <x:v>自行车练习与楼梯险情、针线和衣物破损、未成年角色胸罩带笑料、教师要求学生脱下待修衣物的越界式喜剧</x:v>
       </x:c>
       <x:c r="O93" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P93" s="36" t="n">
         <x:v>679</x:v>
@@ -6488,7 +6488,7 @@
         <x:v>高频肢体暴力与羞辱式搞笑、欺骗和胁迫、涉及未成年人的身体／生殖器／性知识笑话、窥视裙底企图、围绕身体与性别的猜测及带偏见玩笑、排泄物与体液笑料</x:v>
       </x:c>
       <x:c r="O94" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P94" s="36" t="n">
         <x:v>681</x:v>
@@ -6553,7 +6553,7 @@
         <x:v>校园与升学压力、离别焦虑、咖啡因反应与轻度身体喜剧。</x:v>
       </x:c>
       <x:c r="O95" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P95" s="36" t="n">
         <x:v>695</x:v>
@@ -6618,7 +6618,7 @@
         <x:v>入学受阻、返乡、轻度嫉妒式反应与烧烤烟雾误会</x:v>
       </x:c>
       <x:c r="O96" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P96" s="36" t="n">
         <x:v>697</x:v>
@@ -6683,7 +6683,7 @@
         <x:v>登山与天气风险、高原反应、恐高焦虑、朋友争吵、裙子恶作剧、温泉／泳装场面</x:v>
       </x:c>
       <x:c r="O97" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P97" s="36" t="n">
         <x:v>707</x:v>
@@ -6748,7 +6748,7 @@
         <x:v>未经同意的用药与身体改变、青春期身体和如厕内容、未成年身体的性化喜剧、成年意识处于青春期身体。</x:v>
       </x:c>
       <x:c r="O98" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P98" s="36" t="n">
         <x:v>720</x:v>
@@ -6813,7 +6813,7 @@
         <x:v>儿童卷入魔法战斗、重伤与灾害、亲子控制与创伤、丧亲、替代身份、使魔契约和保护性用语可能被误读为恋爱</x:v>
       </x:c>
       <x:c r="O99" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P99" s="36" t="n">
         <x:v>740</x:v>
@@ -6878,7 +6878,7 @@
         <x:v>未成年角色受伤、组织阴谋、人体／机械实验、战斗威胁，以及含身体接近意味的喜剧式追求。</x:v>
       </x:c>
       <x:c r="O100" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P100" s="36" t="n">
         <x:v>751</x:v>
@@ -6943,7 +6943,7 @@
         <x:v>校园嘲弄、地牢怪物、古龙危机与幻想战斗。</x:v>
       </x:c>
       <x:c r="O101" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P101" s="36" t="n">
         <x:v>755</x:v>
@@ -7008,7 +7008,7 @@
         <x:v>亲子失约、童年走失与分离、纪念物遗失、歉疚</x:v>
       </x:c>
       <x:c r="O102" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P102" s="36" t="n">
         <x:v>757</x:v>
@@ -7073,7 +7073,7 @@
         <x:v>未成年角色的性化身体笑料、未经同意的身体接触、成人教师与学生的单向迷恋、性别与身体笑料</x:v>
       </x:c>
       <x:c r="O103" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P103" s="36" t="n">
         <x:v>761</x:v>
@@ -7138,7 +7138,7 @@
         <x:v>人体实验、克隆体死亡、恐怖袭击与严重受伤；越界式性追求和身体笑料；未成年角色受害。</x:v>
       </x:c>
       <x:c r="O104" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P104" s="36" t="n">
         <x:v>780</x:v>
@@ -7203,7 +7203,7 @@
         <x:v>战争与死亡、青少年被军事与宗教机构利用、被迫作出性别选择、悲伤与幸存者负担、亲密边界侵犯、姐妹关系中的性意味、年龄差与指导关系中的权力不对称。</x:v>
       </x:c>
       <x:c r="O105" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P105" s="36" t="n">
         <x:v>790</x:v>
@@ -7268,7 +7268,7 @@
         <x:v>血腥战斗、死亡、严重身体伤害、精神操纵、家庭与继承压力、未成年人参与高风险除灵。</x:v>
       </x:c>
       <x:c r="O106" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P106" s="36" t="n">
         <x:v>793</x:v>
@@ -7333,7 +7333,7 @@
         <x:v>初中女生身体与服装的摄影／舞台凝视、意外露出笑话、共同淋浴与互相冲洗、戏谑脱衣、身体自卑、轻微运动碰撞。</x:v>
       </x:c>
       <x:c r="O107" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P107" s="36" t="n">
         <x:v>795</x:v>
@@ -7398,7 +7398,7 @@
         <x:v>校园排斥与欺凌、占有和控制、自伤、相约自杀、死亡、药物依赖与烟草、持刀伤人、绝症、亲属间越界依恋。</x:v>
       </x:c>
       <x:c r="O108" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P108" s="36" t="n">
         <x:v>801</x:v>
@@ -7463,7 +7463,7 @@
         <x:v>校园日常、美术馆与泳池活动、共同留宿、家务喜剧。</x:v>
       </x:c>
       <x:c r="O109" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P109" s="36" t="n">
         <x:v>806</x:v>
@@ -7528,7 +7528,7 @@
         <x:v>战斗、怪物袭击、爆炸、Faunus 歧视、犯罪组织、男性单恋和求舞、反派胁迫与列车灾难。</x:v>
       </x:c>
       <x:c r="O110" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P110" s="36" t="n">
         <x:v>813</x:v>
@@ -7540,13 +7540,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S110" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T110" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U110" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="57" customHeight="1">
@@ -7593,7 +7593,7 @@
         <x:v>单方面婚礼笑料、儿童角色的喜欢与结婚语言、伊露露—竹人恋爱方向、露科亚—翔太支线的性化诱惑与抵触、龙族暴力。</x:v>
       </x:c>
       <x:c r="O111" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P111" s="36" t="n">
         <x:v>817</x:v>
@@ -7658,7 +7658,7 @@
         <x:v>教师服装与身体笑话、集体入浴、体重与节食笑话、疾病照护、客座角色对男性的单相思。</x:v>
       </x:c>
       <x:c r="O112" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P112" s="36" t="n">
         <x:v>825</x:v>
@@ -7723,7 +7723,7 @@
         <x:v>魔女受迫害历史再现、校园惩罚与公开嘲弄、同伴争吵与绝交措辞、巨人出现与魔法危机。</x:v>
       </x:c>
       <x:c r="O113" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P113" s="36" t="n">
         <x:v>838</x:v>
@@ -7788,7 +7788,7 @@
         <x:v>姐妹争吵、校园竞争、恋人身份谜题与未成年角色的喜剧化身体笑料。</x:v>
       </x:c>
       <x:c r="O114" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P114" s="36" t="n">
         <x:v>840</x:v>
@@ -7853,7 +7853,7 @@
         <x:v>未获同意的性追求与亲吻尝试、疑似下药企图、窃取贴身衣物、反复掀裙与内衣笑料、未成年泳装和身体性笑料、肢体惩罚、暴力与爆炸、昏迷、儿童人体实验及生命危险。</x:v>
       </x:c>
       <x:c r="O115" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P115" s="36" t="n">
         <x:v>841</x:v>
@@ -7918,7 +7918,7 @@
         <x:v>儿童时期遭成年男性性侵害与强迫亲吻、监护人忽视并否定求助、跟踪与越界粉丝、饮食障碍及催吐、体重羞辱和身体凝视、严苛竞争压力。</x:v>
       </x:c>
       <x:c r="O116" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P116" s="36" t="n">
         <x:v>847</x:v>
@@ -7983,7 +7983,7 @@
         <x:v>舞台竞争、象征性武器战斗、失去闪耀、强制分离与反复演出。</x:v>
       </x:c>
       <x:c r="O117" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P117" s="36" t="n">
         <x:v>866</x:v>
@@ -8048,7 +8048,7 @@
         <x:v>性化评论、洗浴换衣喜剧、家庭分离与竞赛威胁。</x:v>
       </x:c>
       <x:c r="O118" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P118" s="36" t="n">
         <x:v>869</x:v>
@@ -8113,7 +8113,7 @@
         <x:v>求婚式想象、亲吻拟声、相思病角色扮演、鼻血与身体话题笑料。</x:v>
       </x:c>
       <x:c r="O119" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P119" s="36" t="n">
         <x:v>872</x:v>
@@ -8178,7 +8178,7 @@
         <x:v>中学生群像喜剧、角色幻想中的恋爱情景、澡堂场景、夸张肢体笑料和整蛊</x:v>
       </x:c>
       <x:c r="O120" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P120" s="36" t="n">
         <x:v>880</x:v>
@@ -8243,7 +8243,7 @@
         <x:v>害怕分离、嫉妒和占有性语言；“没有对方就无法前进”的依赖表述；过劳与睡眠不足；泳装情节。</x:v>
       </x:c>
       <x:c r="O121" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P121" s="36" t="n">
         <x:v>883</x:v>
@@ -8308,7 +8308,7 @@
         <x:v>赛场受伤、退赛、过度训练、竞技失败、自我否定、不可见朋友及高强度比赛。</x:v>
       </x:c>
       <x:c r="O122" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P122" s="36" t="n">
         <x:v>885</x:v>
@@ -8373,7 +8373,7 @@
         <x:v>社团分组与公开投票、前后辈压力、练习挫败、竞赛压力和第一顺位玩笑。</x:v>
       </x:c>
       <x:c r="O123" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P123" s="36" t="n">
         <x:v>905</x:v>
@@ -8438,7 +8438,7 @@
         <x:v>姐妹争吵、恋人身份谜题、朋友间情绪波动、校园喜剧。</x:v>
       </x:c>
       <x:c r="O124" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P124" s="36" t="n">
         <x:v>916</x:v>
@@ -8503,7 +8503,7 @@
         <x:v>Q 版夸张事故与灾害喜剧、身体互换和变形笑点、轻度惊吓、食物与旅行危险玩笑、多乐队角色快速切换。</x:v>
       </x:c>
       <x:c r="O125" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P125" s="36" t="n">
         <x:v>920</x:v>
@@ -8568,7 +8568,7 @@
         <x:v>贫困、童年分离、家庭契约、贵族婚配压力、战争创伤与长期失联。</x:v>
       </x:c>
       <x:c r="O126" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P126" s="36" t="n">
         <x:v>922</x:v>
@@ -8633,7 +8633,7 @@
         <x:v>亲职失责与家庭冲突、职场权力压力、绑架与非自愿束缚、性骚扰／窥视、强迫脱衣与未成年角色性化玩笑、言语攻击和肢体冲突。</x:v>
       </x:c>
       <x:c r="O127" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P127" s="36" t="n">
         <x:v>928</x:v>
@@ -8698,7 +8698,7 @@
         <x:v>校园与咖啡店日常、姐姐／妹妹式玩笑、制服与咖啡因笑料、朋友分开时的寂寞。</x:v>
       </x:c>
       <x:c r="O128" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P128" s="36" t="n">
         <x:v>933</x:v>
@@ -8763,7 +8763,7 @@
         <x:v>严重社交焦虑、自我否定、文化祭公开表演压力、未经同意提交报名表后的边界协商、舞台事故、成年角色饮酒与总集篇剪辑压缩。</x:v>
       </x:c>
       <x:c r="O129" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P129" s="36" t="n">
         <x:v>941</x:v>
@@ -8781,7 +8781,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="U129" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="57" customHeight="1">
@@ -8828,7 +8828,7 @@
         <x:v>贫困与食物不足、喜剧化伤害及战斗威胁、侵入梦境并试图用暗示促使对方献血、15 岁角色暴露度较高的变身服装及相关玩笑、家人失踪／被封印与角色可能消失的恐惧。</x:v>
       </x:c>
       <x:c r="O130" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P130" s="36" t="n">
         <x:v>947</x:v>
@@ -8893,7 +8893,7 @@
         <x:v>未出生双胞胎妹妹死亡与哀悼、幸存者内疚、梦／幻视、自我责罚式训练、伤病风险、强烈竞技压力与哭泣。</x:v>
       </x:c>
       <x:c r="O131" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P131" s="36" t="n">
         <x:v>951</x:v>
@@ -8958,7 +8958,7 @@
         <x:v>枪械与冷兵器战斗、怪物袭击、校园霸凌与勒索、针对 Faunus 的歧视及暴力叙述。</x:v>
       </x:c>
       <x:c r="O132" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P132" s="36" t="n">
         <x:v>958</x:v>
@@ -8970,13 +8970,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S132" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T132" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U132" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="57" customHeight="1">
@@ -9023,7 +9023,7 @@
         <x:v>幻想战斗、未成年人遇险、分离与失落、反派操纵、单向青春期告白与被拒。</x:v>
       </x:c>
       <x:c r="O133" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P133" s="36" t="n">
         <x:v>966</x:v>
@@ -9088,7 +9088,7 @@
         <x:v>父亲去世后的回忆、毕业与离别情绪，以及反复出现的异性迷恋笑料</x:v>
       </x:c>
       <x:c r="O134" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P134" s="36" t="n">
         <x:v>977</x:v>
@@ -9153,7 +9153,7 @@
         <x:v>性骚扰与掀裙回忆、未成年年龄差性化玩笑、身体笑话、占有欲及以自伤威胁作笑料、网络攻击、抽卡与打赏情节、种族化夸张想象</x:v>
       </x:c>
       <x:c r="O135" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P135" s="36" t="n">
         <x:v>992</x:v>
@@ -9218,7 +9218,7 @@
         <x:v>中学生群像喜剧、水球和湿身笑料、留宿、拍摄睡脸的恶作剧。</x:v>
       </x:c>
       <x:c r="O136" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P136" s="36" t="n">
         <x:v>993</x:v>
@@ -9283,7 +9283,7 @@
         <x:v>泳装与公共泳池、不会游泳的安全话题、校园情书。</x:v>
       </x:c>
       <x:c r="O137" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P137" s="36" t="n">
         <x:v>996</x:v>
@@ -9348,7 +9348,7 @@
         <x:v>来客未经同意触碰角色、温泉裸露与身体笑料、冒充熟人诱导亲密、死亡与离别主题</x:v>
       </x:c>
       <x:c r="O138" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P138" s="36" t="n">
         <x:v>1000</x:v>
@@ -9413,7 +9413,7 @@
         <x:v>口头拒绝后仍继续亲吻与身体压制、浴室和温泉中的裸露及性化情节、未成年角色间性话题、掌掴、焦虑与反复自我贬低</x:v>
       </x:c>
       <x:c r="O139" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P139" s="36" t="n">
         <x:v>1034</x:v>
@@ -9478,7 +9478,7 @@
         <x:v>高中年龄亲生双胞胎姐妹间的恋爱指向、床铺与亲密暗示笑料、嫉妒和关系误会、咲夜对奏的单向追求及照片相关表述。</x:v>
       </x:c>
       <x:c r="O140" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P140" s="36" t="n">
         <x:v>1036</x:v>
@@ -9543,7 +9543,7 @@
         <x:v>奇幻暴力、未成年人遇险、校园欺凌、受制状态下的强迫约会要求、诅咒变形、控制型家长、家庭分离、监禁及石化威胁。</x:v>
       </x:c>
       <x:c r="O141" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P141" s="36" t="n">
         <x:v>1037</x:v>
@@ -9555,13 +9555,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S141" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T141" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U141" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="57" customHeight="1">
@@ -9608,7 +9608,7 @@
         <x:v>儿童虐待与忽视、强行带走与不稳定照料、持枪暴力、犯罪组织、监禁与逃亡、绑架、以未成年人为威胁对象。</x:v>
       </x:c>
       <x:c r="O142" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P142" s="36" t="n">
         <x:v>1039</x:v>
@@ -9673,7 +9673,7 @@
         <x:v>奇幻暴力与未成年人遇险、组织操控和实验、记忆改写、控制型亲子冲突、身体变化、年龄回退式回忆及校园恐怖情境。</x:v>
       </x:c>
       <x:c r="O143" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P143" s="36" t="n">
         <x:v>1049</x:v>
@@ -9738,7 +9738,7 @@
         <x:v>涉及小学生角色的性化笑料、成年外形角色对小学生反复作出令其抗拒的身体接近、裸露与身体笑料、嫉妒和占有欲笑料、饮酒、奇幻暴力与死亡威胁。</x:v>
       </x:c>
       <x:c r="O144" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P144" s="36" t="n">
         <x:v>1071</x:v>
@@ -9803,7 +9803,7 @@
         <x:v>战争、未成年参战、负伤与死亡威胁、裸体及内衣式服装取景、第 7 话身体笑料与带性意味的接触。</x:v>
       </x:c>
       <x:c r="O145" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P145" s="36" t="n">
         <x:v>1085</x:v>
@@ -9868,7 +9868,7 @@
         <x:v>分离焦虑、依赖与排他表达；竞争与误解；同好会重组；偶像演出和轻度服务性镜头。</x:v>
       </x:c>
       <x:c r="O146" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P146" s="36" t="n">
         <x:v>1093</x:v>
@@ -9933,7 +9933,7 @@
         <x:v>暂时离开共同生活场所造成的失落与想念，家庭团聚与姐妹称呼，未成年角色的泳装、换装和身材笑料；英文字幕未同步画面复核。</x:v>
       </x:c>
       <x:c r="O147" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P147" s="36" t="n">
         <x:v>1103</x:v>
@@ -9998,7 +9998,7 @@
         <x:v>职场加班与留宿、成人饮酒、身体与换装笑话、恋爱式误会主要以喜剧方式呈现。</x:v>
       </x:c>
       <x:c r="O148" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P148" s="36" t="n">
         <x:v>1118</x:v>
@@ -10063,7 +10063,7 @@
         <x:v>父亲去世与遗物照片带来的回忆和悲伤、迁居、旧友重逢与离别情绪</x:v>
       </x:c>
       <x:c r="O149" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P149" s="36" t="n">
         <x:v>1123</x:v>
@@ -10128,7 +10128,7 @@
         <x:v>Q 版事故、灾害与身体变形喜剧，快速切换的群像短篇</x:v>
       </x:c>
       <x:c r="O150" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P150" s="36" t="n">
         <x:v>1147</x:v>
@@ -10193,7 +10193,7 @@
         <x:v>长期加班与留宿公司、内衣与换装笑话、游戏角色裙底笑话、成人职场饮酒、仿真枪与气枪笑话。</x:v>
       </x:c>
       <x:c r="O151" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P151" s="36" t="n">
         <x:v>1154</x:v>
@@ -10258,7 +10258,7 @@
         <x:v>战车炮击、车辆损伤、竞技险情、学校经费压力与夸张的队长崇拜喜剧</x:v>
       </x:c>
       <x:c r="O152" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P152" s="36" t="n">
         <x:v>1157</x:v>
@@ -10323,7 +10323,7 @@
         <x:v>演唱会音量与闪光、舞台竞争、大量歌曲表演、关系推进有限</x:v>
       </x:c>
       <x:c r="O153" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P153" s="36" t="n">
         <x:v>1170</x:v>
@@ -10388,7 +10388,7 @@
         <x:v>毕业与分离焦虑、恋爱话题和暧昧配对笑料、旅行中的更衣与身体话题笑料。</x:v>
       </x:c>
       <x:c r="O154" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P154" s="36" t="n">
         <x:v>1178</x:v>
@@ -10453,7 +10453,7 @@
         <x:v>严重社交焦虑、公开演出压力、夸张出丑笑料、成年角色饮酒及借钱笑料。</x:v>
       </x:c>
       <x:c r="O155" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P155" s="36" t="n">
         <x:v>1180</x:v>
@@ -10471,7 +10471,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="U155" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="57" customHeight="1">
@@ -10518,7 +10518,7 @@
         <x:v>高中生麻将比赛中的高压、晕厥与身体危险；超能力化的竞技表现和夸张身体反应；家庭分离、姊妹矛盾与全国赛压力；部分喜剧段落包含对高中女生身体的性化评论。</x:v>
       </x:c>
       <x:c r="O156" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P156" s="36" t="n">
         <x:v>1197</x:v>
@@ -10583,7 +10583,7 @@
         <x:v>儿童虐待、替代身份危机、儿童战斗与空间灾害</x:v>
       </x:c>
       <x:c r="O157" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P157" s="36" t="n">
         <x:v>1203</x:v>
@@ -10648,7 +10648,7 @@
         <x:v>18+成人内容；照护与亲密发展交错</x:v>
       </x:c>
       <x:c r="O158" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P158" s="36" t="n">
         <x:v>1209</x:v>
@@ -10660,7 +10660,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S158" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T158" s="33" t="n">
         <x:v>96</x:v>
@@ -10713,7 +10713,7 @@
         <x:v>大量肢解与流血、食人和身体恐怖、儿童受虐与遇险、性暴力威胁、人体改造、酷刑、死亡、自我牺牲、自杀及请求他人结束生命</x:v>
       </x:c>
       <x:c r="O159" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P159" s="36" t="n">
         <x:v>1217</x:v>
@@ -10778,7 +10778,7 @@
         <x:v>枪击与死亡、暗杀和政变、自尽、儿童遭殴打及人体实验、家庭暴力、贫困与阶级歧视、战争与革命、身份互换和长期冒名。</x:v>
       </x:c>
       <x:c r="O160" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P160" s="36" t="n">
         <x:v>1221</x:v>
@@ -10843,7 +10843,7 @@
         <x:v>竞赛压力与失败、团队冲突与排斥、成员离队和寻找失联伙伴、学校与舞台压力。</x:v>
       </x:c>
       <x:c r="O161" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P161" s="36" t="n">
         <x:v>1253</x:v>
@@ -10908,7 +10908,7 @@
         <x:v>Q 版夸张事故、灾害和身体变形喜剧，快速切换角色与三分钟短篇结构。</x:v>
       </x:c>
       <x:c r="O162" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P162" s="36" t="n">
         <x:v>1265</x:v>
@@ -10973,7 +10973,7 @@
         <x:v>未成年角色的更衣、内衣、泳装与身材笑料，兔女郎式制服，枪械和刀具笑料，咖啡因醉态，患病及死亡／哀伤提及。</x:v>
       </x:c>
       <x:c r="O163" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P163" s="36" t="n">
         <x:v>1278</x:v>
@@ -11038,7 +11038,7 @@
         <x:v>夸张战斗与爆炸、绑架和人质危机、重伤住院、地区武装冲突、温泉裸露与身体笑料、控制型亲子关系。</x:v>
       </x:c>
       <x:c r="O164" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P164" s="36" t="n">
         <x:v>1322</x:v>
@@ -11103,7 +11103,7 @@
         <x:v>高中女生的泳装、身高和身体笑料；跨文化和金发刻板笑点；占有式反应、追逐和夸张肢体喜剧；朋友暂时分别带来的寂寞。</x:v>
       </x:c>
       <x:c r="O165" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P165" s="36" t="n">
         <x:v>1326</x:v>
@@ -11168,7 +11168,7 @@
         <x:v>学校合并与活动取消压力、童年同伴利用与孤立的回忆、火灾、可疑成年男性进入女子校活动、喜剧性碰撞与受伤。</x:v>
       </x:c>
       <x:c r="O166" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P166" s="36" t="n">
         <x:v>1336</x:v>
@@ -11233,7 +11233,7 @@
         <x:v>成人性内容、三人结构、姐妹称呼与主仆权力差；字幕含拒绝、请求回家与被带走的台词，完整画面与语境未核实。</x:v>
       </x:c>
       <x:c r="O167" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P167" s="36" t="n">
         <x:v>1340</x:v>
@@ -11245,7 +11245,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S167" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T167" s="33" t="n">
         <x:v>64</x:v>
@@ -11298,7 +11298,7 @@
         <x:v>逃课、社会孤立、嫉妒与独占愿望；未经事先确认的突然拉手与拥抱，随后出现明确制止或许可对话。</x:v>
       </x:c>
       <x:c r="O168" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P168" s="36" t="n">
         <x:v>1341</x:v>
@@ -11363,7 +11363,7 @@
         <x:v>列车性骚扰、与年长女性亲属的过往恋爱及年龄／家庭关系差、家人盘问同性关系与性行为、对女高中生身体的评论、学生对成年教师的单恋、婚约安排、失恋与分手。</x:v>
       </x:c>
       <x:c r="O169" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P169" s="36" t="n">
         <x:v>1355</x:v>
@@ -11428,7 +11428,7 @@
         <x:v>超自然战斗、爆炸与重伤、死亡和创伤、精神操控与身体夺取、战争与大规模伤亡威胁。</x:v>
       </x:c>
       <x:c r="O170" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P170" s="36" t="n">
         <x:v>1356</x:v>
@@ -11493,7 +11493,7 @@
         <x:v>姐妹长期隔离、失去父母、严寒与魔法失控、角色短暂濒危、求婚表象与背叛。</x:v>
       </x:c>
       <x:c r="O171" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P171" s="36" t="n">
         <x:v>1369</x:v>
@@ -11505,13 +11505,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S171" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T171" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U171" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="57" customHeight="1">
@@ -11558,7 +11558,7 @@
         <x:v>幻想战斗与受伤、未成年人遇险、反派操控绝望情绪、亲人离世回忆、世界毁灭威胁、离别悲伤、未确认的青春期异性初恋。</x:v>
       </x:c>
       <x:c r="O172" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P172" s="36" t="n">
         <x:v>1371</x:v>
@@ -11623,7 +11623,7 @@
         <x:v>自杀意念与不幸经历、身体异变、欺骗与情绪操纵、女性对女性的吸引表达。</x:v>
       </x:c>
       <x:c r="O173" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P173" s="36" t="n">
         <x:v>1373</x:v>
@@ -11688,7 +11688,7 @@
         <x:v>女大学生对小学五年级儿童的一见钟情式迷恋；甜点换穿服装及拍照；拒绝或限制后继续请求、连拍与偷拍；成人同龄人的长期观察与尾随。</x:v>
       </x:c>
       <x:c r="O174" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P174" s="36" t="n">
         <x:v>1385</x:v>
@@ -11753,7 +11753,7 @@
         <x:v>父亲去世与遗物相机带来的回忆和悲伤、迁居、重新交友与创作焦虑；具体身体或亲密场面因缺少完整字幕和视听材料无法穷尽。</x:v>
       </x:c>
       <x:c r="O175" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P175" s="36" t="n">
         <x:v>1391</x:v>
@@ -11818,7 +11818,7 @@
         <x:v>军事组织、未成年战斗与重伤、人工生命、囚禁、身体改造和创伤。</x:v>
       </x:c>
       <x:c r="O176" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P176" s="36" t="n">
         <x:v>1394</x:v>
@@ -11883,7 +11883,7 @@
         <x:v>网络炎上与围攻、直播中的肢体冲突、反复追求吸血及身体边界协商、痛感描写、强制转化为吸血鬼的回忆、死亡与长期哀悼、酒精与赌博、欺骗式大型恶作剧。</x:v>
       </x:c>
       <x:c r="O177" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P177" s="36" t="n">
         <x:v>1395</x:v>
@@ -11948,7 +11948,7 @@
         <x:v>魔法战斗、重伤、亲友背叛、复仇、家庭病痛、身份控制与暴力画面</x:v>
       </x:c>
       <x:c r="O178" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P178" s="36" t="n">
         <x:v>1398</x:v>
@@ -12013,7 +12013,7 @@
         <x:v>多名女性围绕同一主角的告白与嫉妒、同时交往及“二股”讨论、对同性恋爱是否普通的自我怀疑、cosplay、旅馆与浴室情节、身体暴露、自责与自我贬低</x:v>
       </x:c>
       <x:c r="O179" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P179" s="36" t="n">
         <x:v>1408</x:v>
@@ -12025,7 +12025,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S179" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>有</x:v>
       </x:c>
       <x:c r="T179" s="33" t="n">
         <x:v>97</x:v>
@@ -12078,7 +12078,7 @@
         <x:v>拘禁与喜剧化拷问、制度权力不对等、阵营冲突、魔法失控和轻度身体危险。</x:v>
       </x:c>
       <x:c r="O180" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P180" s="36" t="n">
         <x:v>1418</x:v>
@@ -12143,7 +12143,7 @@
         <x:v>胸围、体型、泳装、内衣与入浴笑料，以及对金发和国籍差异的夸张调侃。</x:v>
       </x:c>
       <x:c r="O181" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P181" s="36" t="n">
         <x:v>1442</x:v>
@@ -12208,7 +12208,7 @@
         <x:v>毕业与团体结束压力、异国行程、离别与未来选择。</x:v>
       </x:c>
       <x:c r="O182" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P182" s="36" t="n">
         <x:v>1443</x:v>
@@ -12273,7 +12273,7 @@
         <x:v>战斗、牺牲与死亡风险、身体衰弱、自伤表述、强烈情绪依存</x:v>
       </x:c>
       <x:c r="O183" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P183" s="36" t="n">
         <x:v>1447</x:v>
@@ -12285,7 +12285,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S183" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T183" s="33" t="n">
         <x:v>50</x:v>
@@ -12338,7 +12338,7 @@
         <x:v>公开演出焦虑、对亡母的追忆、日常喜剧、自动转写准确度限制</x:v>
       </x:c>
       <x:c r="O184" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P184" s="36" t="n">
         <x:v>1465</x:v>
@@ -12403,7 +12403,7 @@
         <x:v>奇幻战斗与校园灾害演习、对身体变化和换装的喜剧性言谈、嫉妒、短暂争执与分离焦虑、以爱情魔药制造的喜剧桥段；现有材料没有确认接吻、交往或性描写。</x:v>
       </x:c>
       <x:c r="O185" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P185" s="36" t="n">
         <x:v>1469</x:v>
@@ -12468,7 +12468,7 @@
         <x:v>竞赛压力与失败、成员时间冲突、能力差异与临场失误、学校与舞台压力。</x:v>
       </x:c>
       <x:c r="O186" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P186" s="36" t="n">
         <x:v>1471</x:v>
@@ -12533,7 +12533,7 @@
         <x:v>间谍行动、枪战、爆炸、克隆与身份置换；男女恋爱、操纵、背叛、牺牲与死亡。</x:v>
       </x:c>
       <x:c r="O187" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P187" s="36" t="n">
         <x:v>1474</x:v>
@@ -12598,7 +12598,7 @@
         <x:v>武打与武器、流血和重伤、绑架与囚禁、下药和中毒、死亡威胁、人体与内力操控、饮酒。</x:v>
       </x:c>
       <x:c r="O188" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P188" s="36" t="n">
         <x:v>1475</x:v>
@@ -12663,7 +12663,7 @@
         <x:v>强迫政治婚约、父权式家族与企业控制、绑架伪装和追捕、公司贪腐与武器走私、宇宙战斗和未成年角色受险。</x:v>
       </x:c>
       <x:c r="O189" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P189" s="36" t="n">
         <x:v>1500</x:v>
@@ -12728,7 +12728,7 @@
         <x:v>未成年人受险与死亡、推落站台、连环杀人与肢解、身体恐怖、活体切割与医学实验、亲子虐待与宗教操控、近亲性关系、成年人对未成年人的欲望、战时人体实验、自杀言行。</x:v>
       </x:c>
       <x:c r="O190" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P190" s="36" t="n">
         <x:v>1510</x:v>
@@ -12793,7 +12793,7 @@
         <x:v>毕业与团体解散、失去共同体的焦虑、校园偶像竞争和表演压力、性别气质取笑、泳装／洗浴／更衣相关场景。</x:v>
       </x:c>
       <x:c r="O191" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P191" s="36" t="n">
         <x:v>1513</x:v>
@@ -12858,7 +12858,7 @@
         <x:v>双胞胎姐妹接吻与近亲指向、依存和身份融合、女女关系中的施压与边界侵犯、裸体绘画模特、偷窥式隐藏摄像、梦境中的持刀及自杀表述、亲人死亡与哀伤、爆炸及事故。</x:v>
       </x:c>
       <x:c r="O192" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P192" s="36" t="n">
         <x:v>1528</x:v>
@@ -12923,7 +12923,7 @@
         <x:v>儿童死亡与葬礼、遗属哀伤、激烈战斗、身体机能及记忆丧失、制度性利用与强制存活。</x:v>
       </x:c>
       <x:c r="O193" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P193" s="36" t="n">
         <x:v>1550</x:v>
@@ -12988,7 +12988,7 @@
         <x:v>睡眠中非自愿亲吻、占有与控制、针对第三者的暴力、同性欲望污名化、精神操控、朋友间强制战斗、暂时死亡、哀伤、裸露与性化画面。</x:v>
       </x:c>
       <x:c r="O194" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P194" s="36" t="n">
         <x:v>1569</x:v>
@@ -13053,7 +13053,7 @@
         <x:v>肢解与出血黑色喜剧、强制同居、谋杀企图、赌博与借贷、跟踪和权力滥用、饥饿及性化笑料</x:v>
       </x:c>
       <x:c r="O195" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P195" s="36" t="n">
         <x:v>1602</x:v>
@@ -13118,7 +13118,7 @@
         <x:v>片场／NG 恶搞、摔打与失态笑料、贬损性称呼、酒精与醉酒笑话、裙装／内衣／换装笑料，以及局部男友与婚姻假设。</x:v>
       </x:c>
       <x:c r="O196" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P196" s="36" t="n">
         <x:v>1618</x:v>
@@ -13183,7 +13183,7 @@
         <x:v>成年工作压力、项目中止、地方设施改造、露营施工与户外安全风险。</x:v>
       </x:c>
       <x:c r="O197" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P197" s="36" t="n">
         <x:v>1630</x:v>
@@ -13248,7 +13248,7 @@
         <x:v>工具误操作与反复轻伤的喜剧化表现、丧亲回忆、短暂离别</x:v>
       </x:c>
       <x:c r="O198" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P198" s="36" t="n">
         <x:v>1637</x:v>
@@ -13313,7 +13313,7 @@
         <x:v>刀剑与拳法暴力、绑架和人口贩运、药物依赖与死亡、宗教诈骗、诬告与处刑威胁，以及喜剧性裸露和偷窥</x:v>
       </x:c>
       <x:c r="O199" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P199" s="36" t="n">
         <x:v>1652</x:v>
@@ -13378,7 +13378,7 @@
         <x:v>死亡、枪击与食人意象，校园欺凌和集体排除，性化裸露与暗示，成年人对未成年学生的捕食性接近及强迫接吻未遂，嫉妒、背叛、丧亲、童年伤害、记忆抹除与身体变形。</x:v>
       </x:c>
       <x:c r="O200" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P200" s="36" t="n">
         <x:v>1659</x:v>
@@ -13443,7 +13443,7 @@
         <x:v>战争、空战、负伤和牺牲风险；部队解散与重组压力；频繁裸体、内衣式服装和身体凝视笑料；前后辈崇拜、守护和分离情绪。</x:v>
       </x:c>
       <x:c r="O201" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P201" s="36" t="n">
         <x:v>1692</x:v>
@@ -13508,7 +13508,7 @@
         <x:v>战争、死亡与儿童受伤威胁、姐妹创伤、监禁与政治暴力、酒精滥用、地下格斗、自我毁灭／自杀意念、背叛，以及 Vi／Caitlyn 的冲突与高强度情感对话。</x:v>
       </x:c>
       <x:c r="O202" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P202" s="36" t="n">
         <x:v>1694</x:v>
@@ -13520,13 +13520,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S202" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T202" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U202" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="57" customHeight="1">
@@ -13573,7 +13573,7 @@
         <x:v>麻将竞技压力、晕厥与住院、丧母回忆、对高中女生身体的性化玩笑。</x:v>
       </x:c>
       <x:c r="O203" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P203" s="36" t="n">
         <x:v>1728</x:v>
@@ -13638,7 +13638,7 @@
         <x:v>战争与空战、青少年参战、负伤与死亡威胁、频繁裸体及内衣式服装、身体凝视与浴室笑料、带性意味的接触、牺牲式守护。</x:v>
       </x:c>
       <x:c r="O204" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P204" s="36" t="n">
         <x:v>1747</x:v>
@@ -13703,7 +13703,7 @@
         <x:v>频繁杀人、肢解与尸体处理，血腥重伤、绑架监禁、非自愿人体实验、年龄倒退与身份扰乱、家庭创伤、身体笑料、赌博成瘾和经济剥削。</x:v>
       </x:c>
       <x:c r="O205" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P205" s="36" t="n">
         <x:v>1751</x:v>
@@ -13768,7 +13768,7 @@
         <x:v>人偶未完成状态、创造者承认焦虑、身体衰弱与行走练习、战斗、关系破裂及伤害性言语。</x:v>
       </x:c>
       <x:c r="O206" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P206" s="36" t="n">
         <x:v>1764</x:v>
@@ -13833,7 +13833,7 @@
         <x:v>喜剧化肘击、敲打、假死与死亡玩笑；心肺复苏假设；拍摄未成年女高中生裸腿的笑话</x:v>
       </x:c>
       <x:c r="O207" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P207" s="36" t="n">
         <x:v>1766</x:v>
@@ -13898,7 +13898,7 @@
         <x:v>项目解体威胁、竞争性选拔、工作压力、失去自信、情绪低落、组合分流、舞台责任与未成年人过劳风险。</x:v>
       </x:c>
       <x:c r="O208" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P208" s="36" t="n">
         <x:v>1779</x:v>
@@ -13963,7 +13963,7 @@
         <x:v>反复求婚与共同生活要求被喜剧化处理、魔法导致的非自愿情感暴露、姐妹间欲望、身体互换、家庭虐待暗示、奴役、怀孕与亲人或恋人被杀、较强暴力和血腥场面、身体边界侵犯。</x:v>
       </x:c>
       <x:c r="O209" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P209" s="36" t="n">
         <x:v>1790</x:v>
@@ -14028,7 +14028,7 @@
         <x:v>地下赌博与犯罪组织胁迫、枪击与致命暴力、贫困和强制拆迁、带性意味的威吓与身体边界侵犯、未成年角色处于高风险环境、少量裸露与性化玩笑</x:v>
       </x:c>
       <x:c r="O210" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P210" s="36" t="n">
         <x:v>1806</x:v>
@@ -14093,7 +14093,7 @@
         <x:v>未经同意的触摸与女浴区侵入、偷窥／性骚扰笑料、胸部和身体羞辱、性化服装、暴力与强制夺取能力、校园排斥与背叛回忆、家庭缺席、身体及人格变化危机。</x:v>
       </x:c>
       <x:c r="O211" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P211" s="36" t="n">
         <x:v>1817</x:v>
@@ -14158,7 +14158,7 @@
         <x:v>过度训练后病倒、朋友隐瞒离别计划与关系破裂、未经同意的胸部触碰笑料、泳装与洗浴场景、外貌及体型笑料。</x:v>
       </x:c>
       <x:c r="O212" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P212" s="36" t="n">
         <x:v>1818</x:v>
@@ -14223,7 +14223,7 @@
         <x:v>校园纪律压力、秘密与谎言引发的信任破裂、学生恋爱被调查、恋爱练习中的性别角色笑料。</x:v>
       </x:c>
       <x:c r="O213" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P213" s="36" t="n">
         <x:v>1826</x:v>
@@ -14288,7 +14288,7 @@
         <x:v>科幻战斗与死亡、阶级压迫与制度暴力、记忆操控、身体更替与复制人、自杀意念、药物及医疗危机、儿童受威胁、少量性化画面及骚扰式玩笑</x:v>
       </x:c>
       <x:c r="O214" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P214" s="36" t="n">
         <x:v>1845</x:v>
@@ -14353,7 +14353,7 @@
         <x:v>跟踪、反复拍摄及制作等身人像，利用他人制造嫉妒；另有冒充家属、把参赛者骗离赛场并反锁、校园斗殴、欺凌、比赛受伤及师长失职。</x:v>
       </x:c>
       <x:c r="O215" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P215" s="36" t="n">
         <x:v>1852</x:v>
@@ -14418,7 +14418,7 @@
         <x:v>大额购买唱片和付费接触、带病或受伤工作与观演、夸张伤病喜剧、偶像恋爱禁忌、绯闻压力和粉丝占有欲。</x:v>
       </x:c>
       <x:c r="O216" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P216" s="36" t="n">
         <x:v>1854</x:v>
@@ -14483,7 +14483,7 @@
         <x:v>短篇节奏、旅行与道路活动、轻度地方传说惊吓</x:v>
       </x:c>
       <x:c r="O217" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P217" s="36" t="n">
         <x:v>1865</x:v>
@@ -14548,7 +14548,7 @@
         <x:v>校园排斥与身体羞辱、家庭压力和丧亲、记忆消除与身份动摇、顾客遭遇的单恋和关系欺瞒、愿望被替人决定、社交媒体比较、经济／学业压力、青少年被成年人操纵参与魔法劳动。</x:v>
       </x:c>
       <x:c r="O218" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P218" s="36" t="n">
         <x:v>1867</x:v>
@@ -14613,7 +14613,7 @@
         <x:v>以女性向欲望和鼻血作反复笑料、对女学生身体的性化凝视、胁迫与秘密威胁、被迫同住和监视、羞辱性称呼与校园排斥、性别表达被用于欺骗和揭露笑料、宗教学校意象戏仿。</x:v>
       </x:c>
       <x:c r="O219" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P219" s="36" t="n">
         <x:v>1872</x:v>
@@ -14678,7 +14678,7 @@
         <x:v>幻想战斗与未成年人遇险、敌方胁迫、离别与哀伤、校园冲突。</x:v>
       </x:c>
       <x:c r="O220" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P220" s="36" t="n">
         <x:v>1902</x:v>
@@ -14743,7 +14743,7 @@
         <x:v>奇幻战斗与未成年人遇险、附身和强制送往异界的威胁、青少年角色的泳装／身体笑料、姐妹死亡与家庭创伤、人类—妖怪歧视和牺牲政策、饮酒笑料。</x:v>
       </x:c>
       <x:c r="O221" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P221" s="36" t="n">
         <x:v>1928</x:v>
@@ -14808,7 +14808,7 @@
         <x:v>奇幻战斗与怪物威胁、时间回溯与记忆影响、朋友实施的绑架骗局、涉及年轻外形角色的泳装及性化画面、学校与师生权力结构</x:v>
       </x:c>
       <x:c r="O222" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P222" s="36" t="n">
         <x:v>1930</x:v>
@@ -14873,7 +14873,7 @@
         <x:v>哮喘与慢性病、童年忽视与女仆欺凌、寄养与家庭遗弃焦虑、发烧与筒仓恐惧、父母死亡与哀伤、跨代家庭创伤和记忆混淆。</x:v>
       </x:c>
       <x:c r="O223" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P223" s="36" t="n">
         <x:v>1933</x:v>
@@ -14938,7 +14938,7 @@
         <x:v>夸张战斗、温泉与身体笑料、能力丧失、团队挫败、催眠操控、侦探／怪盗／警察多方冲突。</x:v>
       </x:c>
       <x:c r="O224" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P224" s="36" t="n">
         <x:v>1944</x:v>
@@ -15003,7 +15003,7 @@
         <x:v>单恋、拒绝与失去友谊焦虑、同性倾向带来的孤立与污名压力、以喜剧处理的暴露隐私和胁迫、女装及性别表达喜剧、涉及青少年角色的泳装／服务性画面、空手道暴力与肢体喜剧</x:v>
       </x:c>
       <x:c r="O225" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P225" s="36" t="n">
         <x:v>1957</x:v>
@@ -15068,7 +15068,7 @@
         <x:v>贯穿全季的饮酒与醉态、吸烟、夜间酒吧及俱乐部、醉后判断能力降低、穿耳洞与亲密行动中的边界确认、关系不确定与嫉妒。</x:v>
       </x:c>
       <x:c r="O226" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P226" s="36" t="n">
         <x:v>1968</x:v>
@@ -15133,7 +15133,7 @@
         <x:v>追捕与拘禁、人体与能源实验、身体分解及身份置换、战争与恐怖活动、死亡和哀伤、儿童受伤、强制结对。</x:v>
       </x:c>
       <x:c r="O227" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P227" s="36" t="n">
         <x:v>1981</x:v>
@@ -15198,7 +15198,7 @@
         <x:v>空战、枪炮、坠机与伤亡风险，政治强迫与宣传，饮酒，异性调情、求婚及失败婚姻笑料</x:v>
       </x:c>
       <x:c r="O228" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P228" s="36" t="n">
         <x:v>2022</x:v>
@@ -15263,7 +15263,7 @@
         <x:v>轻度枪械与秘密组织设定、幽灵恶作剧、留宿与换制服桥段。</x:v>
       </x:c>
       <x:c r="O229" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P229" s="36" t="n">
         <x:v>2038</x:v>
@@ -15328,7 +15328,7 @@
         <x:v>奇幻战斗、儿童与青少年遇险、时间停止、记忆丧失、亲子分离、胁迫与世界危机。</x:v>
       </x:c>
       <x:c r="O230" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P230" s="36" t="n">
         <x:v>2044</x:v>
@@ -15393,7 +15393,7 @@
         <x:v>未成年角色之间围绕亲吻／唾液补给的台词与尴尬玩笑、角色犹豫的补给台词、男性恋爱药剂、魔法战斗与生命危险</x:v>
       </x:c>
       <x:c r="O231" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P231" s="36" t="n">
         <x:v>2045</x:v>
@@ -15458,7 +15458,7 @@
         <x:v>亲生双胞胎姐妹的恋爱方向、血亲题材、自动字幕证据限制</x:v>
       </x:c>
       <x:c r="O232" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P232" s="36" t="n">
         <x:v>2054</x:v>
@@ -15523,7 +15523,7 @@
         <x:v>初次交往中的不安、嫉妒与沟通困难，毕业／升学带来的未来压力。</x:v>
       </x:c>
       <x:c r="O233" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P233" s="36" t="n">
         <x:v>2061</x:v>
@@ -15588,7 +15588,7 @@
         <x:v>未成年角色的性化喜剧、亲吻式魔力补给与身体边界问题、义兄恋爱笑点、魔法战斗与生命危险</x:v>
       </x:c>
       <x:c r="O234" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P234" s="36" t="n">
         <x:v>2064</x:v>
@@ -15653,7 +15653,7 @@
         <x:v>儿童死亡与长期哀伤、怪物暴力和身体恐怖、儿童陷入战斗、人工生命体死亡与被迫分离、复制／操纵／消除记忆、姐妹身份与恋爱方向叠加、强烈依赖及分离焦虑、丧亲。</x:v>
       </x:c>
       <x:c r="O235" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P235" s="36" t="n">
         <x:v>2107</x:v>
@@ -15718,7 +15718,7 @@
         <x:v>未成年少女战斗、受伤、角色死亡、同伴哀伤与未完成约定</x:v>
       </x:c>
       <x:c r="O236" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P236" s="36" t="n">
         <x:v>2108</x:v>
@@ -15783,7 +15783,7 @@
         <x:v>承接 TV 第三季、海外旅行、舞台压力、临场受伤与完整剧透</x:v>
       </x:c>
       <x:c r="O237" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P237" s="36" t="n">
         <x:v>2112</x:v>
@@ -15848,7 +15848,7 @@
         <x:v>网络恶评与传言扩散、危险驾驶及下坡滑板、暴食与肠胃不适笑料、幽灵及伪纪录恐怖、短暂绝望时的随口轻生表达、动物遇险。</x:v>
       </x:c>
       <x:c r="O238" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P238" s="36" t="n">
         <x:v>2117</x:v>
@@ -15913,7 +15913,7 @@
         <x:v>童年坠落骨折与恐高、初学登山风险、坏鞋下山。</x:v>
       </x:c>
       <x:c r="O239" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P239" s="36" t="n">
         <x:v>2118</x:v>
@@ -15978,7 +15978,7 @@
         <x:v>暗杀、枪击、刺伤与死亡，犯罪组织和政治暴力，儿童杀手训练、失忆与身份操纵，邪教式控制与强迫仪式，家人被杀与复仇，要求对方杀死自己，强迫性的“死亡之吻”威胁和身体控制，火灾、溺水及心理崩溃。</x:v>
       </x:c>
       <x:c r="O240" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P240" s="36" t="n">
         <x:v>2160</x:v>
@@ -16043,7 +16043,7 @@
         <x:v>未成年人在信息不完整的情况下被投入战斗、身体机能损失、失忆、残障、制度操控、自毁式牺牲、自杀念头、毁灭世界的行动与末世威胁。</x:v>
       </x:c>
       <x:c r="O241" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P241" s="36" t="n">
         <x:v>2176</x:v>
@@ -16108,7 +16108,7 @@
         <x:v>频繁喜剧化击打、关节技、刀枪与暗杀笑话；意外身体接触；公共浴室与身体笑点；情人节恋爱惯例及误认</x:v>
       </x:c>
       <x:c r="O242" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P242" s="36" t="n">
         <x:v>2183</x:v>
@@ -16173,7 +16173,7 @@
         <x:v>女性间性化骚扰、索取内衣、窥视／拍摄企图、身体笑料、未经同意入室、捆绑与打闹。</x:v>
       </x:c>
       <x:c r="O243" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P243" s="36" t="n">
         <x:v>2186</x:v>
@@ -16238,7 +16238,7 @@
         <x:v>怪兽暴力与城市破坏、死亡及记忆被抹除、刺伤与流血、失忆和身份置换、情感操纵、梦境诱导、自我否定。</x:v>
       </x:c>
       <x:c r="O244" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P244" s="36" t="n">
         <x:v>2192</x:v>
@@ -16303,7 +16303,7 @@
         <x:v>突然发起的亲吻与边界误会、对未成年角色的性化身体笑料、亲戚关系、家族安排的男性婚约。</x:v>
       </x:c>
       <x:c r="O245" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P245" s="36" t="n">
         <x:v>2196</x:v>
@@ -16368,7 +16368,7 @@
         <x:v>贫困与食物不安全、居住和劳动不对等、异族／阶层歧视用语、族裔刻板描写、性骚扰笑料、丧亲与家园可能消失。</x:v>
       </x:c>
       <x:c r="O246" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P246" s="36" t="n">
         <x:v>2205</x:v>
@@ -16433,7 +16433,7 @@
         <x:v>成人向性化台词语境、暴力、强制同化；未作逐镜视觉判断</x:v>
       </x:c>
       <x:c r="O247" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P247" s="36" t="n">
         <x:v>2231</x:v>
@@ -16498,7 +16498,7 @@
         <x:v>主从等级、洗脑与人格剥夺、强制融合、共同跳楼与处分威胁、馆邸监视、单向恋爱与权力不平等。</x:v>
       </x:c>
       <x:c r="O248" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P248" s="36" t="n">
         <x:v>2237</x:v>
@@ -16563,7 +16563,7 @@
         <x:v>女性向欲望、鼻血与身体凝视被反复用于喜剧；女学生身体、气味与梦境场景被性化；鞠也和茉莉花的捉弄与辛辣言辞；梦境和夸张想象不能单独当作现实交往证据。</x:v>
       </x:c>
       <x:c r="O249" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P249" s="36" t="n">
         <x:v>2242</x:v>
@@ -16628,7 +16628,7 @@
         <x:v>捕捉、处理和食用鱼类及海洋生物，活饵与昆虫，利用主人公恐惧促成入部，成人教师饮酒后向学生说结婚与亲吻笑话并遭拒绝，泳装与身体笑料，水上安全风险。</x:v>
       </x:c>
       <x:c r="O250" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P250" s="36" t="n">
         <x:v>2284</x:v>
@@ -16693,7 +16693,7 @@
         <x:v>校园文化祭准备、过度努力的喜剧化描写、女生之间的争宠与暧昧笑料、跨文化误解、身体与更衣话题笑料</x:v>
       </x:c>
       <x:c r="O251" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P251" s="36" t="n">
         <x:v>2292</x:v>
@@ -16758,7 +16758,7 @@
         <x:v>未成年人物的身体／内衣／泳装／沐浴与胸部笑料、剧中 TL 与成人性内容讨论、尾随和惊吓式边界侵犯、成人醉酒、体重与节食笑料、强烈自我否定和退稿压力、恐怖与血迹意象</x:v>
       </x:c>
       <x:c r="O252" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P252" s="36" t="n">
         <x:v>2305</x:v>
@@ -16823,7 +16823,7 @@
         <x:v>群像切换频繁、场地受损后的紧急修复与演出压力。</x:v>
       </x:c>
       <x:c r="O253" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P253" s="36" t="n">
         <x:v>2312</x:v>
@@ -16888,7 +16888,7 @@
         <x:v>暗杀误会、伪造自杀与诅咒故事、跟踪与偷窥误会、喜剧性暴力和武器、VR 战斗、身体笑料、诈骗与网络攻击。</x:v>
       </x:c>
       <x:c r="O254" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P254" s="36" t="n">
         <x:v>2319</x:v>
@@ -16953,7 +16953,7 @@
         <x:v>星球灾害、父亲病危、姐妹冲突、欺骗与利用、控制、复仇、儿童战斗、前篇悬念。</x:v>
       </x:c>
       <x:c r="O255" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P255" s="36" t="n">
         <x:v>2330</x:v>
@@ -17018,7 +17018,7 @@
         <x:v>碎片化概念叙事、抽象神性意象、魔法少女战斗与不安氛围。</x:v>
       </x:c>
       <x:c r="O256" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P256" s="36" t="n">
         <x:v>2377</x:v>
@@ -17083,7 +17083,7 @@
         <x:v>饥饿与居住惩罚、打闹暴力、非自愿身体接触、脱衣和胸部笑料、男性性骚扰、暴露、活埋及溺水险境。</x:v>
       </x:c>
       <x:c r="O257" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P257" s="36" t="n">
         <x:v>2392</x:v>
@@ -17148,7 +17148,7 @@
         <x:v>战争与空战、未成年角色参战、负伤与推定死亡、丧亲和战时分离、频繁裸体与内衣式服装、身体凝视、侵入性触摸和浴室服务性内容。</x:v>
       </x:c>
       <x:c r="O258" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P258" s="36" t="n">
         <x:v>2393</x:v>
@@ -17213,7 +17213,7 @@
         <x:v>小学六年级少女承担战斗职责、受伤与组织压力；含温泉和身体发育笑料。</x:v>
       </x:c>
       <x:c r="O259" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P259" s="36" t="n">
         <x:v>2397</x:v>
@@ -17278,7 +17278,7 @@
         <x:v>超能力战斗、枪击、爆炸、记忆与身份被操纵；校园离别、创伤及异性恋人背景。</x:v>
       </x:c>
       <x:c r="O260" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P260" s="36" t="n">
         <x:v>2419</x:v>
@@ -17343,7 +17343,7 @@
         <x:v>离别焦虑、排斥朋友的尝试、情绪痛苦、归属冲突、暂时消失与重逢</x:v>
       </x:c>
       <x:c r="O261" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P261" s="36" t="n">
         <x:v>2428</x:v>
@@ -17408,7 +17408,7 @@
         <x:v>枪击与死亡、人体实验和精神操纵、跟踪与占有式控制、非自愿亲吻、绑架与拘束、研究者／受试者权力差、要求亲近者开枪及短暂死亡、丧亲与针对性别不合规范人物的贬称。</x:v>
       </x:c>
       <x:c r="O262" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P262" s="36" t="n">
         <x:v>2431</x:v>
@@ -17473,7 +17473,7 @@
         <x:v>露骨性双关、色情书与性工作笑料、未成年少女性化、冒充亲属、边界侵犯、非自愿干预与长期昏睡。</x:v>
       </x:c>
       <x:c r="O263" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P263" s="36" t="n">
         <x:v>2433</x:v>
@@ -17538,7 +17538,7 @@
         <x:v>枪战、威权控制、自杀笑话、身体笑料与带强迫意味的亲密幻想</x:v>
       </x:c>
       <x:c r="O264" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P264" s="36" t="n">
         <x:v>2440</x:v>
@@ -17603,7 +17603,7 @@
         <x:v>反复谋杀、肢解、酷刑与出血笑料；强制召唤与同居；跟踪、绑走、占有式骚扰和警权滥用；经济剥削与赌博；无家可归、饥饿；裸露、泳装及性化笑料。</x:v>
       </x:c>
       <x:c r="O265" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P265" s="36" t="n">
         <x:v>2442</x:v>
@@ -17668,7 +17668,7 @@
         <x:v>病中照料、喂食、擦拭身体玩笑、同学调侃与轻微身体笑料。</x:v>
       </x:c>
       <x:c r="O266" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P266" s="36" t="n">
         <x:v>2459</x:v>
@@ -17733,7 +17733,7 @@
         <x:v>初中年龄角色被持续性化；非自愿束缚、剥衣、猥亵及乳房／生殖器刺激；封闭房间中的胁迫亲吻和性行为；施虐、受虐、羞辱与高潮反应；触手、怪物袭击和公开暴露；勒索变身、身份威胁、精神控制、幼儿化角色扮演、战斗伤害和城市破坏。</x:v>
       </x:c>
       <x:c r="O267" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P267" s="36" t="n">
         <x:v>2470</x:v>
@@ -17798,7 +17798,7 @@
         <x:v>强迫赌博、债务与制度性奴役、羞辱与霸凌、枪械与求死欲望、性化支配和受虐、拔指甲与流血、强制婚育和职业安排。</x:v>
       </x:c>
       <x:c r="O268" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P268" s="36" t="n">
         <x:v>2471</x:v>
@@ -17863,7 +17863,7 @@
         <x:v>性别未确认的非人搭档另有单向潜在恋爱读法；自杀与自杀未遂、未成年人死亡、家庭暴力、儿童性剥削与被迫拍摄、谋杀与枪击、校园霸凌、解离身份与污名、昏迷、媒体骚扰、动物死亡、忽视与遗弃。</x:v>
       </x:c>
       <x:c r="O269" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P269" s="36" t="n">
         <x:v>2494</x:v>
@@ -17928,7 +17928,7 @@
         <x:v>未成年人遭成人性化凝视与纠缠；男性角色的跟踪、偷窥和婚姻妄想；贫困与食物短缺；校园孤立与利用；魔物袭击、战斗、受伤及爆炸；邪教笑料、宗教操控和低俗性笑话。</x:v>
       </x:c>
       <x:c r="O270" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P270" s="36" t="n">
         <x:v>2500</x:v>
@@ -17993,7 +17993,7 @@
         <x:v>夸张肢体暴力、威胁、强行剥衣与身体边界侵犯、内衣和局部裸露笑料、同性身体骚扰、未定对象暗恋／失恋、男朋友与异性求偶笑话、身材与青春期羞辱、粗俗语言及生殖器笑话。</x:v>
       </x:c>
       <x:c r="O271" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P271" s="36" t="n">
         <x:v>2545</x:v>
@@ -18058,7 +18058,7 @@
         <x:v>含共同生活、配偶与生育笑料、儿童角色的单向对象明确欲望及竞争性喜剧；未做画面复核。</x:v>
       </x:c>
       <x:c r="O272" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P272" s="36" t="n">
         <x:v>2586</x:v>
@@ -18123,7 +18123,7 @@
         <x:v>师生年龄与职权差、教师查看学生衣物的越界笑料、未成年角色的泳装与身体笑料、社交焦虑、升学中断、饮酒照护。</x:v>
       </x:c>
       <x:c r="O273" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P273" s="36" t="n">
         <x:v>2591</x:v>
@@ -18188,7 +18188,7 @@
         <x:v>未经邀请搬入、反复试探边界、拒绝后吸血、秘密搬运导致阳光与海水风险、洗浴与身体笑料、针对年轻女性的性化评论、装病延长照料、占有欲与嫉妒。</x:v>
       </x:c>
       <x:c r="O274" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P274" s="36" t="n">
         <x:v>2593</x:v>
@@ -18253,7 +18253,7 @@
         <x:v>战斗、角色死亡、肢体重伤、失去手臂、Faunus 歧视、心理操纵、前盟友占有与暴力、异性求偶语境。</x:v>
       </x:c>
       <x:c r="O275" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P275" s="36" t="n">
         <x:v>2596</x:v>
@@ -18265,13 +18265,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S275" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T275" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U275" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="57" customHeight="1">
@@ -18318,7 +18318,7 @@
         <x:v>枪械、拘留与营救、审讯、政治暴力、身份隐瞒、尸体发现与未完调查。</x:v>
       </x:c>
       <x:c r="O276" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P276" s="36" t="n">
         <x:v>2597</x:v>
@@ -18383,7 +18383,7 @@
         <x:v>童年好友病逝与哀伤、拒学和负罪感、跟踪拍摄及个人边界侵犯笑料、涉及高中生的体液／排泄／性暗示笑料、诅咒与受伤幻想、单恋与拒绝</x:v>
       </x:c>
       <x:c r="O277" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P277" s="36" t="n">
         <x:v>2632</x:v>
@@ -18448,7 +18448,7 @@
         <x:v>绑架与强迫偶像出道、商业利用、喜剧性追逐与战斗、职业选择冲突</x:v>
       </x:c>
       <x:c r="O278" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P278" s="36" t="n">
         <x:v>2633</x:v>
@@ -18513,7 +18513,7 @@
         <x:v>夸张想念与寻找、暗锅恶作剧、饮食与体重笑料、校园群像日常</x:v>
       </x:c>
       <x:c r="O279" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P279" s="36" t="n">
         <x:v>2637</x:v>
@@ -18578,7 +18578,7 @@
         <x:v>高强度战斗、身体与精神控制、重伤与死亡、姐妹失去、灾难威胁、实验和政治阴谋。</x:v>
       </x:c>
       <x:c r="O280" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P280" s="36" t="n">
         <x:v>2670</x:v>
@@ -18643,7 +18643,7 @@
         <x:v>赛场严重骨折与急救、长期复健和再次受伤恐惧、过量训练、体重与节食笑料、男性训练师未经同意触碰腿部的性骚扰笑料、主人公出生母亲去世。</x:v>
       </x:c>
       <x:c r="O281" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P281" s="36" t="n">
         <x:v>2679</x:v>
@@ -18708,7 +18708,7 @@
         <x:v>犯罪与丑闻、职业赛事压力、身体不适与医疗风险、家族冲突。</x:v>
       </x:c>
       <x:c r="O282" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P282" s="36" t="n">
         <x:v>2690</x:v>
@@ -18773,7 +18773,7 @@
         <x:v>战争与空战、未成年参战、离散与战后重建、频繁裸体和内衣式服装、身体凝视与服务性笑料、照护责任及牺牲风险。</x:v>
       </x:c>
       <x:c r="O283" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P283" s="36" t="n">
         <x:v>2704</x:v>
@@ -18838,7 +18838,7 @@
         <x:v>殴打、飞刀、关节技、暗杀威胁、强行靠近与恶作剧被作为动作喜剧笑点；未作画面复核。</x:v>
       </x:c>
       <x:c r="O284" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P284" s="36" t="n">
         <x:v>2720</x:v>
@@ -18903,7 +18903,7 @@
         <x:v>旧乐队解散、关系操控、强烈依赖、排斥、情绪崩溃与舞台表演</x:v>
       </x:c>
       <x:c r="O285" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P285" s="36" t="n">
         <x:v>2722</x:v>
@@ -18968,7 +18968,7 @@
         <x:v>未成年人遭遇宇宙险境与轻度魔法战斗；住院、昏迷与死亡威胁；自我消失意愿；亲友离别、记忆断裂及丧亲回忆</x:v>
       </x:c>
       <x:c r="O286" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P286" s="36" t="n">
         <x:v>2723</x:v>
@@ -19033,7 +19033,7 @@
         <x:v>连续谋杀与未遂谋杀、欺骗与利用信任、刀伤与死亡、校园欺凌、以恋爱名义实施的恶作剧和胁迫、自伤式伪装、动物虐待、童年创伤与丧亲</x:v>
       </x:c>
       <x:c r="O287" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P287" s="36" t="n">
         <x:v>2790</x:v>
@@ -19098,7 +19098,7 @@
         <x:v>儿童被工具化、收养家庭、家人死亡、魔法战争、绑架、牺牲选择、重伤与世界毁灭。</x:v>
       </x:c>
       <x:c r="O288" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P288" s="36" t="n">
         <x:v>2793</x:v>
@@ -19163,7 +19163,7 @@
         <x:v>亲密玩笑与捉弄，穿衣洗澡、床上场景、胸部和性暗示笑料，以及对“好想死／不想死”的语言玩笑。</x:v>
       </x:c>
       <x:c r="O289" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P289" s="36" t="n">
         <x:v>2808</x:v>
@@ -19228,7 +19228,7 @@
         <x:v>时代性别歧视、未成年婚约与年龄差、侵入式求爱、家长隐瞒和禁足、以断绝关系相威胁、运动伤害、夜间冲突及犯罪威胁。</x:v>
       </x:c>
       <x:c r="O290" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P290" s="36" t="n">
         <x:v>2814</x:v>
@@ -19293,7 +19293,7 @@
         <x:v>潜水风险、分离焦虑、梦境及男女恋爱副线。</x:v>
       </x:c>
       <x:c r="O291" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P291" s="36" t="n">
         <x:v>2817</x:v>
@@ -19358,7 +19358,7 @@
         <x:v>高速荒诞喜剧、夸张肢体与追逐笑料、身体和内衣笑料、非自愿附身。</x:v>
       </x:c>
       <x:c r="O292" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P292" s="36" t="n">
         <x:v>2823</x:v>
@@ -19423,7 +19423,7 @@
         <x:v>高中生角色的身体与内衣笑料，亲吻、触摸胸部等请求，口头拒绝与身体边界被用作喜剧，成年教师与学生之间的胸部笑料。</x:v>
       </x:c>
       <x:c r="O293" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P293" s="36" t="n">
         <x:v>2828</x:v>
@@ -19488,7 +19488,7 @@
         <x:v>海战与实弹攻击、爆炸和沉船危险、病毒导致失控攻击、受伤与溺水威胁、幼年丧亲回忆、灾难撤离、少量洗浴／内衣及体重笑话</x:v>
       </x:c>
       <x:c r="O294" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P294" s="36" t="n">
         <x:v>2837</x:v>
@@ -19553,7 +19553,7 @@
         <x:v>未成年角色的裸体、洗浴、胸部与身体笑料，性器官查验笑话，性别气质刻板判断，异性隔离与强制性恋爱教育，身体惩罚、轻度暴力、疾病、运动伤害、外貌比较与羞辱。</x:v>
       </x:c>
       <x:c r="O295" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P295" s="36" t="n">
         <x:v>2848</x:v>
@@ -19618,7 +19618,7 @@
         <x:v>泳装、沐浴与身体玩笑；偷拍与跟随同伴的喜剧处理；嫉妒、私奔、同住与妻子角色玩笑；搬迁与离别焦虑；病弱、疲劳和灾害回忆</x:v>
       </x:c>
       <x:c r="O296" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P296" s="36" t="n">
         <x:v>2861</x:v>
@@ -19683,7 +19683,7 @@
         <x:v>偶像行业与表演压力、情绪崩溃和暂时退出、压力性发热，以及轻度服装和身体笑料</x:v>
       </x:c>
       <x:c r="O297" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P297" s="36" t="n">
         <x:v>2870</x:v>
@@ -19748,7 +19748,7 @@
         <x:v>僵尸灾难、感染、死亡、血腥与武器、创伤性否认、同伴处置困境、教师与犬只死亡</x:v>
       </x:c>
       <x:c r="O298" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P298" s="36" t="n">
         <x:v>2896</x:v>
@@ -19813,7 +19813,7 @@
         <x:v>澡堂同浴、女性身体服务笑料、黑子对美琴的性感化言语与越界触摸愿望</x:v>
       </x:c>
       <x:c r="O299" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P299" s="36" t="n">
         <x:v>2899</x:v>
@@ -19878,7 +19878,7 @@
         <x:v>小学年龄角色、温泉裸身语境、女女性暗示身体交换、兄妹称谓下的单向性挑逗、成人用品与双关笑料</x:v>
       </x:c>
       <x:c r="O300" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P300" s="36" t="n">
         <x:v>2927</x:v>
@@ -19943,7 +19943,7 @@
         <x:v>石化病毒、怪物袭击、血腥死亡、身体恐怖、双胞胎分离、自我牺牲、身份错位、复制／替代存在与现实边界。</x:v>
       </x:c>
       <x:c r="O301" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P301" s="36" t="n">
         <x:v>2941</x:v>
@@ -20008,7 +20008,7 @@
         <x:v>长途骑行、山路、吊桥、夜间露营与交通安全风险，低温、野外环境、用火与露营装备风险，少量公共浴池或泡澡场景。</x:v>
       </x:c>
       <x:c r="O302" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P302" s="36" t="n">
         <x:v>2949</x:v>
@@ -20073,7 +20073,7 @@
         <x:v>未成年角色性化笑剧、强制人偶化与意识操纵、囚禁、战争及战斗伤害</x:v>
       </x:c>
       <x:c r="O303" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P303" s="36" t="n">
         <x:v>2999</x:v>
@@ -20138,7 +20138,7 @@
         <x:v>少女绑架、战争与政治阴谋、军事代理、主人—奥托梅权力差、轻度裸露与身体暴露。</x:v>
       </x:c>
       <x:c r="O304" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P304" s="36" t="n">
         <x:v>3026</x:v>
@@ -20203,7 +20203,7 @@
         <x:v>宇宙追捕与战斗、未成年角色危险、威胁与强制逃离、家庭离散、服务性演出和身体笑料。</x:v>
       </x:c>
       <x:c r="O305" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P305" s="36" t="n">
         <x:v>3028</x:v>
@@ -20268,7 +20268,7 @@
         <x:v>超高速荒诞、肢体与洗浴笑料、竞争与追逐、男性棒球部和外星人单元。</x:v>
       </x:c>
       <x:c r="O306" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P306" s="36" t="n">
         <x:v>3052</x:v>
@@ -20333,7 +20333,7 @@
         <x:v>性侵与强行接吻、击打和压制、操纵与蓄意造成心理伤害、自伤／自杀举动、相爱者互相持械伤害、死亡献祭、灭世灾难、血与战斗伤、未成年角色裸露和性化、同性恋爱遭否定的社会压力。</x:v>
       </x:c>
       <x:c r="O307" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P307" s="36" t="n">
         <x:v>3069</x:v>
@@ -20398,7 +20398,7 @@
         <x:v>短篇喜剧将亲密互动压缩为笑点；侑与步梦有特殊幼驯染读法；“妹妹”游戏、竞争和恶作剧会夸张呈现关系边界。</x:v>
       </x:c>
       <x:c r="O308" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P308" s="36" t="n">
         <x:v>3084</x:v>
@@ -20463,7 +20463,7 @@
         <x:v>包办婚约与未先行同意的同居、姐妹执着及越界喜剧、性化玩笑、幼态角色置于高中语境、事故失忆和疾病／雪山救援</x:v>
       </x:c>
       <x:c r="O309" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P309" s="36" t="n">
         <x:v>3085</x:v>
@@ -20528,7 +20528,7 @@
         <x:v>突然逼近与试图亲吻、无视连续拒绝的强迫亲密、创伤性错认、单向感情与占有、情感操纵、重病与死亡、长期哀伤、骑马事故与失忆</x:v>
       </x:c>
       <x:c r="O310" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P310" s="36" t="n">
         <x:v>3088</x:v>
@@ -20593,7 +20593,7 @@
         <x:v>未成年角色遭遇战斗危险与性化喜剧；强制魔法契约；对义兄的单向恋心；误认对象的接吻喜剧</x:v>
       </x:c>
       <x:c r="O311" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P311" s="36" t="n">
         <x:v>3096</x:v>
@@ -20658,7 +20658,7 @@
         <x:v>高中生泳装与身体尺寸笑料、夸张打闹与威胁、占有式反应被当作笑点、成年男性校医对女学生的恋物化言论、未经充分协商的身体接触笑料</x:v>
       </x:c>
       <x:c r="O312" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P312" s="36" t="n">
         <x:v>3098</x:v>
@@ -20723,7 +20723,7 @@
         <x:v>枪械与机器人暴力、死亡、人体与意识实验、宗教操纵、未成年人遭控制、偶像及成人影像产业剥削、裸体与性暗示。</x:v>
       </x:c>
       <x:c r="O313" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P313" s="36" t="n">
         <x:v>3104</x:v>
@@ -20788,7 +20788,7 @@
         <x:v>武侠暴力、兵器、流血与重伤、擂台及多方冲突、身份伪装与阴谋、拘禁风险、死亡威胁、群像焦点转移</x:v>
       </x:c>
       <x:c r="O314" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P314" s="36" t="n">
         <x:v>3105</x:v>
@@ -20853,7 +20853,7 @@
         <x:v>恐怖袭击、枪战与死亡、生化感染与人体实验、囚禁胁迫、创伤与心理操控</x:v>
       </x:c>
       <x:c r="O315" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P315" s="36" t="n">
         <x:v>3106</x:v>
@@ -20918,7 +20918,7 @@
         <x:v>高速台词、荒诞暴力与死亡笑料、身体触碰与性化玩笑、昆虫与动物威胁、电影戏仿</x:v>
       </x:c>
       <x:c r="O316" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P316" s="36" t="n">
         <x:v>3112</x:v>
@@ -20983,7 +20983,7 @@
         <x:v>赌博债务与强迫、制度性羞辱、身体伤害、生死赌局、性化支配、家庭权力冲突</x:v>
       </x:c>
       <x:c r="O317" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P317" s="36" t="n">
         <x:v>3118</x:v>
@@ -21048,7 +21048,7 @@
         <x:v>性侵或性侵未遂、未成年角色性化裸露、控制与政治暴力、朋友背叛、角色死亡、战争、失忆、年龄及权力差恋爱</x:v>
       </x:c>
       <x:c r="O318" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P318" s="36" t="n">
         <x:v>3121</x:v>
@@ -21113,7 +21113,7 @@
         <x:v>乐队竞争与演出压力、暂时疏离、被离开焦虑、行业契约压力及轻度奇幻危险。</x:v>
       </x:c>
       <x:c r="O319" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P319" s="36" t="n">
         <x:v>3131</x:v>
@@ -21178,7 +21178,7 @@
         <x:v>夸张打闹和危险特技、如厕／身体／衣着笑话、女学生对成年教师的单向心意、前暴走族相关追逐与威胁笑料、地位羞辱式喜剧</x:v>
       </x:c>
       <x:c r="O320" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P320" s="36" t="n">
         <x:v>3138</x:v>
@@ -21243,7 +21243,7 @@
         <x:v>朋友间占有与嫉妒、言语冲突和短暂决裂、家庭对社团活动的压力、姐妹冲突与师生角色张力、官方梗概中的温泉合宿语境</x:v>
       </x:c>
       <x:c r="O321" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P321" s="36" t="n">
         <x:v>3171</x:v>
@@ -21308,7 +21308,7 @@
         <x:v>高速对白、荒诞肢体笑料、身体与性暗示笑料、竞争与追逐</x:v>
       </x:c>
       <x:c r="O322" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P322" s="36" t="n">
         <x:v>3172</x:v>
@@ -21373,7 +21373,7 @@
         <x:v>赌博债务、羞辱与“家畜”制度；异性配对赌局与“过夜”赌注；婚约和性别权力压力；背叛、操控与心理威吓。</x:v>
       </x:c>
       <x:c r="O323" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P323" s="36" t="n">
         <x:v>3182</x:v>
@@ -21438,7 +21438,7 @@
         <x:v>成年人对小学生的特殊关注、明显年龄差与照护边界不对等，以及服装、摄影、点心交换、旅行风险和家庭感伤。</x:v>
       </x:c>
       <x:c r="O324" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P324" s="36" t="n">
         <x:v>3200</x:v>
@@ -21503,7 +21503,7 @@
         <x:v>未成年角色遇险、欺骗与心理操纵、家庭分离、世界危机与石化。</x:v>
       </x:c>
       <x:c r="O325" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P325" s="36" t="n">
         <x:v>3201</x:v>
@@ -21568,7 +21568,7 @@
         <x:v>高速语言、夸张受伤与威胁笑料、身体和内衣玩笑、轻度性暗示。</x:v>
       </x:c>
       <x:c r="O326" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P326" s="36" t="n">
         <x:v>3202</x:v>
@@ -21633,7 +21633,7 @@
         <x:v>高速短片、荒诞暴力与死亡笑料、胸部和内裤话题、未经同意的触摸台词。</x:v>
       </x:c>
       <x:c r="O327" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P327" s="36" t="n">
         <x:v>3236</x:v>
@@ -21698,7 +21698,7 @@
         <x:v>枪械、追捕、拘留、营救、暗杀未遂、政变阴谋、政治暴力、双重间谍、重要人物死亡与悬念式结尾。</x:v>
       </x:c>
       <x:c r="O328" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P328" s="36" t="n">
         <x:v>3242</x:v>
@@ -21763,7 +21763,7 @@
         <x:v>工作压力、职业受挫、地方衰退、朋友冲突、疾病与性别化婚恋压力</x:v>
       </x:c>
       <x:c r="O329" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P329" s="36" t="n">
         <x:v>3243</x:v>
@@ -21828,7 +21828,7 @@
         <x:v>女子乐队解散创伤、归属焦虑、隐瞒、关系操控、激烈争执与情绪崩溃</x:v>
       </x:c>
       <x:c r="O330" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P330" s="36" t="n">
         <x:v>3247</x:v>
@@ -21893,7 +21893,7 @@
         <x:v>喜剧化暴力、威胁与死亡玩笑；带性意味的画面或台词；性别角色扮演笑话</x:v>
       </x:c>
       <x:c r="O331" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P331" s="36" t="n">
         <x:v>3257</x:v>
@@ -21958,7 +21958,7 @@
         <x:v>高速对白、洗澡闯入、全裸、内裤、胸部与擦身笑料、夸张暴力和死亡表达、危险饮食、幽灵及混合性别集会误导。</x:v>
       </x:c>
       <x:c r="O332" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P332" s="36" t="n">
         <x:v>3266</x:v>
@@ -22023,7 +22023,7 @@
         <x:v>主从等级、洗脑与记忆剥夺、人格去除、囚禁威胁、身体危险。</x:v>
       </x:c>
       <x:c r="O333" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P333" s="36" t="n">
         <x:v>3277</x:v>
@@ -22088,7 +22088,7 @@
         <x:v>短期留学、学园偶像梦想受阻、离别与社团申请压力；未确认女女交往</x:v>
       </x:c>
       <x:c r="O334" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P334" s="36" t="n">
         <x:v>3281</x:v>
@@ -22153,7 +22153,7 @@
         <x:v>战争、枪击、暗杀、死亡、犯罪组织控制、失忆与身份碎裂、绑架、心理操纵、男性强迫求爱与身体胁迫、创伤。</x:v>
       </x:c>
       <x:c r="O335" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P335" s="36" t="n">
         <x:v>3285</x:v>
@@ -22218,7 +22218,7 @@
         <x:v>高速语言、电影戏仿、夸张吐槽、身体与伤害笑料、武器笑话、情人节巧克力及剧中求婚</x:v>
       </x:c>
       <x:c r="O336" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P336" s="36" t="n">
         <x:v>3299</x:v>
@@ -22283,7 +22283,7 @@
         <x:v>未成年人战斗、同伴死亡与失踪、身体损失、制度性献祭、创伤及情绪崩溃</x:v>
       </x:c>
       <x:c r="O337" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P337" s="36" t="n">
         <x:v>3301</x:v>
@@ -22348,7 +22348,7 @@
         <x:v>收养与家庭分离、死亡预兆、白血病与治疗、事故危险、电视正篇前史剧透</x:v>
       </x:c>
       <x:c r="O338" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P338" s="36" t="n">
         <x:v>3334</x:v>
@@ -22413,7 +22413,7 @@
         <x:v>社会孤立、自杀企图相关叙述、危险游戏、高压卡牌战斗、分离、精神伤害、威胁性台词和近亲恋爱欲望。</x:v>
       </x:c>
       <x:c r="O339" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P339" s="36" t="n">
         <x:v>3355</x:v>
@@ -22478,7 +22478,7 @@
         <x:v>祖母去世后的独居与孤独、父母不在身边、升学压力、短暂生病与食欲不适</x:v>
       </x:c>
       <x:c r="O340" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P340" s="36" t="n">
         <x:v>3361</x:v>
@@ -22543,7 +22543,7 @@
         <x:v>舞台竞争与落选压力、人格化 Sense 的消失焦虑、童年记忆与自我认识困惑、剧中剧的异性恋爱／接吻／死亡、职业年龄压力。</x:v>
       </x:c>
       <x:c r="O341" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P341" s="36" t="n">
         <x:v>3386</x:v>
@@ -22608,7 +22608,7 @@
         <x:v>超现实肢体喜剧、内衣与身体边界笑料、泳衣及澡堂裸体笑料、高速台词与感官负荷</x:v>
       </x:c>
       <x:c r="O342" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P342" s="36" t="n">
         <x:v>3399</x:v>
@@ -22673,7 +22673,7 @@
         <x:v>奇幻怪物袭击与危险、慢性病与失声焦虑、家庭分离与王室约束、死亡及幽灵相关内容、喜剧性的暂时年龄变化</x:v>
       </x:c>
       <x:c r="O343" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P343" s="36" t="n">
         <x:v>3405</x:v>
@@ -22738,7 +22738,7 @@
         <x:v>女性角色的裸露、性化服务与性骚扰场景、陨石灾害、战斗与武器、绑架和身体控制、主从契约与国家权力不对等、失踪和世界末日危机。</x:v>
       </x:c>
       <x:c r="O344" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P344" s="36" t="n">
         <x:v>3411</x:v>
@@ -22803,7 +22803,7 @@
         <x:v>战争、奴役、身体改造、精神控制、死亡、重伤和灾难战斗。</x:v>
       </x:c>
       <x:c r="O345" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P345" s="36" t="n">
         <x:v>3458</x:v>
@@ -22868,7 +22868,7 @@
         <x:v>潜水训练中的呼吸困难、水下焦虑与风险、高中生泳装场景</x:v>
       </x:c>
       <x:c r="O346" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P346" s="36" t="n">
         <x:v>3501</x:v>
@@ -22933,7 +22933,7 @@
         <x:v>昏迷与住院、亲属控制与恐惧、记忆改写与身份困惑、虚拟世界中的受困、战斗威胁、孤立与严重心理痛苦</x:v>
       </x:c>
       <x:c r="O347" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P347" s="36" t="n">
         <x:v>3506</x:v>
@@ -22998,7 +22998,7 @@
         <x:v>体重与身材焦虑、身体与肌肉的性化展示、泳装／服装笑料、运动过度与受伤风险笑料、局部异性恋意向</x:v>
       </x:c>
       <x:c r="O348" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P348" s="36" t="n">
         <x:v>3516</x:v>
@@ -23063,7 +23063,7 @@
         <x:v>感冒发热、魔法失控、生日筹备混乱、极短篇幅与音乐喜剧节奏。</x:v>
       </x:c>
       <x:c r="O349" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P349" s="36" t="n">
         <x:v>3525</x:v>
@@ -23075,13 +23075,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S349" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T349" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U349" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="57" customHeight="1">
@@ -23128,7 +23128,7 @@
         <x:v>运动挫折、社交媒体压力、年龄与经验差异</x:v>
       </x:c>
       <x:c r="O350" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P350" s="36" t="n">
         <x:v>3549</x:v>
@@ -23193,7 +23193,7 @@
         <x:v>截稿与职业焦虑、酒后纠缠笑料、自我贬抑、体重与饮食笑话、成人漫画工作话题</x:v>
       </x:c>
       <x:c r="O351" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P351" s="36" t="n">
         <x:v>3562</x:v>
@@ -23258,7 +23258,7 @@
         <x:v>卖弄身体与裸露笑料、身体与生理讨论、未成年人置于暧昧或浴室语境、族群歧视与威权政治讽喻、战争及大规模迫害暗示、儿童照护与疾病。</x:v>
       </x:c>
       <x:c r="O352" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P352" s="36" t="n">
         <x:v>3585</x:v>
@@ -23323,7 +23323,7 @@
         <x:v>自杀意念、自伤威胁、家人死亡、车祸、火灾、溺水、捕食、身体恐怖、强制控制、身体自主权威胁和严重心理痛苦。</x:v>
       </x:c>
       <x:c r="O353" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P353" s="36" t="n">
         <x:v>3620</x:v>
@@ -23388,7 +23388,7 @@
         <x:v>事故、疾病、学校考核、嫉妒及敌对反应的喜剧化表达</x:v>
       </x:c>
       <x:c r="O354" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P354" s="36" t="n">
         <x:v>3647</x:v>
@@ -23453,7 +23453,7 @@
         <x:v>父亲死亡与哀伤、重组家庭适应、性别刻板印象与同伴排斥、饮酒喜剧、成年角色关于年轻女性的喜剧性表述、儿童焦虑与家庭冲突</x:v>
       </x:c>
       <x:c r="O355" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P355" s="36" t="n">
         <x:v>3673</x:v>
@@ -23518,7 +23518,7 @@
         <x:v>食物匮乏、贫困与大食笑料，言语冲突及带血服装笑料。</x:v>
       </x:c>
       <x:c r="O356" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P356" s="36" t="n">
         <x:v>3675</x:v>
@@ -23583,7 +23583,7 @@
         <x:v>女高中生泳装与温泉情境、身体羞耻笑料、演出与公众压力、服装失窃疑云</x:v>
       </x:c>
       <x:c r="O357" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P357" s="36" t="n">
         <x:v>3679</x:v>
@@ -23648,7 +23648,7 @@
         <x:v>性骚扰开场、玩具枪与夸张暴力笑料、欺凌与残酷玩笑、体型羞辱／节食笑料、单向追逐式亲密笑料</x:v>
       </x:c>
       <x:c r="O358" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P358" s="36" t="n">
         <x:v>3706</x:v>
@@ -23713,7 +23713,7 @@
         <x:v>柔道对抗与受伤、比赛失利、学业与家庭期待压力、性别角色笑谈。</x:v>
       </x:c>
       <x:c r="O359" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P359" s="36" t="n">
         <x:v>3714</x:v>
@@ -23778,7 +23778,7 @@
         <x:v>异形与怪诞恐怖、威胁和惊吓、围绕“看得见”的孤立与嘲弄、含女高中生身体与内衣相关的喜剧性台词、丧亲和动物伤害指控主题。</x:v>
       </x:c>
       <x:c r="O360" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P360" s="36" t="n">
         <x:v>3724</x:v>
@@ -23843,7 +23843,7 @@
         <x:v>圣诞生日、夜访、共浴邀请、留宿话题与地方宣传拍摄。</x:v>
       </x:c>
       <x:c r="O361" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P361" s="36" t="n">
         <x:v>3731</x:v>
@@ -23908,7 +23908,7 @@
         <x:v>浴场与泳装画面、饮酒失态喜剧、占术怪异与轻度幻想危机、寻母与童年分离、童年女女亲吻被称为魔法问候</x:v>
       </x:c>
       <x:c r="O362" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P362" s="36" t="n">
         <x:v>3733</x:v>
@@ -23973,7 +23973,7 @@
         <x:v>小学部运动会、成人威胁与“侧室”误会笑料、针对儿童角色的“性感”台词与性化笑料、厕所急迫笑料、竞技压力与过度训练</x:v>
       </x:c>
       <x:c r="O363" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P363" s="36" t="n">
         <x:v>3757</x:v>
@@ -24038,7 +24038,7 @@
         <x:v>女性群像日常、泳装和猫耳玩笑、庆生与团队活动。</x:v>
       </x:c>
       <x:c r="O364" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P364" s="36" t="n">
         <x:v>3760</x:v>
@@ -24103,7 +24103,7 @@
         <x:v>战争与军事占领、枪炮威胁、战争创伤与丧失、敌国偏见、疾病与儿童遇险、关于婚外恋与非婚生育的回忆叙事。</x:v>
       </x:c>
       <x:c r="O365" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P365" s="36" t="n">
         <x:v>3766</x:v>
@@ -24168,7 +24168,7 @@
         <x:v>亲人去世、失去住处与未成年人工作处境；成年角色对未成年角色的性骚扰和性化幻想作为反复笑料；饮酒；浴场、泳池与服务性画面</x:v>
       </x:c>
       <x:c r="O366" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P366" s="36" t="n">
         <x:v>3794</x:v>
@@ -24233,7 +24233,7 @@
         <x:v>追逐与嫉妒笑料、未经邀请的贴近、主从玩笑、性暗示、姐妹依恋竞争与夸张威胁</x:v>
       </x:c>
       <x:c r="O367" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P367" s="36" t="n">
         <x:v>3808</x:v>
@@ -24298,7 +24298,7 @@
         <x:v>枪械、潜入、王位继承危机、暗杀阴谋、政治暴力、身份伪装、儿童权力压力与悬念结尾。</x:v>
       </x:c>
       <x:c r="O368" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P368" s="36" t="n">
         <x:v>3812</x:v>
@@ -24363,7 +24363,7 @@
         <x:v>海上武装战斗、炮击爆炸、舰船危险、儿童被卷入危险、强制劳动与救援行动、密集海事术语。</x:v>
       </x:c>
       <x:c r="O369" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P369" s="36" t="n">
         <x:v>3827</x:v>
@@ -24428,7 +24428,7 @@
         <x:v>精神控制、身体改造、家庭创伤、重伤、死亡和灾难战斗。</x:v>
       </x:c>
       <x:c r="O370" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P370" s="36" t="n">
         <x:v>3835</x:v>
@@ -24493,7 +24493,7 @@
         <x:v>未成年偶像的暴露工作与男性顾客接吻要求、偶像恋爱禁令、羞辱与解雇、事务所剥削、流言、团体冲突</x:v>
       </x:c>
       <x:c r="O371" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P371" s="36" t="n">
         <x:v>3847</x:v>
@@ -24558,7 +24558,7 @@
         <x:v>长寿与历史失落、赌博和金钱困扰的喜剧描写、未成年人的考试焦虑</x:v>
       </x:c>
       <x:c r="O372" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P372" s="36" t="n">
         <x:v>3850</x:v>
@@ -24623,7 +24623,7 @@
         <x:v>未成年人自杀与自伤、校园欺凌与孤立、性暴力与虐待、疑似师生边界越界、身体恐怖与血腥幻想暴力、饮食障碍与身体羞辱、家庭冲突与悲伤、宠物死亡、针对跨性别者的恐同与错称性别伤害、医疗实验与操控。</x:v>
       </x:c>
       <x:c r="O373" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P373" s="36" t="n">
         <x:v>3851</x:v>
@@ -24688,7 +24688,7 @@
         <x:v>英语字幕是主体未标的歌词轨；完整短片画面已经核对，但脸红、同行或身体距离不单独证明恋爱回应或交往；2018 年 OVA 与漫画不在范围内。</x:v>
       </x:c>
       <x:c r="O374" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P374" s="36" t="n">
         <x:v>3857</x:v>
@@ -24753,7 +24753,7 @@
         <x:v>校园丧尸灾难、咬伤、血迹、武器、爆炸、死亡与同伴失去。</x:v>
       </x:c>
       <x:c r="O375" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P375" s="36" t="n">
         <x:v>3860</x:v>
@@ -24818,7 +24818,7 @@
         <x:v>自杀与群体死亡、创伤、性暴力相关叙述、意识控制、战争与枪声。</x:v>
       </x:c>
       <x:c r="O376" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P376" s="36" t="n">
         <x:v>3893</x:v>
@@ -24883,7 +24883,7 @@
         <x:v>个人排名与公开投票压力、伙伴间竞争与退出焦虑、亲子赞助公平冲突、旧搭档失和与修复、未确认的女女浪漫指向</x:v>
       </x:c>
       <x:c r="O377" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P377" s="36" t="n">
         <x:v>3900</x:v>
@@ -24948,7 +24948,7 @@
         <x:v>泳装与身体暴露笑料、赌博与财务失当笑料、失亲与宠物离别、包办婚约与分离焦虑、超自然威胁</x:v>
       </x:c>
       <x:c r="O378" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P378" s="36" t="n">
         <x:v>3920</x:v>
@@ -25013,7 +25013,7 @@
         <x:v>战争入侵与军事占领、枪炮轰炸与战场伤害、军民死亡、处决与灭口、酷刑与火刑叙述、人体实验与克隆、可能致命的自我牺牲、政治宣传与超自然力量工具化、政治性婚约、身体笑料及沐浴／更衣场景。</x:v>
       </x:c>
       <x:c r="O379" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P379" s="36" t="n">
         <x:v>3923</x:v>
@@ -25078,7 +25078,7 @@
         <x:v>怪物袭击、角色受操控、乐队冲突与短暂分离、可能离别带来的情绪压力。</x:v>
       </x:c>
       <x:c r="O380" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P380" s="36" t="n">
         <x:v>4010</x:v>
@@ -25143,7 +25143,7 @@
         <x:v>战争与流离失所、军队纪律、受伤与失去魔力、与使魔分离、少量身体暴露笑料</x:v>
       </x:c>
       <x:c r="O381" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P381" s="36" t="n">
         <x:v>4018</x:v>
@@ -25208,7 +25208,7 @@
         <x:v>幻想战斗与危机、学生之间突如其来的亲吻、魔法造成的短暂情感失常笑料、学校场景与轻度服务性画面。</x:v>
       </x:c>
       <x:c r="O382" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P382" s="36" t="n">
         <x:v>4020</x:v>
@@ -25273,7 +25273,7 @@
         <x:v>恐怖、惨剧循环、谋杀与身体伤害；精神崩溃、家庭暴力、监禁和儿童受害；关系中的执着、操纵与权力失衡。</x:v>
       </x:c>
       <x:c r="O383" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P383" s="36" t="n">
         <x:v>4058</x:v>
@@ -25338,7 +25338,7 @@
         <x:v>越界追随与骚扰、家庭控制与隔离、反移民政治与拘留、职业压力与物化、亲子冲突、疾病与丧失、威胁及非血腥暴力。</x:v>
       </x:c>
       <x:c r="O384" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P384" s="36" t="n">
         <x:v>4073</x:v>
@@ -25403,7 +25403,7 @@
         <x:v>中学生偶像与公开舞台压力、社团存废与竞赛焦虑、家长反对演艺活动、家庭期待与姐妹冲突、喜剧性潜入与误导情报。</x:v>
       </x:c>
       <x:c r="O385" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P385" s="36" t="n">
         <x:v>4114</x:v>
@@ -25468,7 +25468,7 @@
         <x:v>高压卡牌战斗与强制规则、暴力与身体伤害、记忆丧失与身份置换、操控与虐待、晶—乌莉丝关系中的伤害和依赖、花代／游月—香月的近亲恋爱欲望、孤独与自我危险。</x:v>
       </x:c>
       <x:c r="O386" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P386" s="36" t="n">
         <x:v>4119</x:v>
@@ -25533,7 +25533,7 @@
         <x:v>未获确认的女女告白与关系尴尬、男性对女高中生的性化评论、学生角色</x:v>
       </x:c>
       <x:c r="O387" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P387" s="36" t="n">
         <x:v>4120</x:v>
@@ -25598,7 +25598,7 @@
         <x:v>洗浴与局部裸露、性暗示、性别变形及“男の娘”笑料、儿童单向求婚、身体故障与伤害、职场和御宅文化讽刺。</x:v>
       </x:c>
       <x:c r="O388" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P388" s="36" t="n">
         <x:v>4130</x:v>
@@ -25663,7 +25663,7 @@
         <x:v>废弃医院、女性幽灵、死亡与升天告别；脱衣猜拳、身体暴露、捆绑及性化喜剧；男性单向求婚幻想与裸露欲望。</x:v>
       </x:c>
       <x:c r="O389" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P389" s="36" t="n">
         <x:v>4165</x:v>
@@ -25728,7 +25728,7 @@
         <x:v>严重社交焦虑与失语、强势社团招募、慢性声带疾病与健康风险、校园冲突、朋友分离、单向告白与拒绝</x:v>
       </x:c>
       <x:c r="O390" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P390" s="36" t="n">
         <x:v>4206</x:v>
@@ -25793,7 +25793,7 @@
         <x:v>短篇喜剧把亲密互动压缩成笑点；第 2 话的共伞与信件有浪漫读法；第 1、6、11 话的胜利之路是幻想层。</x:v>
       </x:c>
       <x:c r="O391" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P391" s="36" t="n">
         <x:v>4216</x:v>
@@ -25858,7 +25858,7 @@
         <x:v>泳装与身材笑料、性别气质和选美笑话、BL 游戏话题、轻微夸张喜剧。</x:v>
       </x:c>
       <x:c r="O392" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P392" s="36" t="n">
         <x:v>4234</x:v>
@@ -25923,7 +25923,7 @@
         <x:v>奇幻袭击、误判与拘押、竞赛和演出压力、家庭紧急情况、公共冲突与音乐都市危机。</x:v>
       </x:c>
       <x:c r="O393" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P393" s="36" t="n">
         <x:v>4268</x:v>
@@ -25988,7 +25988,7 @@
         <x:v>幻想战斗与受伤、未成年角色遇险、情绪操控与独占、记忆操控、家庭分离与告别、局部异性恋爱支线。</x:v>
       </x:c>
       <x:c r="O394" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P394" s="36" t="n">
         <x:v>4288</x:v>
@@ -26053,7 +26053,7 @@
         <x:v>学业与舞台压力、家庭规划限制、成员短暂失和、住宿与洗浴笑料、竞演焦虑</x:v>
       </x:c>
       <x:c r="O395" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P395" s="36" t="n">
         <x:v>4290</x:v>
@@ -26118,7 +26118,7 @@
         <x:v>身体部位特写、按摩与拉伸、轻度性意味和搭讪玩笑；结尾开启后续悬念。</x:v>
       </x:c>
       <x:c r="O396" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P396" s="36" t="n">
         <x:v>4313</x:v>
@@ -26130,7 +26130,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S396" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T396" s="33" t="n">
         <x:v>0</x:v>
@@ -26183,7 +26183,7 @@
         <x:v>竞赛压力、团队焦虑与意见分歧；局部直接爱意表达的关系语境与相互性未确认恋爱。</x:v>
       </x:c>
       <x:c r="O397" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P397" s="36" t="n">
         <x:v>4342</x:v>
@@ -26248,7 +26248,7 @@
         <x:v>高压许愿游戏、心理痛苦与绝望、记忆丧失和社交隔离、霸凌与公开羞辱、身体／身份置换、近亲恋爱欲望、暴力与自我危险。</x:v>
       </x:c>
       <x:c r="O398" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P398" s="36" t="n">
         <x:v>4407</x:v>
@@ -26313,7 +26313,7 @@
         <x:v>性别隐瞒与女装、由隐瞒形成的恋爱张力、台词提及舞台／意外亲密接触、抢劫与暴力威胁、死亡与幽灵角色。</x:v>
       </x:c>
       <x:c r="O399" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P399" s="36" t="n">
         <x:v>4411</x:v>
@@ -26378,7 +26378,7 @@
         <x:v>舞台事故风险、自我否定、团队争执、自然灾害与交通危机</x:v>
       </x:c>
       <x:c r="O400" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P400" s="36" t="n">
         <x:v>4440</x:v>
@@ -26443,7 +26443,7 @@
         <x:v>短篇喜剧、单向爱意、占有性笑料、接吻话题、性化鞭打玩笑、身体笑料与推理式假伤害。</x:v>
       </x:c>
       <x:c r="O401" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P401" s="36" t="n">
         <x:v>4477</x:v>
@@ -26508,7 +26508,7 @@
         <x:v>18 禁成人内容、亲属关系、操纵、性暴力与同意状态复杂、邪教献祭、血腥恐怖和身体伤害</x:v>
       </x:c>
       <x:c r="O402" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P402" s="36" t="n">
         <x:v>4488</x:v>
@@ -26520,7 +26520,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S402" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T402" s="33" t="n">
         <x:v>60</x:v>
@@ -26573,7 +26573,7 @@
         <x:v>怪兽拟人化、变身、超能力失控、侵略计划、阵营战斗与城市危机。</x:v>
       </x:c>
       <x:c r="O403" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P403" s="36" t="n">
         <x:v>4494</x:v>
@@ -26638,7 +26638,7 @@
         <x:v>单恋受挫、嫉妒、排斥、关系隐瞒、超自然力量失控与消失风险</x:v>
       </x:c>
       <x:c r="O404" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P404" s="36" t="n">
         <x:v>4506</x:v>
@@ -26703,7 +26703,7 @@
         <x:v>战斗、囚禁与人身威胁；成人向裸露／泳装、越界身体笑料及单向追求笑料。</x:v>
       </x:c>
       <x:c r="O405" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P405" s="36" t="n">
         <x:v>4530</x:v>
@@ -26768,7 +26768,7 @@
         <x:v>怪物暴力、血腥与死亡；绑架、囚禁、机构控制、药物致昏迷、束缚、难以行使同意时的性化触碰、裸体、性暴力威胁、心理胁迫、丧亲与绝望。</x:v>
       </x:c>
       <x:c r="O406" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P406" s="36" t="n">
         <x:v>4578</x:v>
@@ -26833,7 +26833,7 @@
         <x:v>肢解、酷刑、出血与再生、强制召唤、谋杀企图、绑架／占有、债务和经济剥削、裸露与性化笑点。</x:v>
       </x:c>
       <x:c r="O407" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P407" s="36" t="n">
         <x:v>4580</x:v>
@@ -26898,7 +26898,7 @@
         <x:v>服务义务、地区活动与舞台压力、创作分歧、合宿和温泉情境</x:v>
       </x:c>
       <x:c r="O408" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P408" s="36" t="n">
         <x:v>4591</x:v>
@@ -26963,7 +26963,7 @@
         <x:v>毕业与团体分离、三年级成员失联、家庭安排婚姻的压力、离别和重聚。</x:v>
       </x:c>
       <x:c r="O409" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P409" s="36" t="n">
         <x:v>4596</x:v>
@@ -27028,7 +27028,7 @@
         <x:v>地下城战斗、怪物袭击、伤亡危险、谋杀未遂、身体笑料、单向理想化与嫉妒。</x:v>
       </x:c>
       <x:c r="O410" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P410" s="36" t="n">
         <x:v>4603</x:v>
@@ -27093,7 +27093,7 @@
         <x:v>严重社交焦虑与回避、紧张引发呕吐或倒下的笑料、幼驯染以绝交为条件的约定、反复害怕被朋友抛下、校园出丑与摔倒、因外貌而令人畏惧的教师。</x:v>
       </x:c>
       <x:c r="O411" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P411" s="36" t="n">
         <x:v>4611</x:v>
@@ -27158,7 +27158,7 @@
         <x:v>儿童交通事故与昏迷、误认姐姐死亡、孤独与虚拟世界不安、学校回避、科幻喜剧暴力。</x:v>
       </x:c>
       <x:c r="O412" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P412" s="36" t="n">
         <x:v>4621</x:v>
@@ -27223,7 +27223,7 @@
         <x:v>家庭分离、亲子关系破裂、龙族战争、战斗、儿童角色卷入危险、性化笑料与暗示性对白。</x:v>
       </x:c>
       <x:c r="O413" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P413" s="36" t="n">
         <x:v>4628</x:v>
@@ -27288,7 +27288,7 @@
         <x:v>校园军事训练与舰艇背景、旧船受损、班级解散传闻、分离焦虑、密令与请愿压力、喜剧性夸张。</x:v>
       </x:c>
       <x:c r="O414" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P414" s="36" t="n">
         <x:v>4639</x:v>
@@ -27353,7 +27353,7 @@
         <x:v>枪战、爆炸、绑架与拘束、人体实验、政治暴力、未成年人反复置于危险中。</x:v>
       </x:c>
       <x:c r="O415" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P415" s="36" t="n">
         <x:v>4657</x:v>
@@ -27418,7 +27418,7 @@
         <x:v>肢体恶作剧、外貌与摄影笑料、学生角色间性玩笑与意外亲吻、单向男性恋爱笑料、家庭冲突与离家情节</x:v>
       </x:c>
       <x:c r="O416" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P416" s="36" t="n">
         <x:v>4661</x:v>
@@ -27483,7 +27483,7 @@
         <x:v>高中生与年幼儿童的恋爱化关系、诱拐与对外隔绝、家庭暴力与遗弃、勒索和操纵、跟踪、肢体伤害、杀人和尸体处理、纵火、性暴力及对未成年人的性化欲望、共同赴死提议、死亡。</x:v>
       </x:c>
       <x:c r="O417" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P417" s="36" t="n">
         <x:v>4674</x:v>
@@ -27548,7 +27548,7 @@
         <x:v>全身义体、武装机器人、爆炸与动作暴力、身体与性暗示笑料。</x:v>
       </x:c>
       <x:c r="O418" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P418" s="36" t="n">
         <x:v>4676</x:v>
@@ -27613,7 +27613,7 @@
         <x:v>童年丧亲与哀伤、失去居所与水族馆闭馆、职业挫败与工作压力、家人疾病住院、孤立与情绪困扰、饮酒。</x:v>
       </x:c>
       <x:c r="O419" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P419" s="36" t="n">
         <x:v>4705</x:v>
@@ -27678,7 +27678,7 @@
         <x:v>末日灾变、青少年长期失联、危险旅行与战斗、身体变形、蘑菇寄生、僵尸、流血与死亡威胁、记忆篡改、精神控制、粗俗笑话和家庭冲突。</x:v>
       </x:c>
       <x:c r="O420" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P420" s="36" t="n">
         <x:v>4747</x:v>
@@ -27743,7 +27743,7 @@
         <x:v>成人色情、教团控制、威胁与强迫、姐妹性化互动、多人性行为、性奴役设定与怀孕焦虑。</x:v>
       </x:c>
       <x:c r="O421" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P421" s="36" t="n">
         <x:v>4779</x:v>
@@ -27755,7 +27755,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S421" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T421" s="33" t="n">
         <x:v>40</x:v>
@@ -27808,7 +27808,7 @@
         <x:v>成人向性感宣传、动作冲突、囚禁、胁迫与越界亲属欲望</x:v>
       </x:c>
       <x:c r="O422" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P422" s="36" t="n">
         <x:v>4785</x:v>
@@ -27873,7 +27873,7 @@
         <x:v>成人向裸露与性化呈现、非自愿触摸与羞辱、战斗伤害／死亡／石化、精神控制与附身、姐妹间单向占有欲、异性婚姻与家庭分离。</x:v>
       </x:c>
       <x:c r="O423" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P423" s="36" t="n">
         <x:v>4818</x:v>
@@ -27938,7 +27938,7 @@
         <x:v>无血缘姊妹欲望、睡眠状态下靠近嘴唇且实际接触与同意未确认、分离与单向爱意、奇幻暴力、死亡、牺牲、黑暗主题与性化呈现。</x:v>
       </x:c>
       <x:c r="O424" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P424" s="36" t="n">
         <x:v>4826</x:v>
@@ -28003,7 +28003,7 @@
         <x:v>指挥官指向的约会与占有台词、泡澡及身体笑料、短暂失忆误会。</x:v>
       </x:c>
       <x:c r="O425" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P425" s="36" t="n">
         <x:v>4831</x:v>
@@ -28068,7 +28068,7 @@
         <x:v>未成年角色的恋爱告白、男性同学的性化妄想、疾病与交通事故误会笑料</x:v>
       </x:c>
       <x:c r="O426" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P426" s="36" t="n">
         <x:v>4832</x:v>
@@ -28133,7 +28133,7 @@
         <x:v>亲人死亡与哀伤、记忆缺失、朋友冲突与和解、掌掴、情绪困扰、分离与角色暂时消失</x:v>
       </x:c>
       <x:c r="O427" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P427" s="36" t="n">
         <x:v>4839</x:v>
@@ -28198,7 +28198,7 @@
         <x:v>成人向裸露、持续身体性化、性化身体接触、强迫服务、战斗受伤、身体侵犯、姐妹间占有、魔法附身与控制、生命力吸取。</x:v>
       </x:c>
       <x:c r="O428" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P428" s="36" t="n">
         <x:v>4870</x:v>
@@ -28263,7 +28263,7 @@
         <x:v>科幻与机甲背景、远距离分隔、友情与恋爱式玩笑并置</x:v>
       </x:c>
       <x:c r="O429" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P429" s="36" t="n">
         <x:v>4901</x:v>
@@ -28328,7 +28328,7 @@
         <x:v>成人色情内容、高中生角色性化、师生关系、亲属间性化互动、多人性行为、窥视、拒绝与同意边界不清。</x:v>
       </x:c>
       <x:c r="O430" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P430" s="36" t="n">
         <x:v>4902</x:v>
@@ -28340,7 +28340,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S430" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T430" s="33" t="n">
         <x:v>50</x:v>
@@ -28393,7 +28393,7 @@
         <x:v>分离焦虑、身体互换与魔法造成的失控／贴近、单向异性恋误会、风暴与遇险。</x:v>
       </x:c>
       <x:c r="O431" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P431" s="36" t="n">
         <x:v>4902</x:v>
@@ -28458,7 +28458,7 @@
         <x:v>高中年龄角色的性内容、师生及前师生边界、单向感情被利用、亲密场景中的同意问题、重叠关系与出轨、言语骚扰、失恋与情绪痛苦。</x:v>
       </x:c>
       <x:c r="O432" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P432" s="36" t="n">
         <x:v>4914</x:v>
@@ -28523,7 +28523,7 @@
         <x:v>科幻侵略与战争、灾难和死亡背景、威胁与肢体攻击、幸存者创伤、分离与牺牲风险</x:v>
       </x:c>
       <x:c r="O433" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P433" s="36" t="n">
         <x:v>4930</x:v>
@@ -28588,7 +28588,7 @@
         <x:v>内衣、身体检查、泳装、月经及身体／性话题笑料；男女交往、师生搭讪语境与跟随进洗手间的紧张设置；流言、姐妹冲突与外貌评价</x:v>
       </x:c>
       <x:c r="O434" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P434" s="36" t="n">
         <x:v>4935</x:v>
@@ -28653,7 +28653,7 @@
         <x:v>架空战争、战斗危险、夸张伤势、裸体、内衣式服装与身体笑料</x:v>
       </x:c>
       <x:c r="O435" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P435" s="36" t="n">
         <x:v>4956</x:v>
@@ -28718,7 +28718,7 @@
         <x:v>阶级霸凌、绑架与非法拘禁、虚假指控及流放或处刑威胁、魔法伤害、占有与嫉妒被喜剧化、收养义姐弟恋爱候选。</x:v>
       </x:c>
       <x:c r="O436" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P436" s="36" t="n">
         <x:v>4963</x:v>
@@ -28783,7 +28783,7 @@
         <x:v>求生险境、脱水和落水救援、捕猎与食用动物／昆虫、救急口腔接触、侵入性补水、体液与卫生话题，以及学生角色的身体和衣物笑料。</x:v>
       </x:c>
       <x:c r="O437" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P437" s="36" t="n">
         <x:v>4966</x:v>
@@ -28848,7 +28848,7 @@
         <x:v>高密度文学梗、以文学为话题的死亡与暴力、肢体闹剧及尖锐吐槽、局部单向异性好感。</x:v>
       </x:c>
       <x:c r="O438" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P438" s="36" t="n">
         <x:v>4984</x:v>
@@ -28913,7 +28913,7 @@
         <x:v>架空战争、军事训练、身体服务性喜剧、裸体与内衣式服装、洗浴和身体接触笑料、前后辈压力。</x:v>
       </x:c>
       <x:c r="O439" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P439" s="36" t="n">
         <x:v>5015</x:v>
@@ -28978,7 +28978,7 @@
         <x:v>家庭控制与短暂限制行动、亲人离散造成的情绪困扰、校园竞赛压力、严厉批评与人际冲突。</x:v>
       </x:c>
       <x:c r="O440" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P440" s="36" t="n">
         <x:v>5021</x:v>
@@ -29043,7 +29043,7 @@
         <x:v>灾害与战斗、死亡与哀伤、身体伤害、操控与阴谋、心理痛苦、学校遇袭</x:v>
       </x:c>
       <x:c r="O441" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P441" s="36" t="n">
         <x:v>5083</x:v>
@@ -29108,7 +29108,7 @@
         <x:v>废校与前途压力、旧友疏离和自责、能力焦虑、喜剧化肢体碰撞及泳装／更衣画面。</x:v>
       </x:c>
       <x:c r="O442" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P442" s="36" t="n">
         <x:v>5112</x:v>
@@ -29173,7 +29173,7 @@
         <x:v>男性主角女装、性别隐瞒与阶级冲突。</x:v>
       </x:c>
       <x:c r="O443" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P443" s="36" t="n">
         <x:v>5125</x:v>
@@ -29188,7 +29188,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T443" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U443" s="27" t="str">
         <x:v>无</x:v>
@@ -29238,7 +29238,7 @@
         <x:v>长距离骑行的疲劳、饥饿与天气暴露；自行车活动的道路安全风险</x:v>
       </x:c>
       <x:c r="O444" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P444" s="36" t="n">
         <x:v>5126</x:v>
@@ -29303,7 +29303,7 @@
         <x:v>地下城战斗、死亡与复活设定、亲人失踪与早年丧失、犯罪团伙的同伴杀害、雇佣与管理权力差。</x:v>
       </x:c>
       <x:c r="O445" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P445" s="36" t="n">
         <x:v>5133</x:v>
@@ -29368,7 +29368,7 @@
         <x:v>历史幻想与战斗、性化服装和身体笑料、强迫服药与囚禁、强推和性化威胁语句、妖术变形、追杀和群体暴力。</x:v>
       </x:c>
       <x:c r="O446" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P446" s="36" t="n">
         <x:v>5134</x:v>
@@ -29433,7 +29433,7 @@
         <x:v>创作期限压力、自我怀疑、疾病与照护，以及涉及未成年角色的恋爱、性别转换和攻受玩笑</x:v>
       </x:c>
       <x:c r="O447" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P447" s="36" t="n">
         <x:v>5142</x:v>
@@ -29498,7 +29498,7 @@
         <x:v>毕业、学校关闭与团体分离压力；成员冲突、竞争与修复；舞台演出和竞赛压力；对未来道路的焦虑。</x:v>
       </x:c>
       <x:c r="O448" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P448" s="36" t="n">
         <x:v>5162</x:v>
@@ -29563,7 +29563,7 @@
         <x:v>贫困与儿童承担劳动、父母缺席与丧亲、疾病及住院焦虑。</x:v>
       </x:c>
       <x:c r="O449" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P449" s="36" t="n">
         <x:v>5169</x:v>
@@ -29628,7 +29628,7 @@
         <x:v>竞技失败、追逐与轻度摔倒笑料，拟人化赛马设定，试胆、悬疑剧场和夸张角色扮演。</x:v>
       </x:c>
       <x:c r="O450" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P450" s="36" t="n">
         <x:v>5191</x:v>
@@ -29693,7 +29693,7 @@
         <x:v>魔法战斗、战争创伤、囚禁、牺牲、死亡与人物工具化。</x:v>
       </x:c>
       <x:c r="O451" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P451" s="36" t="n">
         <x:v>5194</x:v>
@@ -29758,7 +29758,7 @@
         <x:v>魔法战斗、伤害与死亡风险、疾病和失散、记忆操控、组织招募、家庭忽视与情绪困境</x:v>
       </x:c>
       <x:c r="O452" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P452" s="36" t="n">
         <x:v>5245</x:v>
@@ -29823,7 +29823,7 @@
         <x:v>性别呈现与身份隐瞒、记忆处理、夸张科幻威胁、未成年角色危险处境、身体与青春期笑料。</x:v>
       </x:c>
       <x:c r="O453" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P453" s="36" t="n">
         <x:v>5247</x:v>
@@ -29888,7 +29888,7 @@
         <x:v>裤袜／足部和身体部位服务性表现、带性意味的双关、身体接触笑料、男学生与教师的性化幻想喜剧。</x:v>
       </x:c>
       <x:c r="O454" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P454" s="36" t="n">
         <x:v>5288</x:v>
@@ -29953,7 +29953,7 @@
         <x:v>机甲战斗、宇宙战争、政治冲突、城市与地球级灾害、离别、失忆、背叛、危险实验和关系误解</x:v>
       </x:c>
       <x:c r="O455" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P455" s="36" t="n">
         <x:v>5295</x:v>
@@ -30018,7 +30018,7 @@
         <x:v>竞技压力与败北、运动伤痛、身体和内衣笑料、胸部相关笑话。</x:v>
       </x:c>
       <x:c r="O456" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P456" s="36" t="n">
         <x:v>5299</x:v>
@@ -30083,7 +30083,7 @@
         <x:v>成人向露骨性描写、双性体身体设定、秘密勒索、无视拒绝的性接触、把人作为收藏品或赌注、演艺行业权力胁迫与多人性暴力、经理／艺人与支配／服从关系中的权力不对等。</x:v>
       </x:c>
       <x:c r="O457" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P457" s="36" t="n">
         <x:v>5324</x:v>
@@ -30095,7 +30095,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S457" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T457" s="33" t="n">
         <x:v>79</x:v>
@@ -30148,7 +30148,7 @@
         <x:v>舞台恐惧与惊恐反应、童年霸凌、学校停办与财务压力、丧亲、家庭对学业和返乡的压力、网络评价与竞赛挫败、过度训练和中暑风险。</x:v>
       </x:c>
       <x:c r="O458" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P458" s="36" t="n">
         <x:v>5332</x:v>
@@ -30213,7 +30213,7 @@
         <x:v>虚拟枪战与重复模拟死亡、现实自伤／自杀威胁、跟踪和束缚、亲密关系中的威胁与暴力、性化玩笑与亲密边界的模糊描写</x:v>
       </x:c>
       <x:c r="O459" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P459" s="36" t="n">
         <x:v>5335</x:v>
@@ -30278,7 +30278,7 @@
         <x:v>四段恋爱群像、触摸乳房的提及与拒绝性语气、男校师生关系语境、同居表姐与少年、青春期身体变化。</x:v>
       </x:c>
       <x:c r="O460" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P460" s="36" t="n">
         <x:v>5356</x:v>
@@ -30343,7 +30343,7 @@
         <x:v>空战、军用武器、人员伤亡、失忆、救援与同室安排</x:v>
       </x:c>
       <x:c r="O461" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P461" s="36" t="n">
         <x:v>5390</x:v>
@@ -30355,10 +30355,10 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S461" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T461" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U461" s="27" t="str">
         <x:v>无</x:v>
@@ -30408,7 +30408,7 @@
         <x:v>非自愿窥视与掀裙、以泄露秘密相要挟、未经预先协商的接吻与脱衣、公开身体暴露、性化流言、前任出轨、社交孤立、自我否定与激烈争吵。</x:v>
       </x:c>
       <x:c r="O462" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P462" s="36" t="n">
         <x:v>5411</x:v>
@@ -30473,7 +30473,7 @@
         <x:v>夸张暴力与死亡、威胁、粗俗及性暗示笑料、声优贞洁传闻与“处女厨”话题。</x:v>
       </x:c>
       <x:c r="O463" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P463" s="36" t="n">
         <x:v>5426</x:v>
@@ -30538,7 +30538,7 @@
         <x:v>闹剧暴力、受伤与危险竞赛、未成年角色性化笑点、性别转换戏仿、露骨性用语与身体双关。</x:v>
       </x:c>
       <x:c r="O464" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P464" s="36" t="n">
         <x:v>5453</x:v>
@@ -30603,7 +30603,7 @@
         <x:v>男同学对女学生的性化妄想、校服与身体笑料、泳池／浴衣笑料、父母婚姻争吵及成人娱乐场所提及。</x:v>
       </x:c>
       <x:c r="O465" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P465" s="36" t="n">
         <x:v>5455</x:v>
@@ -30668,7 +30668,7 @@
         <x:v>拘捕、监视、双重间谍、身份伪装、政治压力、持械暴力与身体伤害；未作影片画面复核。</x:v>
       </x:c>
       <x:c r="O466" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P466" s="36" t="n">
         <x:v>5457</x:v>
@@ -30733,7 +30733,7 @@
         <x:v>摩托车道路风险、冰冷溪流落水与严寒暴露、未成年主角的无父母生活和经济压力</x:v>
       </x:c>
       <x:c r="O467" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P467" s="36" t="n">
         <x:v>5476</x:v>
@@ -30798,7 +30798,7 @@
         <x:v>心理创伤、社会孤立、友情破裂与失踪、枪炮刀刃伤害、死亡／自毁或自伤意象。</x:v>
       </x:c>
       <x:c r="O468" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P468" s="36" t="n">
         <x:v>5478</x:v>
@@ -30863,7 +30863,7 @@
         <x:v>奇幻袭击、音乐竞演、返乡与家庭压力、公开演出、水上活动。</x:v>
       </x:c>
       <x:c r="O469" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P469" s="36" t="n">
         <x:v>5484</x:v>
@@ -30928,7 +30928,7 @@
         <x:v>成人向色情内容、露骨性描写、群体性行为、女性与男性欲望并置、可能的非自愿接触；未作画面复核。</x:v>
       </x:c>
       <x:c r="O470" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P470" s="36" t="n">
         <x:v>5503</x:v>
@@ -30940,7 +30940,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S470" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T470" s="33" t="n">
         <x:v>60</x:v>
@@ -30993,7 +30993,7 @@
         <x:v>强制婚约与决斗所有权、校园霸凌与阶级歧视、企业胁迫、人体实验、父母操纵、政治暴力、战争与死亡、季末具冲击力的碾压死亡及关系创伤。</x:v>
       </x:c>
       <x:c r="O471" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P471" s="36" t="n">
         <x:v>5504</x:v>
@@ -31058,7 +31058,7 @@
         <x:v>泳装变身、窥视与身体笑料、吉祥物越界玩笑、幽灵及溺水危险。</x:v>
       </x:c>
       <x:c r="O472" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P472" s="36" t="n">
         <x:v>5505</x:v>
@@ -31123,7 +31123,7 @@
         <x:v>机甲战斗、城镇与平民危险、背叛和分离、童年溺水记忆</x:v>
       </x:c>
       <x:c r="O473" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P473" s="36" t="n">
         <x:v>5527</x:v>
@@ -31188,7 +31188,7 @@
         <x:v>异次元迷路、动作战斗、被捕风险、泳装及轻度性化笑料</x:v>
       </x:c>
       <x:c r="O474" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P474" s="36" t="n">
         <x:v>5568</x:v>
@@ -31253,7 +31253,7 @@
         <x:v>未成年人遭受超自然试炼与操控、心理困扰、进食困难、自我消失风险、成人与未成年人权力差、危险和受伤、涉及未成年人的变身与沐浴呈现。</x:v>
       </x:c>
       <x:c r="O475" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P475" s="36" t="n">
         <x:v>5606</x:v>
@@ -31318,7 +31318,7 @@
         <x:v>幻想战斗、伤残与创伤、角色死亡、歧视与政治暴力、家庭控制、异性吸引和追求。</x:v>
       </x:c>
       <x:c r="O476" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P476" s="36" t="n">
         <x:v>5621</x:v>
@@ -31330,13 +31330,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S476" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T476" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U476" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="477" ht="57" customHeight="1">
@@ -31383,7 +31383,7 @@
         <x:v>校园祭群像、恋足癖笑料、轻度裸露、男性配对同人本与其他性化笑料。</x:v>
       </x:c>
       <x:c r="O477" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P477" s="36" t="n">
         <x:v>5622</x:v>
@@ -31448,7 +31448,7 @@
         <x:v>极短篇生活喜剧、食物与季节活动、成员吐槽；不含 TV 版关系冲突。</x:v>
       </x:c>
       <x:c r="O478" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P478" s="36" t="n">
         <x:v>5627</x:v>
@@ -31513,7 +31513,7 @@
         <x:v>成人色情、亲姐弟乱伦、单向女女告白、嫉妒、边界与同意争议</x:v>
       </x:c>
       <x:c r="O479" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P479" s="36" t="n">
         <x:v>5630</x:v>
@@ -31578,7 +31578,7 @@
         <x:v>高中生角色的性暗示与身体笑料、越界式追求、木天蓼茶的边界模糊前提、疾病与照护</x:v>
       </x:c>
       <x:c r="O480" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P480" s="36" t="n">
         <x:v>5662</x:v>
@@ -31643,7 +31643,7 @@
         <x:v>成人向色情、裸露、附身、强奸／强迫、触手、群体性暴力、羞辱、以孩子生命胁迫母亲，以及结尾双方同意的女女性行为。</x:v>
       </x:c>
       <x:c r="O481" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P481" s="36" t="n">
         <x:v>5665</x:v>
@@ -31655,7 +31655,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S481" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T481" s="33" t="n">
         <x:v>79</x:v>
@@ -31708,7 +31708,7 @@
         <x:v>系统性歧视、战争与死亡、霸凌羞辱、性化台词、身体边界与权力不对等、强迫求婚、囚禁及暴力。</x:v>
       </x:c>
       <x:c r="O482" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P482" s="36" t="n">
         <x:v>5688</x:v>
@@ -31773,7 +31773,7 @@
         <x:v>成人恋爱与性话题笑料、相席联谊、饮酒与宿醉、澡堂裸露／搓背／按摩、超现实与元叙事</x:v>
       </x:c>
       <x:c r="O483" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P483" s="36" t="n">
         <x:v>5715</x:v>
@@ -31838,7 +31838,7 @@
         <x:v>成人向露骨性描写、囚禁、性暴力、强迫、群体性行为、扶她、触手、奴役、公开性行为和同意状态不明。</x:v>
       </x:c>
       <x:c r="O484" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P484" s="36" t="n">
         <x:v>5717</x:v>
@@ -31850,7 +31850,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S484" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T484" s="33" t="n">
         <x:v>75</x:v>
@@ -31903,7 +31903,7 @@
         <x:v>玩具机器人战斗、身体与内衣笑料、越界亲吻拟声、持续的性化骚扰与施虐式言谈、商品化身体语境、疾病照料与轻度恐怖笑料。</x:v>
       </x:c>
       <x:c r="O485" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P485" s="36" t="n">
         <x:v>5728</x:v>
@@ -31968,7 +31968,7 @@
         <x:v>姐妹分离、父母遗产、自然灾害、殖民历史与异性恋求婚</x:v>
       </x:c>
       <x:c r="O486" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P486" s="36" t="n">
         <x:v>5730</x:v>
@@ -31980,13 +31980,13 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S486" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T486" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U486" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="487" ht="57" customHeight="1">
@@ -32033,7 +32033,7 @@
         <x:v>奇幻暴力、死亡与失落、胁迫与失去自主、性化呈现、姐妹间单向恋爱与身体欲望、未获回应的追求和占有式语言</x:v>
       </x:c>
       <x:c r="O487" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P487" s="36" t="n">
         <x:v>5735</x:v>
@@ -32098,7 +32098,7 @@
         <x:v>迷你单元喜剧、轻度战斗训练、身体笑料、婚礼化与占有式玩笑。</x:v>
       </x:c>
       <x:c r="O488" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P488" s="36" t="n">
         <x:v>5740</x:v>
@@ -32163,7 +32163,7 @@
         <x:v>泳装、裸露、强制脱衣、胸部与性化身体笑料、巨大章鱼危机</x:v>
       </x:c>
       <x:c r="O489" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P489" s="36" t="n">
         <x:v>5752</x:v>
@@ -32228,7 +32228,7 @@
         <x:v>舞台竞演、夸张恶作剧、摔角式身体喜剧；与手游企划绑定但不纳入手游剧情。</x:v>
       </x:c>
       <x:c r="O490" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P490" s="36" t="n">
         <x:v>5762</x:v>
@@ -32293,7 +32293,7 @@
         <x:v>高压卡牌战斗、记忆丧失、人格／身体转换、绑架、操控、暴力、创伤关系及近亲恋爱欲望前史。</x:v>
       </x:c>
       <x:c r="O491" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P491" s="36" t="n">
         <x:v>5781</x:v>
@@ -32358,7 +32358,7 @@
         <x:v>公开羞辱与政治婚约解除；权力斗争与魔法战斗伤害；亲吻前未见明确口头确认（仅字幕语境）</x:v>
       </x:c>
       <x:c r="O492" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P492" s="36" t="n">
         <x:v>5782</x:v>
@@ -32423,7 +32423,7 @@
         <x:v>高原乡镇、父母经营的旅店、夜间骑行、海边出行、离别与同学音乐创作；字幕为社区英语译文，未核画面和日文原文。</x:v>
       </x:c>
       <x:c r="O493" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P493" s="36" t="n">
         <x:v>5803</x:v>
@@ -32488,7 +32488,7 @@
         <x:v>高空训练与失误风险、恐高与比赛压力、旧队友冲突、未成年学生计划向年长女性家庭教师告白。</x:v>
       </x:c>
       <x:c r="O494" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P494" s="36" t="n">
         <x:v>5809</x:v>
@@ -32553,7 +32553,7 @@
         <x:v>梦境、校园异变、成员疑似生病与短暂失联。</x:v>
       </x:c>
       <x:c r="O495" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P495" s="36" t="n">
         <x:v>5810</x:v>
@@ -32618,7 +32618,7 @@
         <x:v>性化身体竞技、泳装与成人玩笑、身体冲撞和受伤、嫉妒与竞争。</x:v>
       </x:c>
       <x:c r="O496" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P496" s="36" t="n">
         <x:v>5816</x:v>
@@ -32683,7 +32683,7 @@
         <x:v>全身义体、人工智能、恐怖袭击、机器人战斗、爆炸、性化笑料、机械身体相关台词与身体边界冒犯。</x:v>
       </x:c>
       <x:c r="O497" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P497" s="36" t="n">
         <x:v>5821</x:v>
@@ -32748,7 +32748,7 @@
         <x:v>战斗、绑架与威胁；女性床伴表述；性欲笑料；裸体共浴要求、裸露暗示和性化身体内容。</x:v>
       </x:c>
       <x:c r="O498" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P498" s="36" t="n">
         <x:v>5835</x:v>
@@ -32813,7 +32813,7 @@
         <x:v>未成年战斗与重伤、世界毁灭和亲人丧失、校园排挤、不登校，以及裸身／共同洗浴／身体话题；未复核视觉呈现。</x:v>
       </x:c>
       <x:c r="O499" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P499" s="36" t="n">
         <x:v>5850</x:v>
@@ -32878,7 +32878,7 @@
         <x:v>性别转换与身体重建、三角竞争、拒绝与分手、视觉障碍与心理危机、接吻及誓约语境、男性单向追求与性化凝视笑料。</x:v>
       </x:c>
       <x:c r="O500" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P500" s="36" t="n">
         <x:v>5867</x:v>
@@ -32943,7 +32943,7 @@
         <x:v>战争、空战、少女参战、负伤与死亡威胁、姐妹分离与照护责任、喜剧语境中的单向约会式提议。</x:v>
       </x:c>
       <x:c r="O501" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P501" s="36" t="n">
         <x:v>5874</x:v>
@@ -33008,7 +33008,7 @@
         <x:v>成人向性内容、体育仓库禁闭、同意边界不对等、兄妹间性欲望与家庭边界侵犯、重病与死亡、背叛、威胁、离别。</x:v>
       </x:c>
       <x:c r="O502" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P502" s="36" t="n">
         <x:v>5894</x:v>
@@ -33073,7 +33073,7 @@
         <x:v>泳装与身材笑料、偏服务性的喜剧呈现、舞台恐惧与社交焦虑</x:v>
       </x:c>
       <x:c r="O503" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P503" s="36" t="n">
         <x:v>5919</x:v>
@@ -33138,7 +33138,7 @@
         <x:v>泳装变身、未成年角色身体展示、性化笑料、身体边界冒犯、记忆操纵与过劳喜剧。</x:v>
       </x:c>
       <x:c r="O504" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P504" s="36" t="n">
         <x:v>5922</x:v>
@@ -33203,7 +33203,7 @@
         <x:v>跟随式追逐、反复邀约被拒、把拉面激情与亲密关系并置、同学和男性邀约笑料、双向恋爱未确认。</x:v>
       </x:c>
       <x:c r="O505" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P505" s="36" t="n">
         <x:v>5925</x:v>
@@ -33268,7 +33268,7 @@
         <x:v>舞台失误、同伴压力、家庭责任与现场演出竞争。</x:v>
       </x:c>
       <x:c r="O506" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P506" s="36" t="n">
         <x:v>5934</x:v>
@@ -33333,7 +33333,7 @@
         <x:v>摩托车风险、服务性展示、酒后越界言谈与师生权力差。</x:v>
       </x:c>
       <x:c r="O507" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P507" s="36" t="n">
         <x:v>5953</x:v>
@@ -33398,7 +33398,7 @@
         <x:v>架空战争、空战、军队命令、训练压力、事故、裸露、内衣式制服、洗浴、身体笑料、姐妹离别和受伤威胁。</x:v>
       </x:c>
       <x:c r="O508" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P508" s="36" t="n">
         <x:v>5967</x:v>
@@ -33463,7 +33463,7 @@
         <x:v>性别表达压力、家庭分离与重逢、照护冲突、告白后的拒绝与三角关系。</x:v>
       </x:c>
       <x:c r="O509" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P509" s="36" t="n">
         <x:v>5977</x:v>
@@ -33528,7 +33528,7 @@
         <x:v>成年女性对小学女孩的欲望与求婚、雇佣和照护权力差、反复越界与拒绝、丧亲、受虐倾向喜剧</x:v>
       </x:c>
       <x:c r="O510" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P510" s="36" t="n">
         <x:v>5979</x:v>
@@ -33593,7 +33593,7 @@
         <x:v>高频恶搞、卖肉、暴露、性暗示、身体笑料、单向追求、性别错认、学校战斗与绑架式闹剧</x:v>
       </x:c>
       <x:c r="O511" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P511" s="36" t="n">
         <x:v>6000</x:v>
@@ -33658,7 +33658,7 @@
         <x:v>校园谣言、嫉妒、照护与组织权力不对等、短暂男性交往及相亲喜剧。</x:v>
       </x:c>
       <x:c r="O512" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P512" s="36" t="n">
         <x:v>6026</x:v>
@@ -33723,7 +33723,7 @@
         <x:v>校园孤立与欺凌、嫉妒和关系控制、失踪、异世界战斗、枪炮刀刃伤害、自伤与死亡意象。</x:v>
       </x:c>
       <x:c r="O513" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P513" s="36" t="n">
         <x:v>6027</x:v>
@@ -33788,7 +33788,7 @@
         <x:v>偶像活动压力、宿舍拆除危机、对衣乃的过度追随、内衣与身体笑料、未成年角色性化喜剧、姐妹冲突与团队竞争。</x:v>
       </x:c>
       <x:c r="O514" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P514" s="36" t="n">
         <x:v>6067</x:v>
@@ -33853,7 +33853,7 @@
         <x:v>男学生的旁观、取向猜测与妄想；脸颊亲吻、膝枕及山本的带性意味措辞。</x:v>
       </x:c>
       <x:c r="O515" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P515" s="36" t="n">
         <x:v>6070</x:v>
@@ -33918,7 +33918,7 @@
         <x:v>魔法机甲战斗、少女受伤与淘汰、记忆／身份／存在操控、家族压力、嫉妒、牺牲与开放性结尾。</x:v>
       </x:c>
       <x:c r="O516" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P516" s="36" t="n">
         <x:v>6079</x:v>
@@ -33983,7 +33983,7 @@
         <x:v>武侠打斗与兵器、流血和重伤、阴谋与多方势力、伪装、囚禁风险、奇幻力量失控、离别与重逢压力、群像线注意力转移。</x:v>
       </x:c>
       <x:c r="O517" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P517" s="36" t="n">
         <x:v>6089</x:v>
@@ -34048,7 +34048,7 @@
         <x:v>比赛与训练压力、身高和自信问题、泳装与身体服务性画面、表姐妹之间的恋爱指向、搭档竞争与失败。</x:v>
       </x:c>
       <x:c r="O518" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P518" s="36" t="n">
         <x:v>6121</x:v>
@@ -34113,7 +34113,7 @@
         <x:v>贫困与低薪劳动、上下级权力差、战斗、性化笑点。</x:v>
       </x:c>
       <x:c r="O519" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P519" s="36" t="n">
         <x:v>6141</x:v>
@@ -34178,7 +34178,7 @@
         <x:v>突然接吻、灾难与失忆、非人 Doll、死亡、监视与剧团权力冲突。</x:v>
       </x:c>
       <x:c r="O520" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P520" s="36" t="n">
         <x:v>6142</x:v>
@@ -34243,7 +34243,7 @@
         <x:v>未成年角色泳装、裸露／露乳、走光、性化笑料、骚扰、强吻奖品与溺水险情。</x:v>
       </x:c>
       <x:c r="O521" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P521" s="36" t="n">
         <x:v>6146</x:v>
@@ -34308,7 +34308,7 @@
         <x:v>单向恋爱、嫉妒、关系破裂、校园排斥、角色扮演与现实边界、共同体内的冲突。</x:v>
       </x:c>
       <x:c r="O522" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P522" s="36" t="n">
         <x:v>6211</x:v>
@@ -34373,7 +34373,7 @@
         <x:v>竞赛与练习压力、严厉争执、能力差距与自我怀疑、姐妹比较压力、高强度舞台演出与较长音乐段落。</x:v>
       </x:c>
       <x:c r="O523" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P523" s="36" t="n">
         <x:v>6218</x:v>
@@ -34438,7 +34438,7 @@
         <x:v>吸血、献血、失血、身体改造、带性意味的吸血喜剧、身体边界笑点、催眠、成人研究权力、追捕暴力和家族强加婚约。</x:v>
       </x:c>
       <x:c r="O524" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P524" s="36" t="n">
         <x:v>6227</x:v>
@@ -34503,7 +34503,7 @@
         <x:v>极短篇、社交困难、拟人猫、校园竞争、怕猫、祭典走散与重逢。</x:v>
       </x:c>
       <x:c r="O525" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P525" s="36" t="n">
         <x:v>6270</x:v>
@@ -34568,7 +34568,7 @@
         <x:v>医疗与治疗失败焦虑、考试压力、师生权力差异、短暂分离</x:v>
       </x:c>
       <x:c r="O526" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P526" s="36" t="n">
         <x:v>6311</x:v>
@@ -34633,7 +34633,7 @@
         <x:v>平行世界灾难与战斗、哥哥失踪和创伤、强制婚约、泳装／内衣与身体发育笑料、TV与手机游戏的版本边界。</x:v>
       </x:c>
       <x:c r="O527" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P527" s="36" t="n">
         <x:v>6354</x:v>
@@ -34698,7 +34698,7 @@
         <x:v>灵异、死亡与告别、亲人离世、校园喜剧</x:v>
       </x:c>
       <x:c r="O528" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P528" s="36" t="n">
         <x:v>6400</x:v>
@@ -34763,7 +34763,7 @@
         <x:v>间谍行动与暴力、药物控制、绑架和人口贩卖背景、假背叛、死亡误导、记忆消除、师徒分离</x:v>
       </x:c>
       <x:c r="O529" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P529" s="36" t="n">
         <x:v>6416</x:v>
@@ -34828,7 +34828,7 @@
         <x:v>成人向裸露与身体性化、战斗伤害、监禁和魔法支配、性骚扰与带情色意味的强迫接触、姐妹关系中的单向性化欲望与控制行为</x:v>
       </x:c>
       <x:c r="O530" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P530" s="36" t="n">
         <x:v>6417</x:v>
@@ -34893,7 +34893,7 @@
         <x:v>试镜与职业压力、成员竞争、家庭期待、被拒绝的异性婚约安排、离开与留学。</x:v>
       </x:c>
       <x:c r="O531" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P531" s="36" t="n">
         <x:v>6484</x:v>
@@ -34958,7 +34958,7 @@
         <x:v>逆后宫、婚约与多人告白、绑架和非法拘禁、黑暗魔法、家庭创伤、嫉妒与占有式玩笑。</x:v>
       </x:c>
       <x:c r="O532" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P532" s="36" t="n">
         <x:v>6510</x:v>
@@ -35023,7 +35023,7 @@
         <x:v>社交焦虑、不登校压力、竞赛失败、团队冲突、家庭回忆与外星能力设定。</x:v>
       </x:c>
       <x:c r="O533" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P533" s="36" t="n">
         <x:v>6547</x:v>
@@ -35088,7 +35088,7 @@
         <x:v>枪战与恐怖袭击、秘密组织利用未成年少女、濒死与人工心脏、绑架和人质、家庭式操控、杀人与拒绝杀人的伦理冲突、角色间肢体打斗。</x:v>
       </x:c>
       <x:c r="O534" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P534" s="36" t="n">
         <x:v>6608</x:v>
@@ -35153,7 +35153,7 @@
         <x:v>现实职场过劳、异世界战斗、爆炸与追杀、角色数据覆盖和人格消失风险、精神世界侵入、师徒／教学关系及年龄与经验差异。</x:v>
       </x:c>
       <x:c r="O535" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P535" s="36" t="n">
         <x:v>6640</x:v>
@@ -35218,7 +35218,7 @@
         <x:v>战斗、杀戮游戏、血迹、死亡威胁、报复、控制性相伴表达与女性角色性化设计。</x:v>
       </x:c>
       <x:c r="O536" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P536" s="36" t="n">
         <x:v>6651</x:v>
@@ -35283,7 +35283,7 @@
         <x:v>未事先询问或伴随挣扎声的接吻、许可不明、停止要求、师生权力利用、工具性婚约、照片胁迫、陌生成年人风险、继姐妹恋爱。</x:v>
       </x:c>
       <x:c r="O537" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P537" s="36" t="n">
         <x:v>6669</x:v>
@@ -35348,7 +35348,7 @@
         <x:v>异世界战斗、亲子式照料、家庭成员加入，以及对亲吻和交往的喜剧化玩笑。</x:v>
       </x:c>
       <x:c r="O538" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P538" s="36" t="n">
         <x:v>6673</x:v>
@@ -35413,7 +35413,7 @@
         <x:v>姐妹分离与操控、黑暗力量附身、战斗和牺牲威胁、异性分手与复合。</x:v>
       </x:c>
       <x:c r="O539" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P539" s="36" t="n">
         <x:v>6687</x:v>
@@ -35478,7 +35478,7 @@
         <x:v>成人向裸露与持续性化、战斗伤害、囚禁、药物或诅咒控制、奴役训练、强迫接触、羞辱性支配、复仇与死亡威胁。</x:v>
       </x:c>
       <x:c r="O540" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P540" s="36" t="n">
         <x:v>6689</x:v>
@@ -35543,7 +35543,7 @@
         <x:v>政变、护卫遇害、战斗暴力、坠崖、身体／灵魂交换与身份错位。</x:v>
       </x:c>
       <x:c r="O541" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P541" s="36" t="n">
         <x:v>6728</x:v>
@@ -35608,7 +35608,7 @@
         <x:v>创作压力、比赛失落、亡母记忆与家庭传承。</x:v>
       </x:c>
       <x:c r="O542" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P542" s="36" t="n">
         <x:v>6765</x:v>
@@ -35673,7 +35673,7 @@
         <x:v>18+ 露骨性描写、鬼魂、身体变化、触手、可能的强制接触与同意状态不明。</x:v>
       </x:c>
       <x:c r="O543" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P543" s="36" t="n">
         <x:v>6773</x:v>
@@ -35685,7 +35685,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S543" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T543" s="33" t="n">
         <x:v>92</x:v>
@@ -35738,7 +35738,7 @@
         <x:v>社交退缩与孤独、校园排斥、温泉与泳装情境、亲子沟通压力、比赛与公开活动的紧张感、局部单向好感</x:v>
       </x:c>
       <x:c r="O544" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P544" s="36" t="n">
         <x:v>6786</x:v>
@@ -35803,7 +35803,7 @@
         <x:v>幻想战斗、死亡与重伤、歧视和政治暴力、胁迫与背叛、跟踪及暴力威胁、父母抛弃、婚姻利用与家庭创伤。</x:v>
       </x:c>
       <x:c r="O545" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P545" s="36" t="n">
         <x:v>6902</x:v>
@@ -35815,13 +35815,13 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="S545" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T545" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U545" s="27" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="546" ht="57" customHeight="1">
@@ -35868,7 +35868,7 @@
         <x:v>刀剑伤害、死亡与牺牲、强迫控制、家族创伤、失踪与分离</x:v>
       </x:c>
       <x:c r="O546" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P546" s="36" t="n">
         <x:v>6909</x:v>
@@ -35933,7 +35933,7 @@
         <x:v>记忆硬币与高压卡牌战斗、失忆和人格／身体置换、校园孤立与家庭经济压力、操控和强迫参战、铃子—千夏的依赖与决裂、少女角色的暴力和死亡风险、白井对千夏的单向倾慕。</x:v>
       </x:c>
       <x:c r="O547" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P547" s="36" t="n">
         <x:v>6943</x:v>
@@ -35998,7 +35998,7 @@
         <x:v>偶像行业压力与竞争、歌声被夺与身体控制、舞台与案件危险、团队争执、亲人离世回忆、第 8 话局部异性求婚线。</x:v>
       </x:c>
       <x:c r="O548" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P548" s="36" t="n">
         <x:v>6955</x:v>
@@ -36063,7 +36063,7 @@
         <x:v>师徒权力差与破门惩戒、职业竞争与经济压力、绑架／诬陷／勒索威胁、舞台压力，以及落语段子的成人关系或花街语境。</x:v>
       </x:c>
       <x:c r="O549" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P549" s="36" t="n">
         <x:v>6958</x:v>
@@ -36128,7 +36128,7 @@
         <x:v>成人向性化、暴力、绑架、精神操控与羞辱性战败</x:v>
       </x:c>
       <x:c r="O550" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P550" s="36" t="n">
         <x:v>6985</x:v>
@@ -36193,7 +36193,7 @@
         <x:v>儿童与青少年格斗、训练伤害、成人化变身与身体展示、洗澡镜头、家庭创伤和古代记忆。</x:v>
       </x:c>
       <x:c r="O551" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P551" s="36" t="n">
         <x:v>6992</x:v>
@@ -36258,7 +36258,7 @@
         <x:v>饲主与店铺劳动关系、双胞胎性化幻想、兄妹越界欲望笑料、其他性化笑料、走失幼猫与轻度危险。</x:v>
       </x:c>
       <x:c r="O552" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P552" s="36" t="n">
         <x:v>6998</x:v>
@@ -36323,7 +36323,7 @@
         <x:v>成年人饮酒与醉酒、身体与更衣笑料、职场与求职压力、合租生活的隐私边界喜剧。</x:v>
       </x:c>
       <x:c r="O553" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P553" s="36" t="n">
         <x:v>7031</x:v>
@@ -36388,7 +36388,7 @@
         <x:v>超自然威胁、附身、战斗与受伤、家庭分离和丧失。</x:v>
       </x:c>
       <x:c r="O554" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P554" s="36" t="n">
         <x:v>7044</x:v>
@@ -36453,7 +36453,7 @@
         <x:v>成人向裸露、爆衣与战败羞辱、格斗伤害和死亡威胁、绑架拷问、人质处境、精神操控、非自愿战斗、占有式执着与权力不对等。</x:v>
       </x:c>
       <x:c r="O555" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P555" s="36" t="n">
         <x:v>7050</x:v>
@@ -36518,7 +36518,7 @@
         <x:v>性别转换、性化身体喜剧、妖怪袭击与战斗、未确立交往。</x:v>
       </x:c>
       <x:c r="O556" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P556" s="36" t="n">
         <x:v>7066</x:v>
@@ -36583,7 +36583,7 @@
         <x:v>成人向裸露与衣物撕裂、格斗伤害、绑架与失踪、幻术和精神操控、非自愿行动、战败羞辱与权力不对等。</x:v>
       </x:c>
       <x:c r="O557" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P557" s="36" t="n">
         <x:v>7098</x:v>
@@ -36648,7 +36648,7 @@
         <x:v>VRMMO 战斗、怪物攻击、毒与身体变形喜剧、公会竞争、短暂危险与失败。</x:v>
       </x:c>
       <x:c r="O558" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P558" s="36" t="n">
         <x:v>7113</x:v>
@@ -36713,7 +36713,7 @@
         <x:v>五分钟短篇喜剧、角色遭排斥的回忆、料理失败与夸张身体笑料。</x:v>
       </x:c>
       <x:c r="O559" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P559" s="36" t="n">
         <x:v>7120</x:v>
@@ -36778,7 +36778,7 @@
         <x:v>激烈乐队争执、粗口和攻击性手势、家庭再婚与阶层压力、继姐妹敌意、舞台竞争、失败与退队威胁、夸张支配／服从玩笑、性化镜头与性骚扰情节。</x:v>
       </x:c>
       <x:c r="O560" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P560" s="36" t="n">
         <x:v>7135</x:v>
@@ -36843,7 +36843,7 @@
         <x:v>高速荒诞、夸张伤害与死亡笑料、身体变化、排泄与性化笑话、威胁和强制性恶作剧。</x:v>
       </x:c>
       <x:c r="O561" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P561" s="36" t="n">
         <x:v>7172</x:v>
@@ -36908,7 +36908,7 @@
         <x:v>持续暗杀与死亡威胁、刀枪和爆炸、流血及重伤、被迫参加生存游戏、家庭死亡与创伤、制度操纵、童年虐待和利用、自我牺牲式行动、假死及依赖巧合的生还揭晓。</x:v>
       </x:c>
       <x:c r="O562" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P562" s="36" t="n">
         <x:v>7175</x:v>
@@ -36973,7 +36973,7 @@
         <x:v>科幻战斗、死亡威胁、记忆植入、洗脑、身体实验、泳装与内衣服务性画面、强迫亲密和关系认知胁迫。</x:v>
       </x:c>
       <x:c r="O563" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P563" s="36" t="n">
         <x:v>7195</x:v>
@@ -37038,7 +37038,7 @@
         <x:v>未成年角色格斗伤害、校园欺凌、孤儿与收养经历、魔法变身和身体展示。</x:v>
       </x:c>
       <x:c r="O564" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P564" s="36" t="n">
         <x:v>7270</x:v>
@@ -37103,7 +37103,7 @@
         <x:v>全员女性历史幻想、R+／Ecchi 性化笑料、裸露暗示、曹操提出共度一夜的权力交换、盗贼与绑架、战斗和男性冒名者诱导。</x:v>
       </x:c>
       <x:c r="O565" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P565" s="36" t="n">
         <x:v>7276</x:v>
@@ -37168,7 +37168,7 @@
         <x:v>竞技射击与枪械意象、比赛压力与失利、社团争执、喜剧式求婚和恋爱话题</x:v>
       </x:c>
       <x:c r="O566" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P566" s="36" t="n">
         <x:v>7285</x:v>
@@ -37233,7 +37233,7 @@
         <x:v>成人向裸露与性化、战斗伤害、宗教审判、拘禁与越界接近、强制招募与实验、怪物威胁。</x:v>
       </x:c>
       <x:c r="O567" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P567" s="36" t="n">
         <x:v>7299</x:v>
@@ -37298,7 +37298,7 @@
         <x:v>战争与空战、年轻女武神参战、负伤与死亡、亲人哀伤、神祇操纵、泳装战斗和身体凝视。</x:v>
       </x:c>
       <x:c r="O568" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P568" s="36" t="n">
         <x:v>7304</x:v>
@@ -37363,7 +37363,7 @@
         <x:v>高速吐槽、胸部与内衣笑料、如厕和身体尴尬、闻头发、间接接吻及强行亲近的喜剧。</x:v>
       </x:c>
       <x:c r="O569" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P569" s="36" t="n">
         <x:v>7322</x:v>
@@ -37428,7 +37428,7 @@
         <x:v>战争与沉没、死亡循环、身份变化、失落和告别、深海化、强烈分离焦虑。</x:v>
       </x:c>
       <x:c r="O570" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P570" s="36" t="n">
         <x:v>7326</x:v>
@@ -37493,7 +37493,7 @@
         <x:v>自行车训练、比赛压力、体力极限、肩部疼痛、夜间骑行与离别误会。</x:v>
       </x:c>
       <x:c r="O571" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P571" s="36" t="n">
         <x:v>7354</x:v>
@@ -37558,7 +37558,7 @@
         <x:v>高速短篇、网球竞争、毕业与分离焦虑、饮酒及荒诞身体笑料；未作视频复核。</x:v>
       </x:c>
       <x:c r="O572" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P572" s="36" t="n">
         <x:v>7362</x:v>
@@ -37623,7 +37623,7 @@
         <x:v>反复追求与阶级差异；以戏剧化方式处理拒绝、占有和跟随；魔法战斗、校园霸凌、政治冲突、家族与国家暴力。</x:v>
       </x:c>
       <x:c r="O573" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P573" s="36" t="n">
         <x:v>7376</x:v>
@@ -37688,7 +37688,7 @@
         <x:v>强行脱衣与内衣、裸露和身体羞辱、性化恶作剧、教师越界亲吻、未成年角色误饮酒、受影响状态下的接吻提议。</x:v>
       </x:c>
       <x:c r="O574" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P574" s="36" t="n">
         <x:v>7415</x:v>
@@ -37753,7 +37753,7 @@
         <x:v>创作受挫、旅行疲劳、朋友争执与和解。</x:v>
       </x:c>
       <x:c r="O575" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P575" s="36" t="n">
         <x:v>7427</x:v>
@@ -37818,7 +37818,7 @@
         <x:v>机战伤亡与破坏、背叛与团队分裂、强制实验和改造、权力不对等、人与有意识机器的明确恋爱。</x:v>
       </x:c>
       <x:c r="O576" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P576" s="36" t="n">
         <x:v>7434</x:v>
@@ -37883,7 +37883,7 @@
         <x:v>毕业与成员分离压力、竞赛与舞台失败、异国旅行、家庭冲突、姐妹关系破裂与修复、过度训练和公开演出压力。</x:v>
       </x:c>
       <x:c r="O577" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P577" s="36" t="n">
         <x:v>7493</x:v>
@@ -37948,7 +37948,7 @@
         <x:v>魔法军事战斗、未成年角色参战、模拟射击、内衣式服装设计。</x:v>
       </x:c>
       <x:c r="O578" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P578" s="36" t="n">
         <x:v>7501</x:v>
@@ -38013,7 +38013,7 @@
         <x:v>选拔淘汰与舞台压力、亲人离世与心脏移植背景、竞争冲突、团队去留与公开表演焦虑</x:v>
       </x:c>
       <x:c r="O579" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P579" s="36" t="n">
         <x:v>7535</x:v>
@@ -38078,7 +38078,7 @@
         <x:v>短篇职场喜剧、写真与泳装、身体展示和裸照笑料、赶稿压力、漫画中的恋爱与成人题材玩笑。</x:v>
       </x:c>
       <x:c r="O580" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P580" s="36" t="n">
         <x:v>7539</x:v>
@@ -38143,7 +38143,7 @@
         <x:v>校园战斗、超自然威胁、受伤与精神控制、女子宿舍性化笑料、嫉妒与搭档选择压力、局部异性心动</x:v>
       </x:c>
       <x:c r="O581" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P581" s="36" t="n">
         <x:v>7542</x:v>
@@ -38208,7 +38208,7 @@
         <x:v>计划处刑与欺骗、反复死亡、暴力威胁、权力不对等、嫉妒与浴场相关台词。</x:v>
       </x:c>
       <x:c r="O582" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P582" s="36" t="n">
         <x:v>7543</x:v>
@@ -38273,7 +38273,7 @@
         <x:v>卖肉与内衣／泳装情境、女高中生同住和宿舍劳动、身份误会与内疚、游戏与网络直播、家庭与学校压力；不涉及正篇确认交往</x:v>
       </x:c>
       <x:c r="O583" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P583" s="36" t="n">
         <x:v>7549</x:v>
@@ -38338,7 +38338,7 @@
         <x:v>裸露、爆衣、战败羞辱、格斗伤害、拷问、角色死亡、追随死亡意向、精神控制与命运强迫。</x:v>
       </x:c>
       <x:c r="O584" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P584" s="36" t="n">
         <x:v>7614</x:v>
@@ -38403,7 +38403,7 @@
         <x:v>未成年战斗员与军事化教育、怪物袭击和战斗伤害、重要人物死亡与长期哀恸、失控及误伤恐惧、人工生命被实验和非人化、追捕与拘禁威胁、儿童形象角色死亡、精神幻象与自我憎恨、身体化笑料和集体沐浴画面。</x:v>
       </x:c>
       <x:c r="O585" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P585" s="36" t="n">
         <x:v>7628</x:v>
@@ -38468,7 +38468,7 @@
         <x:v>超短篇战斗喜剧、夸张暴力、身体暴露、性暗示、饮酒笑料、男の娘与性别表现的喜剧化处理</x:v>
       </x:c>
       <x:c r="O586" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P586" s="36" t="n">
         <x:v>7648</x:v>
@@ -38533,7 +38533,7 @@
         <x:v>成人向裸露与性化接触、以性刺激触发战斗、监禁与强迫风险、身体控制、创伤、暴力和权力不对等</x:v>
       </x:c>
       <x:c r="O587" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P587" s="36" t="n">
         <x:v>7657</x:v>
@@ -38598,7 +38598,7 @@
         <x:v>高中生主角、裸露与性化笑料、持续拒绝、边界不对称、支配与胁迫场景</x:v>
       </x:c>
       <x:c r="O588" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P588" s="36" t="n">
         <x:v>7668</x:v>
@@ -38663,7 +38663,7 @@
         <x:v>病毒清除、失忆、虚拟世界消失、身份揭示、分离与牺牲。</x:v>
       </x:c>
       <x:c r="O589" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P589" s="36" t="n">
         <x:v>7673</x:v>
@@ -38728,7 +38728,7 @@
         <x:v>夸张的美少女求偶笑料、表亲单向追求、异能对战、受伤、背叛创伤与学园危机</x:v>
       </x:c>
       <x:c r="O590" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P590" s="36" t="n">
         <x:v>7687</x:v>
@@ -38793,7 +38793,7 @@
         <x:v>战争与创伤、恐怖袭击、枪械与杀戮、酷刑和肢解、性暴力威胁、儿童虐待、校园欺凌、药物与强迫、残酷的战后动员；漫画后续不在范围内</x:v>
       </x:c>
       <x:c r="O591" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P591" s="36" t="n">
         <x:v>7706</x:v>
@@ -38858,7 +38858,7 @@
         <x:v>三分钟短篇节奏、身体和服装笑料、竞争性玩笑、未成年人角色的泳池与睡衣场景。</x:v>
       </x:c>
       <x:c r="O592" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P592" s="36" t="n">
         <x:v>7714</x:v>
@@ -38923,7 +38923,7 @@
         <x:v>成人向性化、乳房／圣乳机制、主从与身体控制、霸凌、非自愿或同意不明的亲密处境、未成年角色性化、暴力、死亡及宗教冲突。</x:v>
       </x:c>
       <x:c r="O593" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P593" s="36" t="n">
         <x:v>7772</x:v>
@@ -38988,7 +38988,7 @@
         <x:v>末世灾变与可能的人类灭绝、危险骑行、枪械、AI 损坏、死亡记忆与亲人离散</x:v>
       </x:c>
       <x:c r="O594" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P594" s="36" t="n">
         <x:v>7795</x:v>
@@ -39053,7 +39053,7 @@
         <x:v>异世界战斗、魔族与精灵危机、轻度身体变形和喜剧化危险、母女与姐妹关系、象征性姐妹婚礼，以及佩可拉希望与亚梓莎单独庆生的安排。</x:v>
       </x:c>
       <x:c r="O595" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P595" s="36" t="n">
         <x:v>7796</x:v>
@@ -39118,7 +39118,7 @@
         <x:v>魔物袭击、战斗伤害、死亡与消失、家庭创伤、精神操纵、恶魔化和未成年人承担处刑任务。</x:v>
       </x:c>
       <x:c r="O596" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P596" s="36" t="n">
         <x:v>7799</x:v>
@@ -39183,7 +39183,7 @@
         <x:v>无对白叙事、对未成年女高中生腿部与湿衣的性化笑料、男性角色的单集凝视与笨拙接近、轻微身体危险与日常恶作剧。</x:v>
       </x:c>
       <x:c r="O597" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P597" s="36" t="n">
         <x:v>7836</x:v>
@@ -39248,7 +39248,7 @@
         <x:v>魔法战斗与受伤、时间错位、未成年人遇险、泳装与身体笑料、同居家庭喜剧。</x:v>
       </x:c>
       <x:c r="O598" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P598" s="36" t="n">
         <x:v>7841</x:v>
@@ -39313,7 +39313,7 @@
         <x:v>落水、弄湿制服与风筝惊吓等轻度事故笑点；留宿、共同洗澡、互相洗背和换衣的暧昧／窥探式喜剧；每话篇幅很短。</x:v>
       </x:c>
       <x:c r="O599" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P599" s="36" t="n">
         <x:v>7865</x:v>
@@ -39378,7 +39378,7 @@
         <x:v>超能力战斗、绑架、药物强化、能力实验、家庭排斥、自我消失愿望、失去身体与姐妹失联恐惧、身体检查相关性化玩笑。</x:v>
       </x:c>
       <x:c r="O600" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P600" s="36" t="n">
         <x:v>7869</x:v>
@@ -39443,7 +39443,7 @@
         <x:v>偶像过劳与身体展示压力、家庭创伤、病弱与死亡、幸存者负罪感、解散、监视和制度控制。</x:v>
       </x:c>
       <x:c r="O601" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P601" s="36" t="n">
         <x:v>7913</x:v>
@@ -39508,7 +39508,7 @@
         <x:v>都市传说怪物、枪械与军事行动、失踪与死亡威胁、身体恐怖、心理创伤和危险求生</x:v>
       </x:c>
       <x:c r="O602" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P602" s="36" t="n">
         <x:v>7925</x:v>
@@ -39573,7 +39573,7 @@
         <x:v>刀剑战斗、荒魂追捕与受伤、医疗休养、敌我身份冲突和阶段性悬念。</x:v>
       </x:c>
       <x:c r="O603" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P603" s="36" t="n">
         <x:v>7929</x:v>
@@ -39638,7 +39638,7 @@
         <x:v>运动伤病、竞技压力、身体展示、尖锐竞争语言。</x:v>
       </x:c>
       <x:c r="O604" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P604" s="36" t="n">
         <x:v>8016</x:v>
@@ -39703,7 +39703,7 @@
         <x:v>裸露、性化玩笑、非合意触摸、姐妹间性化表达、暴力与创伤</x:v>
       </x:c>
       <x:c r="O605" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P605" s="36" t="n">
         <x:v>8019</x:v>
@@ -39768,7 +39768,7 @@
         <x:v>未成年角色参与幻想战斗、主人—Doll 权力不对等、人工人格与记忆控制、被遗弃经历、服务性服装与性化喜剧。</x:v>
       </x:c>
       <x:c r="O606" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P606" s="36" t="n">
         <x:v>8055</x:v>
@@ -39833,7 +39833,7 @@
         <x:v>魔法战斗、死亡与失踪风险、悲伤与内疚、梦境和记忆操控、组织控制、强制招募、身份消除、创伤与牺牲。</x:v>
       </x:c>
       <x:c r="O607" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P607" s="36" t="n">
         <x:v>8062</x:v>
@@ -39898,7 +39898,7 @@
         <x:v>运动失败、身体疲劳、新手自我怀疑、户外高尔夫与短篇篇幅限制。</x:v>
       </x:c>
       <x:c r="O608" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P608" s="36" t="n">
         <x:v>8074</x:v>
@@ -39963,7 +39963,7 @@
         <x:v>运动压力、停部经历、触身球及其他棒球伤害、战术责任和比赛失利。</x:v>
       </x:c>
       <x:c r="O609" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P609" s="36" t="n">
         <x:v>8092</x:v>
@@ -40028,7 +40028,7 @@
         <x:v>异世界战斗、失踪儿童与救援、泳装／洗澡等服务性内容、男性婚约压力。</x:v>
       </x:c>
       <x:c r="O610" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P610" s="36" t="n">
         <x:v>8141</x:v>
@@ -40093,7 +40093,7 @@
         <x:v>亡母记忆、陶艺比赛与创作压力；第 1 话含恋爱双关但随后指向陶艺部；真人外景部分不在范围。</x:v>
       </x:c>
       <x:c r="O611" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P611" s="36" t="n">
         <x:v>8192</x:v>
@@ -40158,7 +40158,7 @@
         <x:v>战争、枪击、吸血、身体变异、主要角色死亡、追捕、牺牲、悲剧性告别，以及年龄与权力差异</x:v>
       </x:c>
       <x:c r="O612" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P612" s="36" t="n">
         <x:v>8206</x:v>
@@ -40223,7 +40223,7 @@
         <x:v>末世、战争、身体恐怖、性化与强迫性情节、生殖实验、死亡和牺牲。</x:v>
       </x:c>
       <x:c r="O613" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P613" s="36" t="n">
         <x:v>8215</x:v>
@@ -40288,7 +40288,7 @@
         <x:v>竞技受伤、比赛与舞台压力、家庭与经济困难、过劳和失利后的情绪低落</x:v>
       </x:c>
       <x:c r="O614" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P614" s="36" t="n">
         <x:v>8233</x:v>
@@ -40353,7 +40353,7 @@
         <x:v>一名角色未经许可查看另一名角色的电脑内容，并反复贴近、催促；对方明确要求停止；怯场、公开演出压力与短期离别冲突。</x:v>
       </x:c>
       <x:c r="O615" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P615" s="36" t="n">
         <x:v>8263</x:v>
@@ -40418,7 +40418,7 @@
         <x:v>训练与比赛压力、运动受伤风险、队内责任、失败和自我怀疑。</x:v>
       </x:c>
       <x:c r="O616" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P616" s="36" t="n">
         <x:v>8272</x:v>
@@ -40483,7 +40483,7 @@
         <x:v>末世喜剧、反复谋杀企图、身体攻击、惩罚、强制性同居、权力不对等与地方宣传。</x:v>
       </x:c>
       <x:c r="O617" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P617" s="36" t="n">
         <x:v>8313</x:v>
@@ -40548,7 +40548,7 @@
         <x:v>生存游戏枪械、比赛受伤、团队冲突、心理失衡、泳装与洗浴等服务性演出</x:v>
       </x:c>
       <x:c r="O618" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P618" s="36" t="n">
         <x:v>8341</x:v>
@@ -40613,7 +40613,7 @@
         <x:v>成人性内容、裸露、买主与成人用机器人之间的所有权框架、身体接触；第 1–8 话完成字幕文本复核，未回看视频。</x:v>
       </x:c>
       <x:c r="O619" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P619" s="36" t="n">
         <x:v>8377</x:v>
@@ -40678,7 +40678,7 @@
         <x:v>死亡游戏、血腥暴力、未成年人受害、背叛与操控、自杀、家庭暴力、怀孕角色死亡。</x:v>
       </x:c>
       <x:c r="O620" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P620" s="36" t="n">
         <x:v>8379</x:v>
@@ -40743,7 +40743,7 @@
         <x:v>枪械战斗、校园训练、身体检查与泳池服务性笑料、占有欲和竞争、战姊妹制度的前后辈权力差、男性角色的局部恋爱玩笑。</x:v>
       </x:c>
       <x:c r="O621" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P621" s="36" t="n">
         <x:v>8403</x:v>
@@ -40808,7 +40808,7 @@
         <x:v>飞行运动的坠落与受伤风险、竞技压力、比赛服与泳装展示、改编压缩造成的角色背景跳跃。</x:v>
       </x:c>
       <x:c r="O622" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P622" s="36" t="n">
         <x:v>8441</x:v>
@@ -40873,7 +40873,7 @@
         <x:v>家长控制与搬家压力、未成年角色参与危险逃避行动、移民拘留风险、网络曝光与中伤、关系秘密被公开、男性单恋与女女告白。</x:v>
       </x:c>
       <x:c r="O623" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P623" s="36" t="n">
         <x:v>8464</x:v>
@@ -40938,7 +40938,7 @@
         <x:v>高度性化服务、衣物破坏与战斗暴露、胸部触碰笑料、暴力与死亡威胁、操控／药物／人偶化暗示</x:v>
       </x:c>
       <x:c r="O624" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P624" s="36" t="n">
         <x:v>8476</x:v>
@@ -41003,7 +41003,7 @@
         <x:v>战斗、权力争夺、操纵、背叛、性化笑料、梦境与剧中剧边界</x:v>
       </x:c>
       <x:c r="O625" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P625" s="36" t="n">
         <x:v>8488</x:v>
@@ -41068,7 +41068,7 @@
         <x:v>男性化变身、性别表现混淆、偶像压力、绑架威胁、魔法战斗与身体笑料。</x:v>
       </x:c>
       <x:c r="O626" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P626" s="36" t="n">
         <x:v>8506</x:v>
@@ -41133,7 +41133,7 @@
         <x:v>围绕男性主角的后宫式竞争与性暗示；魔法战斗、控制、身体伤害与姐妹冲突。</x:v>
       </x:c>
       <x:c r="O627" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P627" s="36" t="n">
         <x:v>8514</x:v>
@@ -41198,7 +41198,7 @@
         <x:v>VRMMO 战斗、怪物与触手、变身和吞食式喜剧、竞技冲突、团队分散与危险任务。</x:v>
       </x:c>
       <x:c r="O628" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P628" s="36" t="n">
         <x:v>8557</x:v>
@@ -41263,7 +41263,7 @@
         <x:v>校园日常、社团与比赛、泳装及身体笑料、英语恋爱措辞与摄影语境并置。</x:v>
       </x:c>
       <x:c r="O629" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P629" s="36" t="n">
         <x:v>8569</x:v>
@@ -41328,7 +41328,7 @@
         <x:v>精神痛苦、情绪操纵、姐妹分离、失去与哀恸、战斗伤害。</x:v>
       </x:c>
       <x:c r="O630" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P630" s="36" t="n">
         <x:v>8574</x:v>
@@ -41393,7 +41393,7 @@
         <x:v>儿童向战斗、异世界危机、绑架与救援、家庭分离、身份与责任压力、部分服务性演出。</x:v>
       </x:c>
       <x:c r="O631" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P631" s="36" t="n">
         <x:v>8603</x:v>
@@ -41458,7 +41458,7 @@
         <x:v>社团冲突、沟通障碍、舞台压力、成员去留、能力差异和自卑。</x:v>
       </x:c>
       <x:c r="O632" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P632" s="36" t="n">
         <x:v>8618</x:v>
@@ -41523,7 +41523,7 @@
         <x:v>继兄妹恋爱语境、幽灵附身与共用身体、非对等身体边界、性化台词与装置。</x:v>
       </x:c>
       <x:c r="O633" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P633" s="36" t="n">
         <x:v>8623</x:v>
@@ -41588,7 +41588,7 @@
         <x:v>未成年角色内衣、身体凝视、偷窥／偷拍笑料、接触边界、体型评论、青春期羞耻与身体羞辱</x:v>
       </x:c>
       <x:c r="O634" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P634" s="36" t="n">
         <x:v>8648</x:v>
@@ -41653,7 +41653,7 @@
         <x:v>失踪与救援、成年人研究机构的危险实验、科幻战斗、角色对亲近举动的恋爱式误解笑料、职场压力。</x:v>
       </x:c>
       <x:c r="O635" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P635" s="36" t="n">
         <x:v>8649</x:v>
@@ -41718,7 +41718,7 @@
         <x:v>脱衣、内衣、胸部和性暗示笑料，强迫摆出接吻姿势，剧中女女告白。</x:v>
       </x:c>
       <x:c r="O636" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P636" s="36" t="n">
         <x:v>8672</x:v>
@@ -41783,7 +41783,7 @@
         <x:v>异世界战斗、绑架和营救、儿童角色的危险处境。</x:v>
       </x:c>
       <x:c r="O637" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P637" s="36" t="n">
         <x:v>8673</x:v>
@@ -41848,7 +41848,7 @@
         <x:v>异世界战斗、贫困与儿童危险、照护关系、能力与资源不对称、服务性镜头。</x:v>
       </x:c>
       <x:c r="O638" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P638" s="36" t="n">
         <x:v>8677</x:v>
@@ -41913,7 +41913,7 @@
         <x:v>灵魂夺取、怪物猎杀、枪械与战斗伤害、人格失控、家庭死亡与复仇、强迫、牺牲及校园／家庭创伤。</x:v>
       </x:c>
       <x:c r="O639" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P639" s="36" t="n">
         <x:v>8691</x:v>
@@ -41978,7 +41978,7 @@
         <x:v>赛车风险、争执、支配／服从与 DV 玩笑、同意边界、男性告白竞争。</x:v>
       </x:c>
       <x:c r="O640" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P640" s="36" t="n">
         <x:v>8715</x:v>
@@ -42043,7 +42043,7 @@
         <x:v>寿命诅咒、死亡与失去、收养与家庭秘密、魔法灾害、奇幻危险、危机中的强烈关切。</x:v>
       </x:c>
       <x:c r="O641" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P641" s="36" t="n">
         <x:v>8730</x:v>
@@ -42108,7 +42108,7 @@
         <x:v>战争、机甲战斗、爆炸、角色死亡、控制、囚禁、强迫作战与家人救援。</x:v>
       </x:c>
       <x:c r="O642" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P642" s="36" t="n">
         <x:v>8751</x:v>
@@ -42173,7 +42173,7 @@
         <x:v>成人向露骨性主题、触手寄生、身体控制、强迫、威胁、性暴力与同意边界问题。</x:v>
       </x:c>
       <x:c r="O643" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P643" s="36" t="n">
         <x:v>8764</x:v>
@@ -42185,7 +42185,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="S643" s="42" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="T643" s="33" t="n">
         <x:v>60</x:v>
@@ -42238,7 +42238,7 @@
         <x:v>裸露、性化身体笑料、偷窥、未经同意的身体接触、后宫式争夺、年龄与权力差异</x:v>
       </x:c>
       <x:c r="O644" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P644" s="36" t="n">
         <x:v>8776</x:v>
@@ -42303,7 +42303,7 @@
         <x:v>职场过劳；成年人与幼女形象幽灵之间的亲子式照护；幽灵、化猫的死亡与孤独回忆；仓桥—莉莉的主人／女仆语境。</x:v>
       </x:c>
       <x:c r="O645" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P645" s="36" t="n">
         <x:v>8802</x:v>
@@ -42368,7 +42368,7 @@
         <x:v>战争与恐怖袭击、血腥伤害、校园欺凌回忆、绑架、性骚扰式身体接触、泳装与裸露笑料、主从权力差。</x:v>
       </x:c>
       <x:c r="O646" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P646" s="36" t="n">
         <x:v>8847</x:v>
@@ -42433,7 +42433,7 @@
         <x:v>战斗、能量吸取、命令与再调整、强制性亲密、性化呈现、末日风险。</x:v>
       </x:c>
       <x:c r="O647" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P647" s="36" t="n">
         <x:v>8889</x:v>
@@ -42498,7 +42498,7 @@
         <x:v>成人向性化、性骚扰与羞辱、恶魔契约、拘束与囚禁、心脏夺取、命令和牺牲、战斗伤害与死亡威胁。</x:v>
       </x:c>
       <x:c r="O648" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P648" s="36" t="n">
         <x:v>8905</x:v>
@@ -42563,7 +42563,7 @@
         <x:v>战斗伤害、封印与失控、吸血与身体接触、洗澡和轻度裸露、亲友对立、世界毁灭威胁。</x:v>
       </x:c>
       <x:c r="O649" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P649" s="36" t="n">
         <x:v>8923</x:v>
@@ -42628,7 +42628,7 @@
         <x:v>海战、舰娘受伤与沉没、同伴失踪与哀伤。</x:v>
       </x:c>
       <x:c r="O650" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P650" s="36" t="n">
         <x:v>9003</x:v>
@@ -42693,7 +42693,7 @@
         <x:v>孤儿经历与双亲死亡、魔物战斗与受伤、债务压力、强制婚事安排；日文字幕文字复核，未作画面复核。</x:v>
       </x:c>
       <x:c r="O651" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P651" s="36" t="n">
         <x:v>9008</x:v>
@@ -42758,7 +42758,7 @@
         <x:v>泳装、湿身、身体暴露、破衣与服务性演出，成人笑料和性化台词，水枪碰撞及竞技受伤风险</x:v>
       </x:c>
       <x:c r="O652" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P652" s="36" t="n">
         <x:v>9039</x:v>
@@ -42823,7 +42823,7 @@
         <x:v>职场压力、身份暴露风险、网络围攻、事业暂停风险，以及身体距离和模拟告白笑料。</x:v>
       </x:c>
       <x:c r="O653" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P653" s="36" t="n">
         <x:v>9051</x:v>
@@ -42888,7 +42888,7 @@
         <x:v>战斗伤害、城市灾难、家庭创伤、反派操控和失去</x:v>
       </x:c>
       <x:c r="O654" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P654" s="36" t="n">
         <x:v>9090</x:v>
@@ -42953,7 +42953,7 @@
         <x:v>家族遇袭与死亡、复仇、实验控制与电子项圈、枪械和忍者战斗、年轻角色处于危险行动。</x:v>
       </x:c>
       <x:c r="O655" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P655" s="36" t="n">
         <x:v>9104</x:v>
@@ -43018,7 +43018,7 @@
         <x:v>魔法实验、虫害、受伤、骑士暴力、后半段黑暗惊悚与未解世界观危机。</x:v>
       </x:c>
       <x:c r="O656" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P656" s="36" t="n">
         <x:v>9109</x:v>
@@ -43083,7 +43083,7 @@
         <x:v>长期霸凌与家暴、死亡意念与自伤、性暴力威胁、血腥杀伤、操纵与洗脑。</x:v>
       </x:c>
       <x:c r="O657" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P657" s="36" t="n">
         <x:v>9111</x:v>
@@ -43148,7 +43148,7 @@
         <x:v>战斗与受伤、世界毁灭与失亲、自责、以喜剧处理的偷拍欲望和越界身体接近</x:v>
       </x:c>
       <x:c r="O658" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P658" s="36" t="n">
         <x:v>9165</x:v>
@@ -43213,7 +43213,7 @@
         <x:v>奇幻战斗、怪物与受伤、家庭与商队压力、遗迹风险和炼金事故。</x:v>
       </x:c>
       <x:c r="O659" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P659" s="36" t="n">
         <x:v>9183</x:v>
@@ -43278,7 +43278,7 @@
         <x:v>高处坠落、枪击、血腥战斗、精神控制、自杀风险、角色死亡与强烈关系依赖。</x:v>
       </x:c>
       <x:c r="O660" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P660" s="36" t="n">
         <x:v>9190</x:v>
@@ -43343,7 +43343,7 @@
         <x:v>校园喜剧中的夸张玩笑</x:v>
       </x:c>
       <x:c r="O661" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P661" s="36" t="n">
         <x:v>9193</x:v>
@@ -43408,7 +43408,7 @@
         <x:v>丧尸暴力、谋杀与尸体、封闭空间猜疑、强制投票、自伤痕迹、感染风险、人体实验威胁与遗弃。</x:v>
       </x:c>
       <x:c r="O662" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P662" s="36" t="n">
         <x:v>9233</x:v>
@@ -43473,7 +43473,7 @@
         <x:v>轻度家庭冲突、失落与误会。</x:v>
       </x:c>
       <x:c r="O663" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P663" s="36" t="n">
         <x:v>9249</x:v>
@@ -43488,7 +43488,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T663" s="33" t="str">
-        <x:v>无精确条目</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
       <x:c r="U663" s="27" t="str">
         <x:v>无</x:v>
@@ -43538,7 +43538,7 @@
         <x:v>战斗伤害、强制操控、背叛、身份与家园危机。</x:v>
       </x:c>
       <x:c r="O664" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P664" s="36" t="n">
         <x:v>9326</x:v>
@@ -43603,7 +43603,7 @@
         <x:v>超级英雄战斗、火灾与伤害、亲人死亡、贫困、母女告别、幸存者内疚、操控与情绪失控。</x:v>
       </x:c>
       <x:c r="O665" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P665" s="36" t="n">
         <x:v>9339</x:v>
@@ -43668,7 +43668,7 @@
         <x:v>酒精、性暗示、露骨玩笑、网络骚扰、隐私暴露与夸张迷恋。</x:v>
       </x:c>
       <x:c r="O666" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P666" s="36" t="n">
         <x:v>9347</x:v>
@@ -43733,7 +43733,7 @@
         <x:v>妖魔战斗、秘密组织、压力、失忆、欺凌回忆与实验威胁。</x:v>
       </x:c>
       <x:c r="O667" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P667" s="36" t="n">
         <x:v>9393</x:v>
@@ -43798,7 +43798,7 @@
         <x:v>偶像业绩与解散压力、失声与过度工作、姐妹依赖、家庭去留冲突、虚假恋爱绯闻。</x:v>
       </x:c>
       <x:c r="O668" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P668" s="36" t="n">
         <x:v>9394</x:v>
@@ -43863,7 +43863,7 @@
         <x:v>铁路衰退与地方振兴压力、同伴竞争、温泉同浴、互相搓背与同床邀请；未见明确性行为。</x:v>
       </x:c>
       <x:c r="O669" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P669" s="36" t="n">
         <x:v>9439</x:v>
@@ -43928,7 +43928,7 @@
         <x:v>竞技与胜负压力、社团存废、家庭分别、虚拟竞技冲突</x:v>
       </x:c>
       <x:c r="O670" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P670" s="36" t="n">
         <x:v>9463</x:v>
@@ -43993,7 +43993,7 @@
         <x:v>巨龙袭击、失忆与被怀疑、受伤治疗、局部异性恋委托、未复核的泳装画面</x:v>
       </x:c>
       <x:c r="O671" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P671" s="36" t="n">
         <x:v>9489</x:v>
@@ -44058,7 +44058,7 @@
         <x:v>战争与兵器化、战场死亡、人形失控和强制控制、主动求毁、记忆丧失与人格重置、枪击、火灾及儿童受伤</x:v>
       </x:c>
       <x:c r="O672" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P672" s="36" t="n">
         <x:v>9505</x:v>
@@ -44123,7 +44123,7 @@
         <x:v>武器与怪物战斗、恶梦与昏迷风险、种族歧视、家庭控制和阶级压迫。</x:v>
       </x:c>
       <x:c r="O673" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P673" s="36" t="n">
         <x:v>9508</x:v>
@@ -44188,7 +44188,7 @@
         <x:v>异变与危险动物、孤立和焦虑、昏倒、与动物同伴分离。</x:v>
       </x:c>
       <x:c r="O674" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P674" s="36" t="n">
         <x:v>9545</x:v>
@@ -44253,7 +44253,7 @@
         <x:v>三角恋、分手、嫉妒、亲吻请求与姐妹冲突。</x:v>
       </x:c>
       <x:c r="O675" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P675" s="36" t="n">
         <x:v>9571</x:v>
@@ -44318,7 +44318,7 @@
         <x:v>麻将竞赛、日常调侃、家庭争执和生日礼物的恋爱化玩笑</x:v>
       </x:c>
       <x:c r="O676" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P676" s="36" t="n">
         <x:v>9591</x:v>
@@ -44383,7 +44383,7 @@
         <x:v>企业胁迫、政治婚约、战争与死亡、家庭操纵和创伤。</x:v>
       </x:c>
       <x:c r="O677" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P677" s="36" t="n">
         <x:v>9602</x:v>
@@ -44448,7 +44448,7 @@
         <x:v>学校债务、犯罪团体威胁、绑架、武装冲突、枪击、角色创伤与死亡回忆。</x:v>
       </x:c>
       <x:c r="O678" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P678" s="36" t="n">
         <x:v>9606</x:v>
@@ -44513,7 +44513,7 @@
         <x:v>大量死亡游戏杀戮、肢解与身体恐怖、自杀及被迫牺牲、童年虐待与杀害亲属、心理操纵和背叛、剥削性师徒依附、哀伤与幸存者负罪。</x:v>
       </x:c>
       <x:c r="O679" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P679" s="36" t="n">
         <x:v>9682</x:v>
@@ -44578,7 +44578,7 @@
         <x:v>魔法战斗、疾病、记忆丢失、分离、绝望与牺牲。</x:v>
       </x:c>
       <x:c r="O680" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P680" s="36" t="n">
         <x:v>9717</x:v>
@@ -44643,7 +44643,7 @@
         <x:v>网络攻击与身份曝光、偶像产业与亲子控制、公开羞辱与校园排斥、针对性别呈现的嘲弄、创作劳动被利用、朋友间尖锐争吵、醉酒语境中的亲密行为、偶像营业式亲吻</x:v>
       </x:c>
       <x:c r="O681" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P681" s="36" t="n">
         <x:v>9745</x:v>
@@ -44708,7 +44708,7 @@
         <x:v>姐妹占有与性化、siscon 笑料、前不良、校园威胁、动物拟人和荒诞身体喜剧。</x:v>
       </x:c>
       <x:c r="O682" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P682" s="36" t="n">
         <x:v>9786</x:v>
@@ -44773,7 +44773,7 @@
         <x:v>异世界战斗、疾病治疗、伙伴冲突、监视与分离压力。</x:v>
       </x:c>
       <x:c r="O683" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P683" s="36" t="n">
         <x:v>9819</x:v>
@@ -44838,7 +44838,7 @@
         <x:v>循环、强制控制、严重暴力、心理伤害、学生孤立与亲密关系中的威胁。</x:v>
       </x:c>
       <x:c r="O684" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P684" s="36" t="n">
         <x:v>9851</x:v>
@@ -44903,7 +44903,7 @@
         <x:v>转生前后性别变化设定、战斗与政治压迫、身体接触喜剧。</x:v>
       </x:c>
       <x:c r="O685" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P685" s="36" t="n">
         <x:v>9886</x:v>
@@ -44968,7 +44968,7 @@
         <x:v>竞赛压力、伤病与状态低落、退役与分离感、以恋爱比喻表达的竞争执着。</x:v>
       </x:c>
       <x:c r="O686" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P686" s="36" t="n">
         <x:v>9888</x:v>
@@ -45033,7 +45033,7 @@
         <x:v>魔法战斗、诱骗与监禁威胁、伪造恋爱信件、家人对 boyfriend 的玩笑猜测</x:v>
       </x:c>
       <x:c r="O687" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P687" s="36" t="n">
         <x:v>9890</x:v>
@@ -45098,7 +45098,7 @@
         <x:v>女学生对成年教师的单方爱恋、师生权力差异、竞赛落选、毕业与远距离分离。</x:v>
       </x:c>
       <x:c r="O688" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P688" s="36" t="n">
         <x:v>9898</x:v>
@@ -45163,7 +45163,7 @@
         <x:v>战争、阵营冲突、死亡与失去、精神操控、姐妹式依附</x:v>
       </x:c>
       <x:c r="O689" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P689" s="36" t="n">
         <x:v>9919</x:v>
@@ -45228,7 +45228,7 @@
         <x:v>考试与阶层挫败、家族期待、魔力异常与学园危机；第 8 话出现桑拿话题但未同步画面</x:v>
       </x:c>
       <x:c r="O690" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P690" s="36" t="n">
         <x:v>9933</x:v>
@@ -45293,7 +45293,7 @@
         <x:v>末世战争、死亡、身体损伤、单向占有、仇恨、性暴力威胁与情绪失控</x:v>
       </x:c>
       <x:c r="O691" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P691" s="36" t="n">
         <x:v>9934</x:v>
@@ -45358,7 +45358,7 @@
         <x:v>运动失误、伤病与行动受限、网络骚扰、表演压力；亲近措辞未构成恋爱确认</x:v>
       </x:c>
       <x:c r="O692" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P692" s="36" t="n">
         <x:v>9935</x:v>
@@ -45423,7 +45423,7 @@
         <x:v>奴役与创伤、伤病和暴力、关系依赖及局部男→女好感</x:v>
       </x:c>
       <x:c r="O693" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P693" s="36" t="n">
         <x:v>10023</x:v>
@@ -45488,7 +45488,7 @@
         <x:v>亲密接触、操控、暴力、嫉妒与情绪伤害</x:v>
       </x:c>
       <x:c r="O694" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P694" s="36" t="n">
         <x:v>10076</x:v>
@@ -45553,7 +45553,7 @@
         <x:v>成人叙述视角、性暗示笑料、师生权力差与单向性化示好</x:v>
       </x:c>
       <x:c r="O695" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P695" s="36" t="n">
         <x:v>10077</x:v>
@@ -45618,7 +45618,7 @@
         <x:v>失散、失忆、妖怪战斗、受伤与单向告白</x:v>
       </x:c>
       <x:c r="O696" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P696" s="36" t="n">
         <x:v>10088</x:v>
@@ -45683,7 +45683,7 @@
         <x:v>末世、怪物、战斗、死亡、失去与求生压力。</x:v>
       </x:c>
       <x:c r="O697" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P697" s="36" t="n">
         <x:v>10117</x:v>
@@ -45748,7 +45748,7 @@
         <x:v>战争、兵器、死亡威胁、时间穿越、家庭压力及喜剧化恋爱表达。</x:v>
       </x:c>
       <x:c r="O698" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P698" s="36" t="n">
         <x:v>10146</x:v>
@@ -45813,7 +45813,7 @@
         <x:v>告白与交往压力、失恋、关系争执、交通事故死亡、哀悼和乐队竞争。</x:v>
       </x:c>
       <x:c r="O699" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P699" s="36" t="n">
         <x:v>10154</x:v>
@@ -45878,7 +45878,7 @@
         <x:v>心理失序、关系操控、家庭困境、乐队解散与公开身份暴露</x:v>
       </x:c>
       <x:c r="O700" s="30" t="str">
-        <x:v>有精确条目</x:v>
+        <x:v>有可对应条目</x:v>
       </x:c>
       <x:c r="P700" s="36" t="n">
         <x:v>10168</x:v>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R750879fa290141e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad645e33efb1448b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45944,7 +45944,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-12。AniList 相关度 0、无精确条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-12。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -45986,7 +45986,7 @@
         <x:v>Anime-Planet GL 标签</x:v>
       </x:c>
       <x:c r="B8" s="27" t="str">
-        <x:v>仅精确 GL 算“有”；无精确条目与没有 GL 标签分别记录。</x:v>
+        <x:v>仅可归属的 GL 算“有”；无可对应条目与没有 GL 标签分别记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
@@ -46002,7 +46002,7 @@
         <x:v>MyAnimeList Girls Love 标签</x:v>
       </x:c>
       <x:c r="B10" s="27" t="str">
-        <x:v>仅精确 Girls Love genre 算“有”。</x:v>
+        <x:v>仅能归属于本档案完整内容的 Girls Love genre 算“有”。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
@@ -46066,7 +46066,7 @@
         <x:v>Bangumi 条目状态</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>“无精确条目”表示经审计未确认到对应版本；此时 Rank 与百合标签比例保留同一字符串，不压成空白或零。</x:v>
+        <x:v>“无可对应条目”表示经审计未确认到对应版本；此时 Rank 与百合标签比例保留同一字符串，不压成空白或零。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>d9fc4ccda1257f4bcd4143b0de86781839d24434325ccaaff65c809577b7bd5f</x:v>
+        <x:v>5541e693dbff228af9c51069dc01da70f0dfea6083df5daa7ad5a03c614a33e1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>16b1a58ff8c886e9462ebff7104c9ee4aa50a850ad71158a483b15accc8fc1ed</x:v>
+        <x:v>bfdb9abdcc705ba10eef95279772dce93ecf1e11620852cbc450ea663d7bf95b</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">
@@ -46114,7 +46114,7 @@
         <x:v>状态说明</x:v>
       </x:c>
       <x:c r="B25" s="28" t="str">
-        <x:v>“无精确条目”表示经审计未确认到该数据库对应版本，不等于“没有标签”。本发布表拒绝未解释的未知数据库结果；官方三态中的“所核未见”也不等于官方否定该作品。</x:v>
+        <x:v>“无可对应条目”表示经审计未确认到该数据库对应版本，不等于“没有标签”。本发布表拒绝未解释的未知数据库结果；官方三态中的“所核未见”也不等于官方否定该作品。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R98bb68a2101c442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R53e6f140ea0c4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R82f2c4b891414229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R3eb16de2ef904ad0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad645e33efb1448b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd561dd96ebd4c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>5541e693dbff228af9c51069dc01da70f0dfea6083df5daa7ad5a03c614a33e1</x:v>
+        <x:v>b2597285288a4135fed63ac782a4d8c72fb8be914a5b9976f07109b0c316bfbf</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>bfdb9abdcc705ba10eef95279772dce93ecf1e11620852cbc450ea663d7bf95b</x:v>
+        <x:v>ffad010d783a393a71b04b10eb090bdbb9428c12c2b6f9f550be76c949fa2051</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R82f2c4b891414229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R3eb16de2ef904ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R21041f07896b49c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rf880c5c049884079"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd561dd96ebd4c36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc77b1a9e2f24c8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>b2597285288a4135fed63ac782a4d8c72fb8be914a5b9976f07109b0c316bfbf</x:v>
+        <x:v>624fc487457dc97d595020ca8baf11cc4946905639f4b58d60291d5704e74522</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>ffad010d783a393a71b04b10eb090bdbb9428c12c2b6f9f550be76c949fa2051</x:v>
+        <x:v>79347de9f2fa1010b922cbf769a4aafa9a3093366fd57b4863c7e99b6df67a66</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R21041f07896b49c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rf880c5c049884079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R7f55403cb4b64354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R496d47cc438c46c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc77b1a9e2f24c8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413607d7477c4d74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>624fc487457dc97d595020ca8baf11cc4946905639f4b58d60291d5704e74522</x:v>
+        <x:v>3033681825530d8ebf7992b045e8a1ae931af62507368f969212924d946ee7e1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>79347de9f2fa1010b922cbf769a4aafa9a3093366fd57b4863c7e99b6df67a66</x:v>
+        <x:v>58ff6be2317fc4d4702586953c68853382f3d5ee274268d2ffe7f500893d7e3e</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R8e2b71fe9d534fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R3df781ef19b54267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R0854c14ea8d3419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R854dae80d2a3469e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -783,7 +783,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T6" s="33" t="n">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="U6" s="27" t="str">
         <x:v>无</x:v>
@@ -848,7 +848,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T7" s="33" t="n">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="U7" s="27" t="str">
         <x:v>无</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T26" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U26" s="27" t="str">
         <x:v>无</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T31" s="33" t="n">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U31" s="27" t="str">
         <x:v>无</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T45" s="33" t="n">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="U45" s="27" t="str">
         <x:v>无</x:v>
@@ -5398,7 +5398,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T77" s="33" t="n">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U77" s="27" t="str">
         <x:v>无</x:v>
@@ -5788,7 +5788,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T83" s="33" t="n">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U83" s="27" t="str">
         <x:v>无</x:v>
@@ -5918,7 +5918,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T85" s="33" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U85" s="27" t="str">
         <x:v>无</x:v>
@@ -6048,7 +6048,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T87" s="33" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U87" s="27" t="str">
         <x:v>无</x:v>
@@ -9038,7 +9038,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T133" s="33" t="n">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="U133" s="27" t="str">
         <x:v>无</x:v>
@@ -14693,7 +14693,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T220" s="33" t="n">
-        <x:v>57</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U220" s="27" t="str">
         <x:v>无</x:v>
@@ -15083,7 +15083,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="T226" s="33" t="n">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="U226" s="27" t="str">
         <x:v>有</x:v>
@@ -24053,7 +24053,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T364" s="33" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U364" s="27" t="str">
         <x:v>无</x:v>
@@ -27368,7 +27368,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="T415" s="33" t="n">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U415" s="27" t="str">
         <x:v>无</x:v>
@@ -27628,7 +27628,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T419" s="33" t="n">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U419" s="27" t="str">
         <x:v>无</x:v>
@@ -29903,7 +29903,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T454" s="33" t="n">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U454" s="27" t="str">
         <x:v>无</x:v>
@@ -35038,7 +35038,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T533" s="33" t="n">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="U533" s="27" t="str">
         <x:v>无</x:v>
@@ -35103,7 +35103,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T534" s="33" t="n">
-        <x:v>65</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="U534" s="27" t="str">
         <x:v>无</x:v>
@@ -38288,7 +38288,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T583" s="33" t="n">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="U583" s="27" t="str">
         <x:v>无</x:v>
@@ -44658,7 +44658,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="T681" s="33" t="n">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U681" s="27" t="str">
         <x:v>无</x:v>
@@ -45438,7 +45438,7 @@
         <x:v>有</x:v>
       </x:c>
       <x:c r="T693" s="33" t="n">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="U693" s="27" t="str">
         <x:v>有</x:v>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc56631eb05e34109"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58b0416c6f35448c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>de3f6ee534e98b9b892d59917fead7b05034d8ca1921aeeae317c0142268fa0b</x:v>
+        <x:v>22fbd76d76362a899adef377ec688d28528e2cd2009cbe9a8141ba6696c4df77</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>28f986647a96a911aae1452bf322d3781728410ef3b78ed5d019069d56f79104</x:v>
+        <x:v>21bc9af39bbfc4f362ff9be15fc1472f560677535fec1c716f1b48bf1f9a6f65</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R0854c14ea8d3419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R854dae80d2a3469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Re248ab33ecde4b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rfb5f86fe08d642ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58b0416c6f35448c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R379c3b35998948b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>22fbd76d76362a899adef377ec688d28528e2cd2009cbe9a8141ba6696c4df77</x:v>
+        <x:v>ee935d64d4781fa76daa5726df16c5a859ef5c92b8f85d4f7866ced168447305</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>21bc9af39bbfc4f362ff9be15fc1472f560677535fec1c716f1b48bf1f9a6f65</x:v>
+        <x:v>6296482f51f505312122a33e33308600e6030fe596adf32a7aa4cf329e977cc6</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Re248ab33ecde4b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rfb5f86fe08d642ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R8faea4aae7d94d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R9768e08d45144631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>数据快照日期为 2026-08-14。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
+        <x:v>数据快照日期为 2026-08-15。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -26786,7 +26786,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="U406" s="27" t="str">
-        <x:v>无</x:v>
+        <x:v>无可对应条目</x:v>
       </x:c>
     </x:row>
     <x:row r="407" ht="57" customHeight="1">
@@ -45921,7 +45921,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R379c3b35998948b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R894f93594ee24e91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45944,7 +45944,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-14。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-15。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -46090,7 +46090,7 @@
         <x:v>数据日期</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -46098,7 +46098,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>ee935d64d4781fa76daa5726df16c5a859ef5c92b8f85d4f7866ced168447305</x:v>
+        <x:v>37b32d6787ff0f29b77d61d7127aaaf2c4efa2eb4729c9235a72e8b282ba44d3</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -46106,7 +46106,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>6296482f51f505312122a33e33308600e6030fe596adf32a7aa4cf329e977cc6</x:v>
+        <x:v>3d548821be3dc7b77b38cd38d6b31d46322845a8cd7dbdd9fe9f13fc1e58687b</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R6aa3696808154c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rdd4a5f08c8474041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra6095689f3264a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rb566acd3606845ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a509f0fee0f458d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc77a69a78c645e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>2cdbb6dc0c843afc361d1b7f617dacf09376ecf89708b0bab8596070e4120ee9</x:v>
+        <x:v>3091d2e16e5c3be3fa6e64d783c6665bbfd32c9b1d2d873057283784c83dffb1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>316521cb180cf618e1698ab14ae99cef86013b38c9d425e867daccfb2d7dd0b4</x:v>
+        <x:v>45749d542bf282a6f6cb4a08102b50d763281da29a38d8b98dee80aff32c4546</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra6095689f3264a02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rb566acd3606845ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R0fe6ccff246049be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Ra696d76ab7644fe9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc77a69a78c645e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1258d4d5331542e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>3091d2e16e5c3be3fa6e64d783c6665bbfd32c9b1d2d873057283784c83dffb1</x:v>
+        <x:v>c6fd4080e6927c4865bb80dc214aa9708a1ea408b94240041d069dd49fb1004d</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>45749d542bf282a6f6cb4a08102b50d763281da29a38d8b98dee80aff32c4546</x:v>
+        <x:v>12a3a28275ec583fddffa7b9f919d39539b570d340b7bf9b27f37bbabd9e92ae</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R0fe6ccff246049be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Ra696d76ab7644fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rb94dc656cdef4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R5f6e8e54779141f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1317,19 +1317,19 @@
         <x:v>主线</x:v>
       </x:c>
       <x:c r="C15" s="30" t="str">
-        <x:v>非百合</x:v>
+        <x:v>文类外百合阅读</x:v>
       </x:c>
       <x:c r="D15" s="30" t="str">
-        <x:v>缺席</x:v>
+        <x:v>局部</x:v>
       </x:c>
       <x:c r="E15" s="30" t="str">
-        <x:v>非恋爱</x:v>
+        <x:v>潜在恋爱</x:v>
       </x:c>
       <x:c r="F15" s="30" t="str">
         <x:v>多组异质关系</x:v>
       </x:c>
       <x:c r="G15" s="30" t="str">
-        <x:v>范围内没有性取向身份依据</x:v>
+        <x:v>只有关系性质推断，无身份自述</x:v>
       </x:c>
       <x:c r="H15" s="30" t="str">
         <x:v>所核未见</x:v>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1258d4d5331542e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7311bb17d8e44d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>c6fd4080e6927c4865bb80dc214aa9708a1ea408b94240041d069dd49fb1004d</x:v>
+        <x:v>a53cd5cdeab249536db0c9fee420feea5ff531407e0c71654867565c1ab4c394</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>12a3a28275ec583fddffa7b9f919d39539b570d340b7bf9b27f37bbabd9e92ae</x:v>
+        <x:v>f834fb02cb25d34c41bc800c93faac34afa3f01c8cb67aeac3907d741c7d3e5b</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rb94dc656cdef4881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R5f6e8e54779141f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rf19496a45c084704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R709552ad31f143df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7311bb17d8e44d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e38a5b5d4884db8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>a53cd5cdeab249536db0c9fee420feea5ff531407e0c71654867565c1ab4c394</x:v>
+        <x:v>df096331c35b5c8738723d45969c78150043ea90a76cbbc62a6e9c56e03867e4</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>f834fb02cb25d34c41bc800c93faac34afa3f01c8cb67aeac3907d741c7d3e5b</x:v>
+        <x:v>65355fd12997a670e2f48daef0bc667d76cd3e20fe16cbdda9a5b54e90aa4656</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rf19496a45c084704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R709552ad31f143df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rc28eeef9e7e247c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R9274e64f2207462d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>数据快照日期为 2026-08-16。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
+        <x:v>数据快照日期为 2026-08-17。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -5120,7 +5120,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="N73" s="27" t="str">
-        <x:v>中学生角色的亲吻、婚姻和恋爱想象被用于喜剧，部分肢体接触与恋爱台词属于角色扮演或幻想。</x:v>
+        <x:v>中学生角色的亲吻、婚姻和恋爱想象被用于喜剧；姐妹之间的单向恋爱欲望及对衣物、洗澡和同床的迷恋也被用于喜剧。</x:v>
       </x:c>
       <x:c r="O73" s="30" t="str">
         <x:v>有可对应条目</x:v>
@@ -8668,13 +8668,13 @@
         <x:v>重要副线</x:v>
       </x:c>
       <x:c r="E128" s="30" t="str">
-        <x:v>潜在恋爱</x:v>
+        <x:v>明确女女恋爱欲望</x:v>
       </x:c>
       <x:c r="F128" s="30" t="str">
         <x:v>多组异质关系</x:v>
       </x:c>
       <x:c r="G128" s="30" t="str">
-        <x:v>只有关系性质推断，无身份自述</x:v>
+        <x:v>只有明确关系／欲望事实，无身份自述</x:v>
       </x:c>
       <x:c r="H128" s="30" t="str">
         <x:v>是</x:v>
@@ -9708,13 +9708,13 @@
         <x:v>重要副线</x:v>
       </x:c>
       <x:c r="E144" s="30" t="str">
-        <x:v>潜在恋爱</x:v>
+        <x:v>明确女女恋爱欲望</x:v>
       </x:c>
       <x:c r="F144" s="30" t="str">
         <x:v>多组异质关系</x:v>
       </x:c>
       <x:c r="G144" s="30" t="str">
-        <x:v>只有关系性质推断，无身份自述</x:v>
+        <x:v>只有明确关系／欲望事实，无身份自述</x:v>
       </x:c>
       <x:c r="H144" s="30" t="str">
         <x:v>是</x:v>
@@ -29010,7 +29010,7 @@
         <x:v>文类内百合</x:v>
       </x:c>
       <x:c r="D441" s="30" t="str">
-        <x:v>重要副线</x:v>
+        <x:v>局部</x:v>
       </x:c>
       <x:c r="E441" s="30" t="str">
         <x:v>明确女女恋爱欲望</x:v>
@@ -37590,7 +37590,7 @@
         <x:v>文类内百合</x:v>
       </x:c>
       <x:c r="D573" s="30" t="str">
-        <x:v>重要副线</x:v>
+        <x:v>主线</x:v>
       </x:c>
       <x:c r="E573" s="30" t="str">
         <x:v>明确女女交往关系</x:v>
@@ -46170,7 +46170,7 @@
         <x:v>文类内百合</x:v>
       </x:c>
       <x:c r="D705" s="30" t="str">
-        <x:v>重要副线</x:v>
+        <x:v>主线</x:v>
       </x:c>
       <x:c r="E705" s="30" t="str">
         <x:v>潜在恋爱</x:v>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e38a5b5d4884db8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R031a7025b6b3475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52989,7 +52989,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-16。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-17。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -53135,7 +53135,7 @@
         <x:v>数据日期</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>df096331c35b5c8738723d45969c78150043ea90a76cbbc62a6e9c56e03867e4</x:v>
+        <x:v>13d123675e692c2ce4699de7d74e4f78512b989cffcb7ecae8ec91f714bce3b7</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>65355fd12997a670e2f48daef0bc667d76cd3e20fe16cbdda9a5b54e90aa4656</x:v>
+        <x:v>6e992e8bc8d9830f40af5561f3d1149f3b28861cba28b21f3650ee3a10ec927f</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Rc28eeef9e7e247c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R9274e64f2207462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra32e87dcafd04c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R5f88c871b5f14863"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R031a7025b6b3475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc128ec184384f6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>13d123675e692c2ce4699de7d74e4f78512b989cffcb7ecae8ec91f714bce3b7</x:v>
+        <x:v>6e1ec9771cb2f65af980168fd625824af115296ffd45c58982b4fc921bf4b180</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>6e992e8bc8d9830f40af5561f3d1149f3b28861cba28b21f3650ee3a10ec927f</x:v>
+        <x:v>816c310a45d7fab72f6f63e7416f7e568d31444047fc1cf343552d712efeea65</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">

--- a/data/yuri_classification_database_comparison.xlsx
+++ b/data/yuri_classification_database_comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="Ra32e87dcafd04c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="R5f88c871b5f14863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据库标签对照" sheetId="1" r:id="R1624c2f30eda455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" r:id="Rfba004b48f7848fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,7 +571,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>数据快照日期为 2026-08-17。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
+        <x:v>数据快照日期为 2026-08-18。分类字段来自正篇材料的分层判断；官方证据与四个数据库字段用于对照，不是对作品关系的投票或裁决。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -52966,7 +52966,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc128ec184384f6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc364b2d87a5846d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52989,7 +52989,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>比较快照日期：2026-08-17。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
+        <x:v>比较快照日期：2026-08-18。AniList 相关度 0、无可对应条目、未知、所核未见和资料不足不是同一个状态。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -53135,7 +53135,7 @@
         <x:v>数据日期</x:v>
       </x:c>
       <x:c r="B22" s="27" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -53143,7 +53143,7 @@
         <x:v>数据库源 SHA-256</x:v>
       </x:c>
       <x:c r="B23" s="27" t="str">
-        <x:v>6e1ec9771cb2f65af980168fd625824af115296ffd45c58982b4fc921bf4b180</x:v>
+        <x:v>6d4d1e1892417249d5ab6a1cb821b2390793ecdee9f7867e9f39bc2a97ff79d0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -53151,7 +53151,7 @@
         <x:v>发布计划 SHA-256</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>816c310a45d7fab72f6f63e7416f7e568d31444047fc1cf343552d712efeea65</x:v>
+        <x:v>ee301e9668a48755b18b19cc7d5f57f711e73a1c1c5473f6828131b2320cd68b</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">
